--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.59.0</t>
+    <t>0.61.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T16:26:13+00:00</t>
+    <t>2024-07-24T18:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.354</t>
+    <t>0.66.364</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-19T08:45:12+00:00</t>
+    <t>2024-10-02T18:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5201" uniqueCount="892">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5201" uniqueCount="891">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1310,7 +1310,7 @@
     <t>MedicationRequest.requester</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitioner|http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient|http://hl7.org/fhir/us/core/StructureDefinition/us-core-organization|http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitionerrole|http://hl7.org/fhir/us/core/StructureDefinition/us-core-relatedperson|Device)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Practitioner)
 </t>
   </si>
   <si>
@@ -1379,10 +1379,6 @@
   </si>
   <si>
     <t>MedicationRequest.recorder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole)
-</t>
   </si>
   <si>
     <t>Person who entered the request</t>
@@ -9057,13 +9053,13 @@
         <v>83</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -9129,22 +9125,22 @@
         <v>104</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AL49" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="AL49" t="s" s="2">
+      <c r="AM49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO49" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="AM49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO49" t="s" s="2">
+      <c r="AP49" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="AP49" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>83</v>
@@ -9152,10 +9148,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -9181,13 +9177,13 @@
         <v>256</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -9216,11 +9212,11 @@
         <v>317</v>
       </c>
       <c r="Y50" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="Z50" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="Z50" t="s" s="2">
-        <v>449</v>
-      </c>
       <c r="AA50" t="s" s="2">
         <v>83</v>
       </c>
@@ -9237,7 +9233,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -9258,27 +9254,27 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AN50" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="AN50" t="s" s="2">
+      <c r="AO50" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="AO50" t="s" s="2">
+      <c r="AP50" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="AP50" t="s" s="2">
+      <c r="AQ50" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="AQ50" t="s" s="2">
-        <v>454</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -9301,16 +9297,16 @@
         <v>83</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -9360,7 +9356,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -9381,16 +9377,16 @@
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>310</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>83</v>
@@ -9398,10 +9394,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9424,13 +9420,13 @@
         <v>93</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -9481,7 +9477,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -9502,13 +9498,13 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO52" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>83</v>
@@ -9519,10 +9515,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9548,10 +9544,10 @@
         <v>106</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>470</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -9602,7 +9598,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -9629,7 +9625,7 @@
         <v>83</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>83</v>
@@ -9640,10 +9636,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9666,13 +9662,13 @@
         <v>93</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -9723,7 +9719,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -9744,13 +9740,13 @@
         <v>83</v>
       </c>
       <c r="AM54" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO54" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>476</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>83</v>
@@ -9761,10 +9757,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9790,14 +9786,14 @@
         <v>234</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>478</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>479</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -9846,7 +9842,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -9867,13 +9863,13 @@
         <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO55" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>482</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>83</v>
@@ -9884,10 +9880,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9913,13 +9909,13 @@
         <v>256</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>485</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>486</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9948,11 +9944,11 @@
         <v>317</v>
       </c>
       <c r="Y56" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="Z56" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="Z56" t="s" s="2">
-        <v>488</v>
-      </c>
       <c r="AA56" t="s" s="2">
         <v>83</v>
       </c>
@@ -9969,7 +9965,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -9996,7 +9992,7 @@
         <v>83</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>83</v>
@@ -10007,10 +10003,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -10033,13 +10029,13 @@
         <v>83</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -10090,7 +10086,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -10111,13 +10107,13 @@
         <v>83</v>
       </c>
       <c r="AM57" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO57" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>495</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>83</v>
@@ -10128,10 +10124,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -10154,13 +10150,13 @@
         <v>83</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="M58" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>499</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -10211,7 +10207,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -10226,19 +10222,19 @@
         <v>104</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM58" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="AL58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM58" t="s" s="2">
+      <c r="AN58" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="AN58" t="s" s="2">
+      <c r="AO58" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>503</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>83</v>
@@ -10249,10 +10245,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10275,16 +10271,16 @@
         <v>83</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>508</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -10334,7 +10330,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -10355,13 +10351,13 @@
         <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO59" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>83</v>
@@ -10372,10 +10368,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10493,10 +10489,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10616,14 +10612,14 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -10645,10 +10641,10 @@
         <v>137</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="N62" t="s" s="2">
         <v>180</v>
@@ -10703,7 +10699,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -10741,10 +10737,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10767,17 +10763,17 @@
         <v>93</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>520</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>521</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -10826,7 +10822,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -10853,21 +10849,21 @@
         <v>83</v>
       </c>
       <c r="AO63" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AP63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ63" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="AP63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ63" t="s" s="2">
-        <v>525</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10893,14 +10889,14 @@
         <v>151</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -10949,7 +10945,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -10976,21 +10972,21 @@
         <v>83</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -11016,16 +11012,16 @@
         <v>256</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>533</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="N65" t="s" s="2">
         <v>534</v>
       </c>
-      <c r="N65" t="s" s="2">
+      <c r="O65" t="s" s="2">
         <v>535</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>536</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>83</v>
@@ -11053,28 +11049,28 @@
         <v>317</v>
       </c>
       <c r="Y65" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="Z65" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="Z65" t="s" s="2">
+      <c r="AA65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF65" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>539</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -11101,21 +11097,21 @@
         <v>83</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ65" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -11141,10 +11137,10 @@
         <v>151</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>542</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>543</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -11195,7 +11191,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -11210,7 +11206,7 @@
         <v>104</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>83</v>
@@ -11222,21 +11218,21 @@
         <v>83</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ66" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11259,19 +11255,19 @@
         <v>93</v>
       </c>
       <c r="K67" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="L67" t="s" s="2">
         <v>547</v>
       </c>
-      <c r="L67" t="s" s="2">
+      <c r="M67" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>549</v>
       </c>
-      <c r="N67" t="s" s="2">
+      <c r="O67" t="s" s="2">
         <v>550</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>551</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -11320,7 +11316,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -11347,7 +11343,7 @@
         <v>83</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>83</v>
@@ -11358,10 +11354,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11479,10 +11475,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11602,14 +11598,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -11631,10 +11627,10 @@
         <v>137</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>180</v>
@@ -11689,7 +11685,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -11727,10 +11723,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11756,14 +11752,14 @@
         <v>403</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>558</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>559</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -11812,7 +11808,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -11839,7 +11835,7 @@
         <v>83</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>83</v>
@@ -11850,10 +11846,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11876,17 +11872,17 @@
         <v>93</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="L72" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="L72" t="s" s="2">
+      <c r="M72" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>566</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>83</v>
@@ -11935,34 +11931,34 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
         <v>568</v>
       </c>
-      <c r="AG72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH72" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ72" t="s" s="2">
+      <c r="AK72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO72" t="s" s="2">
         <v>569</v>
-      </c>
-      <c r="AK72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>570</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>83</v>
@@ -11973,10 +11969,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -12094,10 +12090,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12217,10 +12213,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12243,13 +12239,13 @@
         <v>93</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="L75" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="L75" t="s" s="2">
+      <c r="M75" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>576</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -12298,7 +12294,7 @@
         <v>141</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -12325,7 +12321,7 @@
         <v>83</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>83</v>
@@ -12336,13 +12332,13 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="C76" t="s" s="2">
         <v>579</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="C76" t="s" s="2">
-        <v>580</v>
       </c>
       <c r="D76" t="s" s="2">
         <v>83</v>
@@ -12367,10 +12363,10 @@
         <v>288</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>576</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -12421,7 +12417,7 @@
         <v>83</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -12448,7 +12444,7 @@
         <v>83</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>83</v>
@@ -12459,10 +12455,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="B77" t="s" s="2">
         <v>581</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>582</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12580,10 +12576,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="B78" t="s" s="2">
         <v>583</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>584</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12703,10 +12699,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="B79" t="s" s="2">
         <v>585</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>586</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12732,13 +12728,13 @@
         <v>403</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>587</v>
       </c>
-      <c r="M79" t="s" s="2">
+      <c r="N79" t="s" s="2">
         <v>588</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>589</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -12788,48 +12784,48 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI79" t="s" s="2">
         <v>590</v>
-      </c>
-      <c r="AG79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH79" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI79" t="s" s="2">
-        <v>591</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK79" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="AL79" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="AL79" t="s" s="2">
+      <c r="AM79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO79" t="s" s="2">
         <v>593</v>
       </c>
-      <c r="AM79" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN79" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO79" t="s" s="2">
+      <c r="AP79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ79" t="s" s="2">
         <v>594</v>
-      </c>
-      <c r="AP79" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ79" t="s" s="2">
-        <v>595</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="B80" t="s" s="2">
         <v>596</v>
-      </c>
-      <c r="B80" t="s" s="2">
-        <v>597</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12855,66 +12851,66 @@
         <v>403</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>598</v>
       </c>
-      <c r="M80" t="s" s="2">
+      <c r="N80" t="s" s="2">
         <v>599</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>600</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q80" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="R80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF80" t="s" s="2">
         <v>601</v>
       </c>
-      <c r="R80" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S80" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T80" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U80" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V80" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W80" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X80" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y80" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z80" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>602</v>
-      </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
       </c>
@@ -12922,7 +12918,7 @@
         <v>92</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>104</v>
@@ -12940,21 +12936,21 @@
         <v>83</v>
       </c>
       <c r="AO80" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="AP80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ80" t="s" s="2">
         <v>603</v>
-      </c>
-      <c r="AP80" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ80" t="s" s="2">
-        <v>604</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12977,19 +12973,19 @@
         <v>93</v>
       </c>
       <c r="K81" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="L81" t="s" s="2">
         <v>606</v>
       </c>
-      <c r="L81" t="s" s="2">
+      <c r="M81" t="s" s="2">
         <v>607</v>
       </c>
-      <c r="M81" t="s" s="2">
+      <c r="N81" t="s" s="2">
         <v>608</v>
       </c>
-      <c r="N81" t="s" s="2">
+      <c r="O81" t="s" s="2">
         <v>609</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>610</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>83</v>
@@ -13038,7 +13034,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -13065,7 +13061,7 @@
         <v>83</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="AP81" t="s" s="2">
         <v>83</v>
@@ -13076,10 +13072,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13102,13 +13098,13 @@
         <v>93</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>614</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>615</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -13159,7 +13155,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -13186,7 +13182,7 @@
         <v>83</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>83</v>
@@ -13197,10 +13193,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13223,19 +13219,19 @@
         <v>93</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="L83" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="L83" t="s" s="2">
+      <c r="M83" t="s" s="2">
         <v>619</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>620</v>
       </c>
-      <c r="N83" t="s" s="2">
+      <c r="O83" t="s" s="2">
         <v>621</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>622</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>83</v>
@@ -13284,7 +13280,7 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -13311,7 +13307,7 @@
         <v>83</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>83</v>
@@ -13322,10 +13318,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13348,19 +13344,19 @@
         <v>93</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>626</v>
       </c>
-      <c r="M84" t="s" s="2">
-        <v>627</v>
-      </c>
       <c r="N84" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="O84" t="s" s="2">
         <v>621</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>622</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>83</v>
@@ -13409,7 +13405,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -13436,7 +13432,7 @@
         <v>83</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>83</v>
@@ -13447,10 +13443,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13476,10 +13472,10 @@
         <v>112</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>630</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>631</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -13509,28 +13505,28 @@
         <v>250</v>
       </c>
       <c r="Y85" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="Z85" t="s" s="2">
         <v>632</v>
       </c>
-      <c r="Z85" t="s" s="2">
+      <c r="AA85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF85" t="s" s="2">
         <v>633</v>
-      </c>
-      <c r="AA85" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB85" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD85" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE85" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>634</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -13557,7 +13553,7 @@
         <v>83</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>83</v>
@@ -13568,10 +13564,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13594,13 +13590,13 @@
         <v>93</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>637</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>638</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -13608,52 +13604,52 @@
         <v>83</v>
       </c>
       <c r="Q86" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="R86" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF86" t="s" s="2">
         <v>639</v>
-      </c>
-      <c r="R86" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S86" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T86" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U86" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V86" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W86" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X86" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y86" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z86" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA86" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB86" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC86" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD86" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE86" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF86" t="s" s="2">
-        <v>640</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -13680,7 +13676,7 @@
         <v>83</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>83</v>
@@ -13691,10 +13687,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13717,13 +13713,13 @@
         <v>93</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>642</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>643</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -13774,7 +13770,7 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -13801,7 +13797,7 @@
         <v>83</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>83</v>
@@ -13812,10 +13808,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13838,13 +13834,13 @@
         <v>93</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -13895,7 +13891,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -13922,7 +13918,7 @@
         <v>83</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>83</v>
@@ -13933,10 +13929,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13959,13 +13955,13 @@
         <v>93</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="M89" t="s" s="2">
         <v>649</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>650</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -14016,7 +14012,7 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -14043,7 +14039,7 @@
         <v>83</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="AP89" t="s" s="2">
         <v>83</v>
@@ -14054,10 +14050,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14083,10 +14079,10 @@
         <v>112</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -14116,11 +14112,11 @@
         <v>250</v>
       </c>
       <c r="Y90" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="Z90" t="s" s="2">
         <v>632</v>
       </c>
-      <c r="Z90" t="s" s="2">
-        <v>633</v>
-      </c>
       <c r="AA90" t="s" s="2">
         <v>83</v>
       </c>
@@ -14137,7 +14133,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -14164,7 +14160,7 @@
         <v>83</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>83</v>
@@ -14175,10 +14171,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14204,13 +14200,13 @@
         <v>112</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>656</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>657</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>658</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -14240,25 +14236,25 @@
       </c>
       <c r="Y91" s="2"/>
       <c r="Z91" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF91" t="s" s="2">
         <v>659</v>
-      </c>
-      <c r="AA91" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB91" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC91" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD91" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE91" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF91" t="s" s="2">
-        <v>660</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -14296,10 +14292,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14322,16 +14318,16 @@
         <v>93</v>
       </c>
       <c r="K92" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="L92" t="s" s="2">
         <v>662</v>
       </c>
-      <c r="L92" t="s" s="2">
+      <c r="M92" t="s" s="2">
         <v>663</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>664</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>665</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -14381,7 +14377,7 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -14419,10 +14415,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14448,16 +14444,16 @@
         <v>112</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>668</v>
       </c>
-      <c r="M93" t="s" s="2">
+      <c r="N93" t="s" s="2">
         <v>669</v>
       </c>
-      <c r="N93" t="s" s="2">
+      <c r="O93" t="s" s="2">
         <v>670</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>671</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>83</v>
@@ -14485,28 +14481,28 @@
         <v>250</v>
       </c>
       <c r="Y93" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="Z93" t="s" s="2">
         <v>672</v>
       </c>
-      <c r="Z93" t="s" s="2">
+      <c r="AA93" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF93" t="s" s="2">
         <v>673</v>
-      </c>
-      <c r="AA93" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB93" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC93" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD93" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE93" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF93" t="s" s="2">
-        <v>674</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -14533,7 +14529,7 @@
         <v>83</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>83</v>
@@ -14544,10 +14540,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14570,13 +14566,13 @@
         <v>93</v>
       </c>
       <c r="K94" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="L94" t="s" s="2">
         <v>677</v>
       </c>
-      <c r="L94" t="s" s="2">
+      <c r="M94" t="s" s="2">
         <v>678</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>679</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -14627,7 +14623,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -14654,7 +14650,7 @@
         <v>83</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>83</v>
@@ -14665,10 +14661,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14694,13 +14690,13 @@
         <v>256</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>683</v>
       </c>
-      <c r="M95" t="s" s="2">
+      <c r="N95" t="s" s="2">
         <v>684</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>685</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -14729,28 +14725,28 @@
         <v>116</v>
       </c>
       <c r="Y95" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="Z95" t="s" s="2">
         <v>686</v>
       </c>
-      <c r="Z95" t="s" s="2">
+      <c r="AA95" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF95" t="s" s="2">
         <v>687</v>
-      </c>
-      <c r="AA95" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB95" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC95" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD95" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE95" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF95" t="s" s="2">
-        <v>688</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -14777,7 +14773,7 @@
         <v>83</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>83</v>
@@ -14788,10 +14784,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14814,16 +14810,16 @@
         <v>93</v>
       </c>
       <c r="K96" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="L96" t="s" s="2">
         <v>691</v>
       </c>
-      <c r="L96" t="s" s="2">
+      <c r="M96" t="s" s="2">
         <v>692</v>
       </c>
-      <c r="M96" t="s" s="2">
+      <c r="N96" t="s" s="2">
         <v>693</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>694</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -14852,28 +14848,28 @@
         <v>317</v>
       </c>
       <c r="Y96" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="Z96" t="s" s="2">
         <v>695</v>
       </c>
-      <c r="Z96" t="s" s="2">
+      <c r="AA96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF96" t="s" s="2">
         <v>696</v>
-      </c>
-      <c r="AA96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF96" t="s" s="2">
-        <v>697</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -14900,21 +14896,21 @@
         <v>83</v>
       </c>
       <c r="AO96" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="AP96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ96" t="s" s="2">
         <v>698</v>
-      </c>
-      <c r="AP96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ96" t="s" s="2">
-        <v>699</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14940,16 +14936,16 @@
         <v>256</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="M97" t="s" s="2">
         <v>701</v>
       </c>
-      <c r="M97" t="s" s="2">
+      <c r="N97" t="s" s="2">
         <v>702</v>
       </c>
-      <c r="N97" t="s" s="2">
+      <c r="O97" t="s" s="2">
         <v>703</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>704</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>83</v>
@@ -14977,28 +14973,28 @@
         <v>317</v>
       </c>
       <c r="Y97" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="Z97" t="s" s="2">
         <v>705</v>
       </c>
-      <c r="Z97" t="s" s="2">
+      <c r="AA97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF97" t="s" s="2">
         <v>706</v>
-      </c>
-      <c r="AA97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF97" t="s" s="2">
-        <v>707</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -15025,21 +15021,21 @@
         <v>83</v>
       </c>
       <c r="AO97" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="AP97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ97" t="s" s="2">
         <v>708</v>
-      </c>
-      <c r="AP97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ97" t="s" s="2">
-        <v>709</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -15065,14 +15061,14 @@
         <v>256</v>
       </c>
       <c r="L98" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="M98" t="s" s="2">
         <v>711</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>712</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>83</v>
@@ -15100,28 +15096,28 @@
         <v>317</v>
       </c>
       <c r="Y98" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="Z98" t="s" s="2">
         <v>714</v>
       </c>
-      <c r="Z98" t="s" s="2">
+      <c r="AA98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF98" t="s" s="2">
         <v>715</v>
-      </c>
-      <c r="AA98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF98" t="s" s="2">
-        <v>716</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -15148,21 +15144,21 @@
         <v>83</v>
       </c>
       <c r="AO98" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="AP98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ98" t="s" s="2">
         <v>717</v>
-      </c>
-      <c r="AP98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ98" t="s" s="2">
-        <v>718</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15188,16 +15184,16 @@
         <v>256</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>720</v>
       </c>
-      <c r="M99" t="s" s="2">
+      <c r="N99" t="s" s="2">
         <v>721</v>
       </c>
-      <c r="N99" t="s" s="2">
+      <c r="O99" t="s" s="2">
         <v>722</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>723</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>83</v>
@@ -15225,28 +15221,28 @@
         <v>317</v>
       </c>
       <c r="Y99" t="s" s="2">
+        <v>723</v>
+      </c>
+      <c r="Z99" t="s" s="2">
         <v>724</v>
       </c>
-      <c r="Z99" t="s" s="2">
+      <c r="AA99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF99" t="s" s="2">
         <v>725</v>
-      </c>
-      <c r="AA99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF99" t="s" s="2">
-        <v>726</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -15273,21 +15269,21 @@
         <v>83</v>
       </c>
       <c r="AO99" t="s" s="2">
+        <v>726</v>
+      </c>
+      <c r="AP99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ99" t="s" s="2">
         <v>727</v>
-      </c>
-      <c r="AP99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ99" t="s" s="2">
-        <v>728</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15310,13 +15306,13 @@
         <v>93</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>729</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>730</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>731</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -15367,7 +15363,7 @@
         <v>83</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
@@ -15400,15 +15396,15 @@
         <v>83</v>
       </c>
       <c r="AQ100" t="s" s="2">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15526,10 +15522,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15649,10 +15645,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15678,14 +15674,14 @@
         <v>256</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>736</v>
+      </c>
+      <c r="M103" t="s" s="2">
         <v>737</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>738</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" t="s" s="2">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>83</v>
@@ -15713,28 +15709,28 @@
         <v>317</v>
       </c>
       <c r="Y103" t="s" s="2">
+        <v>739</v>
+      </c>
+      <c r="Z103" t="s" s="2">
         <v>740</v>
       </c>
-      <c r="Z103" t="s" s="2">
+      <c r="AA103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF103" t="s" s="2">
         <v>741</v>
-      </c>
-      <c r="AA103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF103" t="s" s="2">
-        <v>742</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>81</v>
@@ -15767,15 +15763,15 @@
         <v>83</v>
       </c>
       <c r="AQ103" t="s" s="2">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15798,19 +15794,19 @@
         <v>93</v>
       </c>
       <c r="K104" t="s" s="2">
+        <v>744</v>
+      </c>
+      <c r="L104" t="s" s="2">
         <v>745</v>
       </c>
-      <c r="L104" t="s" s="2">
+      <c r="M104" t="s" s="2">
         <v>746</v>
       </c>
-      <c r="M104" t="s" s="2">
+      <c r="N104" t="s" s="2">
         <v>747</v>
       </c>
-      <c r="N104" t="s" s="2">
+      <c r="O104" t="s" s="2">
         <v>748</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>749</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>83</v>
@@ -15859,7 +15855,7 @@
         <v>83</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>81</v>
@@ -15886,21 +15882,21 @@
         <v>83</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="AP104" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ104" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15923,19 +15919,19 @@
         <v>93</v>
       </c>
       <c r="K105" t="s" s="2">
+        <v>752</v>
+      </c>
+      <c r="L105" t="s" s="2">
         <v>753</v>
       </c>
-      <c r="L105" t="s" s="2">
+      <c r="M105" t="s" s="2">
         <v>754</v>
       </c>
-      <c r="M105" t="s" s="2">
+      <c r="N105" t="s" s="2">
         <v>755</v>
       </c>
-      <c r="N105" t="s" s="2">
+      <c r="O105" t="s" s="2">
         <v>756</v>
-      </c>
-      <c r="O105" t="s" s="2">
-        <v>757</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>83</v>
@@ -15984,7 +15980,7 @@
         <v>83</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
@@ -16011,21 +16007,21 @@
         <v>83</v>
       </c>
       <c r="AO105" t="s" s="2">
+        <v>758</v>
+      </c>
+      <c r="AP105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ105" t="s" s="2">
         <v>759</v>
-      </c>
-      <c r="AP105" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ105" t="s" s="2">
-        <v>760</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -16048,19 +16044,19 @@
         <v>93</v>
       </c>
       <c r="K106" t="s" s="2">
+        <v>761</v>
+      </c>
+      <c r="L106" t="s" s="2">
         <v>762</v>
       </c>
-      <c r="L106" t="s" s="2">
+      <c r="M106" t="s" s="2">
         <v>763</v>
       </c>
-      <c r="M106" t="s" s="2">
+      <c r="N106" t="s" s="2">
         <v>764</v>
       </c>
-      <c r="N106" t="s" s="2">
+      <c r="O106" t="s" s="2">
         <v>765</v>
-      </c>
-      <c r="O106" t="s" s="2">
-        <v>766</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>83</v>
@@ -16109,7 +16105,7 @@
         <v>83</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
@@ -16136,21 +16132,21 @@
         <v>83</v>
       </c>
       <c r="AO106" t="s" s="2">
+        <v>767</v>
+      </c>
+      <c r="AP106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ106" t="s" s="2">
         <v>768</v>
-      </c>
-      <c r="AP106" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ106" t="s" s="2">
-        <v>769</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -16173,19 +16169,19 @@
         <v>93</v>
       </c>
       <c r="K107" t="s" s="2">
+        <v>770</v>
+      </c>
+      <c r="L107" t="s" s="2">
         <v>771</v>
       </c>
-      <c r="L107" t="s" s="2">
+      <c r="M107" t="s" s="2">
         <v>772</v>
       </c>
-      <c r="M107" t="s" s="2">
+      <c r="N107" t="s" s="2">
         <v>773</v>
       </c>
-      <c r="N107" t="s" s="2">
+      <c r="O107" t="s" s="2">
         <v>774</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>775</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>83</v>
@@ -16234,7 +16230,7 @@
         <v>83</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -16261,7 +16257,7 @@
         <v>83</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="AP107" t="s" s="2">
         <v>83</v>
@@ -16272,10 +16268,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -16298,17 +16294,17 @@
         <v>93</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="L108" t="s" s="2">
+        <v>778</v>
+      </c>
+      <c r="M108" t="s" s="2">
         <v>779</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>780</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" t="s" s="2">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>83</v>
@@ -16357,7 +16353,7 @@
         <v>83</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -16384,7 +16380,7 @@
         <v>83</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="AP108" t="s" s="2">
         <v>83</v>
@@ -16395,10 +16391,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16421,13 +16417,13 @@
         <v>83</v>
       </c>
       <c r="K109" t="s" s="2">
+        <v>783</v>
+      </c>
+      <c r="L109" t="s" s="2">
         <v>784</v>
       </c>
-      <c r="L109" t="s" s="2">
+      <c r="M109" t="s" s="2">
         <v>785</v>
-      </c>
-      <c r="M109" t="s" s="2">
-        <v>786</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -16478,7 +16474,7 @@
         <v>83</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
@@ -16502,10 +16498,10 @@
         <v>83</v>
       </c>
       <c r="AN109" t="s" s="2">
+        <v>786</v>
+      </c>
+      <c r="AO109" t="s" s="2">
         <v>787</v>
-      </c>
-      <c r="AO109" t="s" s="2">
-        <v>788</v>
       </c>
       <c r="AP109" t="s" s="2">
         <v>83</v>
@@ -16516,10 +16512,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -16637,10 +16633,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16760,14 +16756,14 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
@@ -16789,10 +16785,10 @@
         <v>137</v>
       </c>
       <c r="L112" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M112" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="N112" t="s" s="2">
         <v>180</v>
@@ -16847,7 +16843,7 @@
         <v>83</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
@@ -16885,10 +16881,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16911,16 +16907,16 @@
         <v>83</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="L113" t="s" s="2">
+        <v>792</v>
+      </c>
+      <c r="M113" t="s" s="2">
         <v>793</v>
       </c>
-      <c r="M113" t="s" s="2">
+      <c r="N113" t="s" s="2">
         <v>794</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>795</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -16970,7 +16966,7 @@
         <v>83</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
@@ -16997,7 +16993,7 @@
         <v>83</v>
       </c>
       <c r="AO113" t="s" s="2">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AP113" t="s" s="2">
         <v>83</v>
@@ -17008,10 +17004,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -17129,10 +17125,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -17252,14 +17248,14 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
@@ -17281,10 +17277,10 @@
         <v>137</v>
       </c>
       <c r="L116" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M116" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="M116" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="N116" t="s" s="2">
         <v>180</v>
@@ -17339,7 +17335,7 @@
         <v>83</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>81</v>
@@ -17377,10 +17373,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -17403,13 +17399,13 @@
         <v>83</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="L117" t="s" s="2">
+        <v>800</v>
+      </c>
+      <c r="M117" t="s" s="2">
         <v>801</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>802</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -17460,7 +17456,7 @@
         <v>83</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>81</v>
@@ -17487,7 +17483,7 @@
         <v>83</v>
       </c>
       <c r="AO117" t="s" s="2">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="AP117" t="s" s="2">
         <v>83</v>
@@ -17498,10 +17494,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -17524,13 +17520,13 @@
         <v>83</v>
       </c>
       <c r="K118" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="L118" t="s" s="2">
         <v>805</v>
       </c>
-      <c r="L118" t="s" s="2">
+      <c r="M118" t="s" s="2">
         <v>806</v>
-      </c>
-      <c r="M118" t="s" s="2">
-        <v>807</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -17581,7 +17577,7 @@
         <v>83</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>81</v>
@@ -17608,7 +17604,7 @@
         <v>83</v>
       </c>
       <c r="AO118" t="s" s="2">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="AP118" t="s" s="2">
         <v>83</v>
@@ -17619,10 +17615,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -17645,13 +17641,13 @@
         <v>83</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="L119" t="s" s="2">
+        <v>809</v>
+      </c>
+      <c r="M119" t="s" s="2">
         <v>810</v>
-      </c>
-      <c r="M119" t="s" s="2">
-        <v>811</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -17702,7 +17698,7 @@
         <v>83</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>81</v>
@@ -17729,7 +17725,7 @@
         <v>83</v>
       </c>
       <c r="AO119" t="s" s="2">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="AP119" t="s" s="2">
         <v>83</v>
@@ -17740,10 +17736,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17769,16 +17765,16 @@
         <v>288</v>
       </c>
       <c r="L120" t="s" s="2">
+        <v>812</v>
+      </c>
+      <c r="M120" t="s" s="2">
         <v>813</v>
       </c>
-      <c r="M120" t="s" s="2">
+      <c r="N120" t="s" s="2">
         <v>814</v>
       </c>
-      <c r="N120" t="s" s="2">
+      <c r="O120" t="s" s="2">
         <v>815</v>
-      </c>
-      <c r="O120" t="s" s="2">
-        <v>816</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>83</v>
@@ -17827,7 +17823,7 @@
         <v>83</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>81</v>
@@ -17851,10 +17847,10 @@
         <v>83</v>
       </c>
       <c r="AN120" t="s" s="2">
+        <v>816</v>
+      </c>
+      <c r="AO120" t="s" s="2">
         <v>817</v>
-      </c>
-      <c r="AO120" t="s" s="2">
-        <v>818</v>
       </c>
       <c r="AP120" t="s" s="2">
         <v>83</v>
@@ -17865,10 +17861,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17891,16 +17887,16 @@
         <v>83</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="L121" t="s" s="2">
+        <v>819</v>
+      </c>
+      <c r="M121" t="s" s="2">
         <v>820</v>
       </c>
-      <c r="M121" t="s" s="2">
+      <c r="N121" t="s" s="2">
         <v>821</v>
-      </c>
-      <c r="N121" t="s" s="2">
-        <v>822</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -17950,7 +17946,7 @@
         <v>83</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>81</v>
@@ -17965,33 +17961,33 @@
         <v>104</v>
       </c>
       <c r="AK121" t="s" s="2">
+        <v>822</v>
+      </c>
+      <c r="AL121" t="s" s="2">
         <v>823</v>
       </c>
-      <c r="AL121" t="s" s="2">
+      <c r="AM121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN121" t="s" s="2">
         <v>824</v>
       </c>
-      <c r="AM121" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN121" t="s" s="2">
+      <c r="AO121" t="s" s="2">
         <v>825</v>
       </c>
-      <c r="AO121" t="s" s="2">
+      <c r="AP121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ121" t="s" s="2">
         <v>826</v>
-      </c>
-      <c r="AP121" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ121" t="s" s="2">
-        <v>827</v>
       </c>
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -18014,13 +18010,13 @@
         <v>83</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="L122" t="s" s="2">
+        <v>828</v>
+      </c>
+      <c r="M122" t="s" s="2">
         <v>829</v>
-      </c>
-      <c r="M122" t="s" s="2">
-        <v>830</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -18071,7 +18067,7 @@
         <v>83</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>81</v>
@@ -18086,33 +18082,33 @@
         <v>104</v>
       </c>
       <c r="AK122" t="s" s="2">
+        <v>830</v>
+      </c>
+      <c r="AL122" t="s" s="2">
         <v>831</v>
       </c>
-      <c r="AL122" t="s" s="2">
+      <c r="AM122" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN122" t="s" s="2">
         <v>832</v>
       </c>
-      <c r="AM122" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN122" t="s" s="2">
+      <c r="AO122" t="s" s="2">
         <v>833</v>
       </c>
-      <c r="AO122" t="s" s="2">
+      <c r="AP122" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ122" t="s" s="2">
         <v>834</v>
-      </c>
-      <c r="AP122" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ122" t="s" s="2">
-        <v>835</v>
       </c>
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -18135,16 +18131,16 @@
         <v>83</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="L123" t="s" s="2">
+        <v>836</v>
+      </c>
+      <c r="M123" t="s" s="2">
         <v>837</v>
       </c>
-      <c r="M123" t="s" s="2">
+      <c r="N123" t="s" s="2">
         <v>838</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>839</v>
       </c>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
@@ -18194,7 +18190,7 @@
         <v>83</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>81</v>
@@ -18209,19 +18205,19 @@
         <v>104</v>
       </c>
       <c r="AK123" t="s" s="2">
+        <v>839</v>
+      </c>
+      <c r="AL123" t="s" s="2">
         <v>840</v>
       </c>
-      <c r="AL123" t="s" s="2">
+      <c r="AM123" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN123" t="s" s="2">
         <v>841</v>
       </c>
-      <c r="AM123" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN123" t="s" s="2">
+      <c r="AO123" t="s" s="2">
         <v>842</v>
-      </c>
-      <c r="AO123" t="s" s="2">
-        <v>843</v>
       </c>
       <c r="AP123" t="s" s="2">
         <v>83</v>
@@ -18232,10 +18228,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -18261,10 +18257,10 @@
         <v>295</v>
       </c>
       <c r="L124" t="s" s="2">
+        <v>844</v>
+      </c>
+      <c r="M124" t="s" s="2">
         <v>845</v>
-      </c>
-      <c r="M124" t="s" s="2">
-        <v>846</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -18315,7 +18311,7 @@
         <v>83</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>81</v>
@@ -18342,10 +18338,10 @@
         <v>83</v>
       </c>
       <c r="AO124" t="s" s="2">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="AP124" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AQ124" t="s" s="2">
         <v>83</v>
@@ -18353,10 +18349,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -18379,13 +18375,13 @@
         <v>83</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="L125" t="s" s="2">
+        <v>848</v>
+      </c>
+      <c r="M125" t="s" s="2">
         <v>849</v>
-      </c>
-      <c r="M125" t="s" s="2">
-        <v>850</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
@@ -18436,7 +18432,7 @@
         <v>83</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>81</v>
@@ -18460,10 +18456,10 @@
         <v>83</v>
       </c>
       <c r="AN125" t="s" s="2">
+        <v>850</v>
+      </c>
+      <c r="AO125" t="s" s="2">
         <v>851</v>
-      </c>
-      <c r="AO125" t="s" s="2">
-        <v>852</v>
       </c>
       <c r="AP125" t="s" s="2">
         <v>83</v>
@@ -18474,10 +18470,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -18595,10 +18591,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -18718,14 +18714,14 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
@@ -18747,10 +18743,10 @@
         <v>137</v>
       </c>
       <c r="L128" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M128" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="M128" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="N128" t="s" s="2">
         <v>180</v>
@@ -18805,7 +18801,7 @@
         <v>83</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>81</v>
@@ -18843,10 +18839,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18869,16 +18865,16 @@
         <v>83</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="L129" t="s" s="2">
+        <v>856</v>
+      </c>
+      <c r="M129" t="s" s="2">
         <v>857</v>
       </c>
-      <c r="M129" t="s" s="2">
+      <c r="N129" t="s" s="2">
         <v>858</v>
-      </c>
-      <c r="N129" t="s" s="2">
-        <v>859</v>
       </c>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
@@ -18907,11 +18903,11 @@
         <v>317</v>
       </c>
       <c r="Y129" t="s" s="2">
+        <v>859</v>
+      </c>
+      <c r="Z129" t="s" s="2">
         <v>860</v>
       </c>
-      <c r="Z129" t="s" s="2">
-        <v>861</v>
-      </c>
       <c r="AA129" t="s" s="2">
         <v>83</v>
       </c>
@@ -18928,7 +18924,7 @@
         <v>83</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>92</v>
@@ -18952,24 +18948,24 @@
         <v>83</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="AO129" t="s" s="2">
+        <v>861</v>
+      </c>
+      <c r="AP129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ129" t="s" s="2">
         <v>862</v>
-      </c>
-      <c r="AP129" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ129" t="s" s="2">
-        <v>863</v>
       </c>
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18995,10 +18991,10 @@
         <v>256</v>
       </c>
       <c r="L130" t="s" s="2">
+        <v>864</v>
+      </c>
+      <c r="M130" t="s" s="2">
         <v>865</v>
-      </c>
-      <c r="M130" t="s" s="2">
-        <v>866</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -19028,11 +19024,11 @@
         <v>317</v>
       </c>
       <c r="Y130" t="s" s="2">
+        <v>866</v>
+      </c>
+      <c r="Z130" t="s" s="2">
         <v>867</v>
       </c>
-      <c r="Z130" t="s" s="2">
-        <v>868</v>
-      </c>
       <c r="AA130" t="s" s="2">
         <v>83</v>
       </c>
@@ -19049,7 +19045,7 @@
         <v>83</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>81</v>
@@ -19073,24 +19069,24 @@
         <v>83</v>
       </c>
       <c r="AN130" t="s" s="2">
+        <v>868</v>
+      </c>
+      <c r="AO130" t="s" s="2">
         <v>869</v>
       </c>
-      <c r="AO130" t="s" s="2">
+      <c r="AP130" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ130" t="s" s="2">
         <v>870</v>
-      </c>
-      <c r="AP130" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ130" t="s" s="2">
-        <v>871</v>
       </c>
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -19113,13 +19109,13 @@
         <v>83</v>
       </c>
       <c r="K131" t="s" s="2">
+        <v>872</v>
+      </c>
+      <c r="L131" t="s" s="2">
         <v>873</v>
       </c>
-      <c r="L131" t="s" s="2">
+      <c r="M131" t="s" s="2">
         <v>874</v>
-      </c>
-      <c r="M131" t="s" s="2">
-        <v>875</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
@@ -19170,7 +19166,7 @@
         <v>83</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>81</v>
@@ -19191,13 +19187,13 @@
         <v>83</v>
       </c>
       <c r="AM131" t="s" s="2">
+        <v>875</v>
+      </c>
+      <c r="AN131" t="s" s="2">
+        <v>868</v>
+      </c>
+      <c r="AO131" t="s" s="2">
         <v>876</v>
-      </c>
-      <c r="AN131" t="s" s="2">
-        <v>869</v>
-      </c>
-      <c r="AO131" t="s" s="2">
-        <v>877</v>
       </c>
       <c r="AP131" t="s" s="2">
         <v>83</v>
@@ -19208,14 +19204,14 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
@@ -19234,16 +19230,16 @@
         <v>83</v>
       </c>
       <c r="K132" t="s" s="2">
+        <v>879</v>
+      </c>
+      <c r="L132" t="s" s="2">
         <v>880</v>
       </c>
-      <c r="L132" t="s" s="2">
+      <c r="M132" t="s" s="2">
         <v>881</v>
       </c>
-      <c r="M132" t="s" s="2">
+      <c r="N132" t="s" s="2">
         <v>882</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>883</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -19293,7 +19289,7 @@
         <v>83</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>81</v>
@@ -19320,7 +19316,7 @@
         <v>83</v>
       </c>
       <c r="AO132" t="s" s="2">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="AP132" t="s" s="2">
         <v>83</v>
@@ -19331,10 +19327,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -19357,16 +19353,16 @@
         <v>83</v>
       </c>
       <c r="K133" t="s" s="2">
+        <v>885</v>
+      </c>
+      <c r="L133" t="s" s="2">
         <v>886</v>
       </c>
-      <c r="L133" t="s" s="2">
+      <c r="M133" t="s" s="2">
         <v>887</v>
       </c>
-      <c r="M133" t="s" s="2">
+      <c r="N133" t="s" s="2">
         <v>888</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>889</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
@@ -19416,7 +19412,7 @@
         <v>83</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>81</v>
@@ -19437,13 +19433,13 @@
         <v>83</v>
       </c>
       <c r="AM133" t="s" s="2">
+        <v>889</v>
+      </c>
+      <c r="AN133" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO133" t="s" s="2">
         <v>890</v>
-      </c>
-      <c r="AN133" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO133" t="s" s="2">
-        <v>891</v>
       </c>
       <c r="AP133" t="s" s="2">
         <v>83</v>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5201" uniqueCount="891">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5201" uniqueCount="892">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -960,6 +960,9 @@
   </si>
   <si>
     <t>This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
+  </si>
+  <si>
+    <t>draft</t>
   </si>
   <si>
     <t>A code specifying the state of the prescribing event. Describes the lifecycle of the prescription.</t>
@@ -6998,7 +7001,7 @@
         <v>83</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>11</v>
+        <v>306</v>
       </c>
       <c r="T32" t="s" s="2">
         <v>83</v>
@@ -7016,10 +7019,10 @@
         <v>250</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>83</v>
@@ -7052,22 +7055,22 @@
         <v>104</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>83</v>
@@ -7075,10 +7078,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -7104,13 +7107,13 @@
         <v>256</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -7136,13 +7139,13 @@
         <v>83</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>83</v>
@@ -7160,7 +7163,7 @@
         <v>83</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -7181,13 +7184,13 @@
         <v>83</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>83</v>
@@ -7198,10 +7201,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -7227,13 +7230,13 @@
         <v>112</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -7262,10 +7265,10 @@
         <v>250</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>83</v>
@@ -7283,7 +7286,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>92</v>
@@ -7304,16 +7307,16 @@
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>83</v>
@@ -7321,10 +7324,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -7350,13 +7353,13 @@
         <v>256</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -7382,19 +7385,19 @@
         <v>83</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AC35" s="2"/>
       <c r="AD35" t="s" s="2">
@@ -7404,7 +7407,7 @@
         <v>141</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -7428,13 +7431,13 @@
         <v>83</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>83</v>
@@ -7442,13 +7445,13 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>83</v>
@@ -7473,13 +7476,13 @@
         <v>256</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -7508,10 +7511,10 @@
         <v>250</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>83</v>
@@ -7529,7 +7532,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -7553,13 +7556,13 @@
         <v>83</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>83</v>
@@ -7567,10 +7570,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7596,10 +7599,10 @@
         <v>112</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -7629,10 +7632,10 @@
         <v>250</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>83</v>
@@ -7650,7 +7653,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -7671,16 +7674,16 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>83</v>
@@ -7688,10 +7691,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7717,13 +7720,13 @@
         <v>220</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -7773,7 +7776,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -7800,7 +7803,7 @@
         <v>83</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>83</v>
@@ -7811,10 +7814,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7837,13 +7840,13 @@
         <v>93</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -7894,7 +7897,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -7921,7 +7924,7 @@
         <v>83</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>83</v>
@@ -7932,10 +7935,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7958,16 +7961,16 @@
         <v>93</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7997,13 +8000,13 @@
       </c>
       <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AC40" s="2"/>
       <c r="AD40" t="s" s="2">
@@ -8013,7 +8016,7 @@
         <v>141</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>92</v>
@@ -8034,30 +8037,30 @@
         <v>83</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D41" t="s" s="2">
         <v>83</v>
@@ -8082,13 +8085,13 @@
         <v>256</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -8118,7 +8121,7 @@
       </c>
       <c r="Y41" s="2"/>
       <c r="Z41" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>83</v>
@@ -8136,7 +8139,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>92</v>
@@ -8151,33 +8154,33 @@
         <v>104</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -8200,16 +8203,16 @@
         <v>93</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -8259,7 +8262,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>92</v>
@@ -8280,27 +8283,27 @@
         <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8323,16 +8326,16 @@
         <v>83</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -8382,7 +8385,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -8403,27 +8406,27 @@
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8446,13 +8449,13 @@
         <v>83</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -8503,7 +8506,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -8524,16 +8527,16 @@
         <v>83</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>83</v>
@@ -8541,10 +8544,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8567,13 +8570,13 @@
         <v>93</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -8624,7 +8627,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -8639,33 +8642,33 @@
         <v>104</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8688,13 +8691,13 @@
         <v>93</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -8745,7 +8748,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -8760,22 +8763,22 @@
         <v>104</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>83</v>
@@ -8783,10 +8786,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8809,13 +8812,13 @@
         <v>83</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -8866,7 +8869,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -8887,16 +8890,16 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>83</v>
@@ -8904,10 +8907,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8933,13 +8936,13 @@
         <v>256</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8965,13 +8968,13 @@
         <v>83</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>83</v>
@@ -8989,7 +8992,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -9010,13 +9013,13 @@
         <v>83</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>83</v>
@@ -9027,10 +9030,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -9053,13 +9056,13 @@
         <v>83</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -9110,7 +9113,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -9125,10 +9128,10 @@
         <v>104</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>83</v>
@@ -9137,10 +9140,10 @@
         <v>83</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>83</v>
@@ -9148,10 +9151,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -9177,13 +9180,13 @@
         <v>256</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -9209,13 +9212,13 @@
         <v>83</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>83</v>
@@ -9233,7 +9236,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -9254,27 +9257,27 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -9297,16 +9300,16 @@
         <v>83</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -9356,7 +9359,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -9377,16 +9380,16 @@
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>83</v>
@@ -9394,10 +9397,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9420,13 +9423,13 @@
         <v>93</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -9477,7 +9480,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -9498,13 +9501,13 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>83</v>
@@ -9515,10 +9518,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9544,10 +9547,10 @@
         <v>106</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -9598,7 +9601,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -9625,7 +9628,7 @@
         <v>83</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>83</v>
@@ -9636,10 +9639,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9662,13 +9665,13 @@
         <v>93</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -9719,7 +9722,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -9740,13 +9743,13 @@
         <v>83</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>83</v>
@@ -9757,10 +9760,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9786,14 +9789,14 @@
         <v>234</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -9842,7 +9845,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -9863,13 +9866,13 @@
         <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>83</v>
@@ -9880,10 +9883,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9909,13 +9912,13 @@
         <v>256</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9941,13 +9944,13 @@
         <v>83</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>83</v>
@@ -9965,7 +9968,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -9992,7 +9995,7 @@
         <v>83</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>83</v>
@@ -10003,10 +10006,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -10029,13 +10032,13 @@
         <v>83</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -10086,7 +10089,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -10107,13 +10110,13 @@
         <v>83</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>83</v>
@@ -10124,10 +10127,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -10150,13 +10153,13 @@
         <v>83</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -10207,7 +10210,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -10222,19 +10225,19 @@
         <v>104</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>83</v>
@@ -10245,10 +10248,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10271,16 +10274,16 @@
         <v>83</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -10330,7 +10333,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -10351,13 +10354,13 @@
         <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>83</v>
@@ -10368,10 +10371,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10489,10 +10492,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10612,14 +10615,14 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -10641,10 +10644,10 @@
         <v>137</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N62" t="s" s="2">
         <v>180</v>
@@ -10699,7 +10702,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -10737,10 +10740,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10763,17 +10766,17 @@
         <v>93</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -10822,7 +10825,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -10849,21 +10852,21 @@
         <v>83</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10889,14 +10892,14 @@
         <v>151</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -10945,7 +10948,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -10972,21 +10975,21 @@
         <v>83</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -11012,16 +11015,16 @@
         <v>256</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>83</v>
@@ -11046,13 +11049,13 @@
         <v>83</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>83</v>
@@ -11070,7 +11073,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -11097,21 +11100,21 @@
         <v>83</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ65" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -11137,10 +11140,10 @@
         <v>151</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -11191,7 +11194,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -11206,7 +11209,7 @@
         <v>104</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>83</v>
@@ -11218,21 +11221,21 @@
         <v>83</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ66" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11255,19 +11258,19 @@
         <v>93</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -11316,7 +11319,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -11343,7 +11346,7 @@
         <v>83</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>83</v>
@@ -11354,10 +11357,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11475,10 +11478,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11598,14 +11601,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -11627,10 +11630,10 @@
         <v>137</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>180</v>
@@ -11685,7 +11688,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -11723,10 +11726,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11749,17 +11752,17 @@
         <v>93</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -11808,7 +11811,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -11835,7 +11838,7 @@
         <v>83</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>83</v>
@@ -11846,10 +11849,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11872,17 +11875,17 @@
         <v>93</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>83</v>
@@ -11931,7 +11934,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -11943,7 +11946,7 @@
         <v>83</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>83</v>
@@ -11958,7 +11961,7 @@
         <v>83</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>83</v>
@@ -11969,10 +11972,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -12090,10 +12093,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12213,10 +12216,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12239,13 +12242,13 @@
         <v>93</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -12284,7 +12287,7 @@
         <v>83</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AC75" s="2"/>
       <c r="AD75" t="s" s="2">
@@ -12294,7 +12297,7 @@
         <v>141</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -12321,7 +12324,7 @@
         <v>83</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>83</v>
@@ -12332,13 +12335,13 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D76" t="s" s="2">
         <v>83</v>
@@ -12363,10 +12366,10 @@
         <v>288</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -12417,7 +12420,7 @@
         <v>83</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -12444,7 +12447,7 @@
         <v>83</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>83</v>
@@ -12455,10 +12458,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12576,10 +12579,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12699,10 +12702,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12725,16 +12728,16 @@
         <v>93</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -12784,7 +12787,7 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -12793,16 +12796,16 @@
         <v>92</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>83</v>
@@ -12811,21 +12814,21 @@
         <v>83</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AP79" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ79" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12848,23 +12851,23 @@
         <v>93</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q80" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="R80" t="s" s="2">
         <v>83</v>
@@ -12909,7 +12912,7 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -12918,7 +12921,7 @@
         <v>92</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>104</v>
@@ -12936,21 +12939,21 @@
         <v>83</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AP80" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ80" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12973,19 +12976,19 @@
         <v>93</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>83</v>
@@ -13034,7 +13037,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -13061,7 +13064,7 @@
         <v>83</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AP81" t="s" s="2">
         <v>83</v>
@@ -13072,10 +13075,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13098,13 +13101,13 @@
         <v>93</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -13155,7 +13158,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -13182,7 +13185,7 @@
         <v>83</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>83</v>
@@ -13193,10 +13196,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13219,19 +13222,19 @@
         <v>93</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>83</v>
@@ -13280,7 +13283,7 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -13307,7 +13310,7 @@
         <v>83</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>83</v>
@@ -13318,10 +13321,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13344,19 +13347,19 @@
         <v>93</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>83</v>
@@ -13405,7 +13408,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -13432,7 +13435,7 @@
         <v>83</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>83</v>
@@ -13443,10 +13446,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13472,10 +13475,10 @@
         <v>112</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -13505,10 +13508,10 @@
         <v>250</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>83</v>
@@ -13526,7 +13529,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -13553,7 +13556,7 @@
         <v>83</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>83</v>
@@ -13564,10 +13567,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13590,13 +13593,13 @@
         <v>93</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -13604,7 +13607,7 @@
         <v>83</v>
       </c>
       <c r="Q86" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="R86" t="s" s="2">
         <v>83</v>
@@ -13649,7 +13652,7 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -13676,7 +13679,7 @@
         <v>83</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>83</v>
@@ -13687,10 +13690,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13713,13 +13716,13 @@
         <v>93</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -13770,7 +13773,7 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -13797,7 +13800,7 @@
         <v>83</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>83</v>
@@ -13808,10 +13811,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13834,13 +13837,13 @@
         <v>93</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -13891,7 +13894,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -13918,7 +13921,7 @@
         <v>83</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>83</v>
@@ -13929,10 +13932,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13955,13 +13958,13 @@
         <v>93</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -14012,7 +14015,7 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -14039,7 +14042,7 @@
         <v>83</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AP89" t="s" s="2">
         <v>83</v>
@@ -14050,10 +14053,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14079,10 +14082,10 @@
         <v>112</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -14112,10 +14115,10 @@
         <v>250</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>83</v>
@@ -14133,7 +14136,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -14160,7 +14163,7 @@
         <v>83</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>83</v>
@@ -14171,10 +14174,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14200,13 +14203,13 @@
         <v>112</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -14236,7 +14239,7 @@
       </c>
       <c r="Y91" s="2"/>
       <c r="Z91" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>83</v>
@@ -14254,7 +14257,7 @@
         <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -14292,10 +14295,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14318,16 +14321,16 @@
         <v>93</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -14377,7 +14380,7 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -14415,10 +14418,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14444,16 +14447,16 @@
         <v>112</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>83</v>
@@ -14481,10 +14484,10 @@
         <v>250</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>83</v>
@@ -14502,7 +14505,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -14529,7 +14532,7 @@
         <v>83</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>83</v>
@@ -14540,10 +14543,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14566,13 +14569,13 @@
         <v>93</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -14623,7 +14626,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -14650,7 +14653,7 @@
         <v>83</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>83</v>
@@ -14661,10 +14664,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14690,13 +14693,13 @@
         <v>256</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -14725,10 +14728,10 @@
         <v>116</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>83</v>
@@ -14746,7 +14749,7 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -14773,7 +14776,7 @@
         <v>83</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>83</v>
@@ -14784,10 +14787,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14810,16 +14813,16 @@
         <v>93</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -14845,13 +14848,13 @@
         <v>83</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>83</v>
@@ -14869,7 +14872,7 @@
         <v>83</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -14896,21 +14899,21 @@
         <v>83</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ96" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14936,16 +14939,16 @@
         <v>256</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>83</v>
@@ -14970,13 +14973,13 @@
         <v>83</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>83</v>
@@ -14994,7 +14997,7 @@
         <v>83</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -15021,21 +15024,21 @@
         <v>83</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="AP97" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ97" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -15061,14 +15064,14 @@
         <v>256</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>83</v>
@@ -15093,13 +15096,13 @@
         <v>83</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>83</v>
@@ -15117,7 +15120,7 @@
         <v>83</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -15144,21 +15147,21 @@
         <v>83</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="AP98" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ98" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15184,16 +15187,16 @@
         <v>256</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>83</v>
@@ -15218,13 +15221,13 @@
         <v>83</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>83</v>
@@ -15242,7 +15245,7 @@
         <v>83</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -15269,21 +15272,21 @@
         <v>83</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="AP99" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ99" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15306,13 +15309,13 @@
         <v>93</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -15363,7 +15366,7 @@
         <v>83</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
@@ -15396,15 +15399,15 @@
         <v>83</v>
       </c>
       <c r="AQ100" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15522,10 +15525,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15645,10 +15648,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15674,14 +15677,14 @@
         <v>256</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>83</v>
@@ -15706,13 +15709,13 @@
         <v>83</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>83</v>
@@ -15730,7 +15733,7 @@
         <v>83</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>81</v>
@@ -15763,15 +15766,15 @@
         <v>83</v>
       </c>
       <c r="AQ103" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15794,19 +15797,19 @@
         <v>93</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>83</v>
@@ -15855,7 +15858,7 @@
         <v>83</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>81</v>
@@ -15882,21 +15885,21 @@
         <v>83</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="AP104" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ104" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15919,19 +15922,19 @@
         <v>93</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>83</v>
@@ -15980,7 +15983,7 @@
         <v>83</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
@@ -16007,21 +16010,21 @@
         <v>83</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="AP105" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ105" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -16044,19 +16047,19 @@
         <v>93</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>83</v>
@@ -16105,7 +16108,7 @@
         <v>83</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
@@ -16132,21 +16135,21 @@
         <v>83</v>
       </c>
       <c r="AO106" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="AP106" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ106" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -16169,19 +16172,19 @@
         <v>93</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>83</v>
@@ -16230,7 +16233,7 @@
         <v>83</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -16257,7 +16260,7 @@
         <v>83</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="AP107" t="s" s="2">
         <v>83</v>
@@ -16268,10 +16271,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -16294,17 +16297,17 @@
         <v>93</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>83</v>
@@ -16353,7 +16356,7 @@
         <v>83</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -16380,7 +16383,7 @@
         <v>83</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="AP108" t="s" s="2">
         <v>83</v>
@@ -16391,10 +16394,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16417,13 +16420,13 @@
         <v>83</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -16474,7 +16477,7 @@
         <v>83</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
@@ -16498,10 +16501,10 @@
         <v>83</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="AP109" t="s" s="2">
         <v>83</v>
@@ -16512,10 +16515,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -16633,10 +16636,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16756,14 +16759,14 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
@@ -16785,10 +16788,10 @@
         <v>137</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N112" t="s" s="2">
         <v>180</v>
@@ -16843,7 +16846,7 @@
         <v>83</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
@@ -16881,10 +16884,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16907,16 +16910,16 @@
         <v>83</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -16966,7 +16969,7 @@
         <v>83</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
@@ -16993,7 +16996,7 @@
         <v>83</v>
       </c>
       <c r="AO113" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="AP113" t="s" s="2">
         <v>83</v>
@@ -17004,10 +17007,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -17125,10 +17128,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -17248,14 +17251,14 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
@@ -17277,10 +17280,10 @@
         <v>137</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N116" t="s" s="2">
         <v>180</v>
@@ -17335,7 +17338,7 @@
         <v>83</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>81</v>
@@ -17373,10 +17376,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -17399,13 +17402,13 @@
         <v>83</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -17456,7 +17459,7 @@
         <v>83</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>81</v>
@@ -17483,7 +17486,7 @@
         <v>83</v>
       </c>
       <c r="AO117" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="AP117" t="s" s="2">
         <v>83</v>
@@ -17494,10 +17497,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -17520,13 +17523,13 @@
         <v>83</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -17577,7 +17580,7 @@
         <v>83</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>81</v>
@@ -17604,7 +17607,7 @@
         <v>83</v>
       </c>
       <c r="AO118" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="AP118" t="s" s="2">
         <v>83</v>
@@ -17615,10 +17618,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -17641,13 +17644,13 @@
         <v>83</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -17698,7 +17701,7 @@
         <v>83</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>81</v>
@@ -17725,7 +17728,7 @@
         <v>83</v>
       </c>
       <c r="AO119" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="AP119" t="s" s="2">
         <v>83</v>
@@ -17736,10 +17739,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17765,16 +17768,16 @@
         <v>288</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="O120" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>83</v>
@@ -17823,7 +17826,7 @@
         <v>83</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>81</v>
@@ -17847,10 +17850,10 @@
         <v>83</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="AO120" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="AP120" t="s" s="2">
         <v>83</v>
@@ -17861,10 +17864,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17887,16 +17890,16 @@
         <v>83</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -17946,7 +17949,7 @@
         <v>83</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>81</v>
@@ -17961,33 +17964,33 @@
         <v>104</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="AO121" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="AP121" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ121" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -18010,13 +18013,13 @@
         <v>83</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -18067,7 +18070,7 @@
         <v>83</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>81</v>
@@ -18082,33 +18085,33 @@
         <v>104</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="AO122" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="AP122" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ122" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -18131,16 +18134,16 @@
         <v>83</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
@@ -18190,7 +18193,7 @@
         <v>83</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>81</v>
@@ -18205,19 +18208,19 @@
         <v>104</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="AM123" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="AO123" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="AP123" t="s" s="2">
         <v>83</v>
@@ -18228,10 +18231,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -18257,10 +18260,10 @@
         <v>295</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -18311,7 +18314,7 @@
         <v>83</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>81</v>
@@ -18338,10 +18341,10 @@
         <v>83</v>
       </c>
       <c r="AO124" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="AP124" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AQ124" t="s" s="2">
         <v>83</v>
@@ -18349,10 +18352,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -18375,13 +18378,13 @@
         <v>83</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
@@ -18432,7 +18435,7 @@
         <v>83</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>81</v>
@@ -18456,10 +18459,10 @@
         <v>83</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="AO125" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="AP125" t="s" s="2">
         <v>83</v>
@@ -18470,10 +18473,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -18591,10 +18594,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -18714,14 +18717,14 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
@@ -18743,10 +18746,10 @@
         <v>137</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N128" t="s" s="2">
         <v>180</v>
@@ -18801,7 +18804,7 @@
         <v>83</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>81</v>
@@ -18839,10 +18842,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18865,16 +18868,16 @@
         <v>83</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
@@ -18900,13 +18903,13 @@
         <v>83</v>
       </c>
       <c r="X129" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Y129" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="Z129" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>83</v>
@@ -18924,7 +18927,7 @@
         <v>83</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>92</v>
@@ -18948,24 +18951,24 @@
         <v>83</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="AO129" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="AP129" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ129" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18991,10 +18994,10 @@
         <v>256</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -19021,13 +19024,13 @@
         <v>83</v>
       </c>
       <c r="X130" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Y130" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="Z130" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>83</v>
@@ -19045,7 +19048,7 @@
         <v>83</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>81</v>
@@ -19069,24 +19072,24 @@
         <v>83</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="AO130" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="AP130" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ130" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -19109,13 +19112,13 @@
         <v>83</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
@@ -19166,7 +19169,7 @@
         <v>83</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>81</v>
@@ -19187,13 +19190,13 @@
         <v>83</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="AO131" t="s" s="2">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="AP131" t="s" s="2">
         <v>83</v>
@@ -19204,14 +19207,14 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
@@ -19230,16 +19233,16 @@
         <v>83</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -19289,7 +19292,7 @@
         <v>83</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>81</v>
@@ -19316,7 +19319,7 @@
         <v>83</v>
       </c>
       <c r="AO132" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="AP132" t="s" s="2">
         <v>83</v>
@@ -19327,10 +19330,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -19353,16 +19356,16 @@
         <v>83</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
@@ -19412,7 +19415,7 @@
         <v>83</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>81</v>
@@ -19433,13 +19436,13 @@
         <v>83</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="AN133" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO133" t="s" s="2">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="AP133" t="s" s="2">
         <v>83</v>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.425</t>
+    <t>0.69.436</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T15:07:22+00:00</t>
+    <t>2024-12-04T11:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file PENDING OUTPATIENT ORDERS (52.41) to us-core-medicationrequest</t>
+    <t>This StructureDefinition contains the maps for VistA file PENDING OUTPATIENT ORDERS (52.41) to us-core-medicationrequest.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$133</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$136</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5201" uniqueCount="892">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5318" uniqueCount="909">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -960,9 +960,6 @@
   </si>
   <si>
     <t>This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
-  </si>
-  <si>
-    <t>draft</t>
   </si>
   <si>
     <t>A code specifying the state of the prescribing event. Describes the lifecycle of the prescription.</t>
@@ -1035,6 +1032,9 @@
     <t>http://hl7.org/fhir/ValueSet/medicationrequest-intent</t>
   </si>
   <si>
+    <t>2197: target not supported</t>
+  </si>
+  <si>
     <t>Request.intent</t>
   </si>
   <si>
@@ -1064,6 +1064,9 @@
   <si>
     <t xml:space="preserve">pattern:$this}
 </t>
+  </si>
+  <si>
+    <t>2198: target not supported</t>
   </si>
   <si>
     <t>Message/Body/NewRx/MedicationPrescribed/Directions@@ -1085,6 +1088,9 @@
     <t>The type of medication order.</t>
   </si>
   <si>
+    <t>2199: target not supported</t>
+  </si>
+  <si>
     <t>MedicationRequest.priority</t>
   </si>
   <si>
@@ -1137,7 +1143,36 @@
     <t>Indicates if this record was captured as a secondary 'reported' record rather than as an original primary source-of-truth record.  It may also indicate the source of the report.</t>
   </si>
   <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
+    <t>closed</t>
+  </si>
+  <si>
     <t>.participation[typeCode=INF].role</t>
+  </si>
+  <si>
+    <t>MedicationRequest.reported[x]:reportedBoolean</t>
+  </si>
+  <si>
+    <t>reportedBoolean</t>
+  </si>
+  <si>
+    <t>2200: target not supported</t>
+  </si>
+  <si>
+    <t>MedicationRequest.reported[x]:reportedReference</t>
+  </si>
+  <si>
+    <t>reportedReference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitioner|http://hl7.org/fhir/us/core/StructureDefinition/us-core-organization|http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient|http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitionerrole|http://hl7.org/fhir/us/core/StructureDefinition/us-core-relatedperson)
+</t>
+  </si>
+  <si>
+    <t>2201: target not supported</t>
   </si>
   <si>
     <t>MedicationRequest.medication[x]</t>
@@ -1157,10 +1192,6 @@
   </si>
   <si>
     <t>http://cts.nlm.nih.gov/fhir/ValueSet/2.16.840.1.113762.1.4.1010.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type:$this}
-</t>
   </si>
   <si>
     <t>Request.code</t>
@@ -1196,6 +1227,19 @@
     <t>RxOut.PendingRxOrder.LocalDrugIEN,RxOut.PendingRxOrder.LocalDrugSID</t>
   </si>
   <si>
+    <t>MedicationRequest.medication[x]:medicationReference</t>
+  </si>
+  <si>
+    <t>medicationReference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-medication)
+</t>
+  </si>
+  <si>
+    <t>2202: target not supported</t>
+  </si>
+  <si>
     <t>MedicationRequest.subject</t>
   </si>
   <si>
@@ -1210,6 +1254,9 @@
   </si>
   <si>
     <t>The subject on a medication request is mandatory.  For the secondary use case where the actual subject is not provided, there still must be an anonymized subject specified.</t>
+  </si>
+  <si>
+    <t>2203: target not supported</t>
   </si>
   <si>
     <t>Request.subject</t>
@@ -1245,6 +1292,9 @@
     <t>This will typically be the encounter the event occurred within, but some activities may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter."    If there is a need to link to episodes of care they will be handled with an extension.</t>
   </si>
   <si>
+    <t>2204: target not supported</t>
+  </si>
+  <si>
     <t>Request.context</t>
   </si>
   <si>
@@ -1670,6 +1720,9 @@
   </si>
   <si>
     <t>Dosage.text</t>
+  </si>
+  <si>
+    <t>2205: target not supported</t>
   </si>
   <si>
     <t>RXO-6; RXE-21</t>
@@ -3091,7 +3144,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AQ133"/>
+  <dimension ref="A1:AQ136"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="87.59375" customWidth="true" bestFit="true"/>
@@ -7001,7 +7054,7 @@
         <v>83</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>306</v>
+        <v>11</v>
       </c>
       <c r="T32" t="s" s="2">
         <v>83</v>
@@ -7019,10 +7072,10 @@
         <v>250</v>
       </c>
       <c r="Y32" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="Z32" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="Z32" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>83</v>
@@ -7055,22 +7108,22 @@
         <v>104</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM32" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="AL32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM32" t="s" s="2">
+      <c r="AN32" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="AN32" t="s" s="2">
+      <c r="AO32" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="AO32" t="s" s="2">
+      <c r="AP32" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="AP32" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>83</v>
@@ -7078,10 +7131,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -7107,13 +7160,13 @@
         <v>256</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -7139,14 +7192,14 @@
         <v>83</v>
       </c>
       <c r="X33" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="Y33" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="Y33" t="s" s="2">
+      <c r="Z33" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="Z33" t="s" s="2">
-        <v>320</v>
-      </c>
       <c r="AA33" t="s" s="2">
         <v>83</v>
       </c>
@@ -7163,7 +7216,7 @@
         <v>83</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -7184,13 +7237,13 @@
         <v>83</v>
       </c>
       <c r="AM33" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AN33" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO33" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>83</v>
@@ -7201,10 +7254,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -7230,13 +7283,13 @@
         <v>112</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -7265,11 +7318,11 @@
         <v>250</v>
       </c>
       <c r="Y34" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="Z34" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="Z34" t="s" s="2">
-        <v>328</v>
-      </c>
       <c r="AA34" t="s" s="2">
         <v>83</v>
       </c>
@@ -7286,7 +7339,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>92</v>
@@ -7301,7 +7354,7 @@
         <v>104</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>83</v>
+        <v>328</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>83</v>
@@ -7385,7 +7438,7 @@
         <v>83</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="Y35" t="s" s="2">
         <v>336</v>
@@ -7422,7 +7475,7 @@
         <v>104</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>83</v>
+        <v>339</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>83</v>
@@ -7431,10 +7484,10 @@
         <v>83</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>331</v>
@@ -7445,13 +7498,13 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>332</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>83</v>
@@ -7511,7 +7564,7 @@
         <v>250</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Z36" t="s" s="2">
         <v>337</v>
@@ -7547,7 +7600,7 @@
         <v>104</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>83</v>
+        <v>345</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>83</v>
@@ -7556,10 +7609,10 @@
         <v>83</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>331</v>
@@ -7570,10 +7623,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7599,10 +7652,10 @@
         <v>112</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -7632,10 +7685,10 @@
         <v>250</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>83</v>
@@ -7653,7 +7706,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -7674,16 +7727,16 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>83</v>
@@ -7691,10 +7744,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7720,13 +7773,13 @@
         <v>220</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -7776,7 +7829,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -7803,7 +7856,7 @@
         <v>83</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>83</v>
@@ -7814,10 +7867,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7840,13 +7893,13 @@
         <v>93</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -7885,19 +7938,17 @@
         <v>83</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>363</v>
+      </c>
+      <c r="AC39" s="2"/>
       <c r="AD39" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>83</v>
+        <v>364</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -7924,7 +7975,7 @@
         <v>83</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>83</v>
@@ -7935,18 +7986,20 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="C40" s="2"/>
+        <v>359</v>
+      </c>
+      <c r="C40" t="s" s="2">
+        <v>367</v>
+      </c>
       <c r="D40" t="s" s="2">
         <v>83</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>92</v>
@@ -7961,17 +8014,15 @@
         <v>93</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>363</v>
+        <v>220</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>366</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>83</v>
@@ -7996,30 +8047,34 @@
         <v>83</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="Y40" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z40" t="s" s="2">
-        <v>367</v>
+        <v>83</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="AC40" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="AD40" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>141</v>
+        <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>92</v>
@@ -8031,36 +8086,36 @@
         <v>104</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>83</v>
+        <v>368</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>369</v>
+        <v>83</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>370</v>
+        <v>83</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>372</v>
+        <v>83</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>373</v>
+        <v>83</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="D41" t="s" s="2">
         <v>83</v>
@@ -8082,17 +8137,15 @@
         <v>93</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>256</v>
+        <v>371</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>366</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>83</v>
@@ -8117,11 +8170,13 @@
         <v>83</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="Y41" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z41" t="s" s="2">
-        <v>367</v>
+        <v>83</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>83</v>
@@ -8139,10 +8194,10 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>92</v>
@@ -8154,33 +8209,33 @@
         <v>104</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>377</v>
+        <v>83</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>369</v>
+        <v>83</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>370</v>
+        <v>83</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>372</v>
+        <v>83</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>373</v>
+        <v>83</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -8203,16 +8258,16 @@
         <v>93</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -8238,31 +8293,27 @@
         <v>83</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y42" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>83</v>
+        <v>378</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>363</v>
+      </c>
+      <c r="AC42" s="2"/>
       <c r="AD42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>83</v>
+        <v>364</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>92</v>
@@ -8283,29 +8334,31 @@
         <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AO42" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AP42" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AQ42" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="AP42" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="AQ42" t="s" s="2">
-        <v>387</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="C43" s="2"/>
+        <v>373</v>
+      </c>
+      <c r="C43" t="s" s="2">
+        <v>385</v>
+      </c>
       <c r="D43" t="s" s="2">
         <v>83</v>
       </c>
@@ -8323,19 +8376,19 @@
         <v>83</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>389</v>
+        <v>256</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>390</v>
+        <v>375</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>391</v>
+        <v>376</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>392</v>
+        <v>377</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -8361,13 +8414,11 @@
         <v>83</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y43" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="Y43" s="2"/>
       <c r="Z43" t="s" s="2">
-        <v>83</v>
+        <v>378</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>83</v>
@@ -8385,10 +8436,10 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>388</v>
+        <v>373</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>92</v>
@@ -8400,35 +8451,37 @@
         <v>104</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>83</v>
+        <v>386</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>83</v>
+        <v>387</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>393</v>
+        <v>379</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>311</v>
+        <v>380</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>394</v>
+        <v>381</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>395</v>
+        <v>382</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>396</v>
+        <v>383</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="C44" s="2"/>
+        <v>373</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>389</v>
+      </c>
       <c r="D44" t="s" s="2">
         <v>83</v>
       </c>
@@ -8437,27 +8490,29 @@
         <v>81</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>399</v>
+        <v>375</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>376</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>377</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>83</v>
@@ -8506,13 +8561,13 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>397</v>
+        <v>373</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>83</v>
@@ -8521,33 +8576,33 @@
         <v>104</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>83</v>
+        <v>391</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>401</v>
+        <v>379</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>83</v>
+        <v>380</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>402</v>
+        <v>381</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>395</v>
+        <v>382</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>83</v>
+        <v>383</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8555,7 +8610,7 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>92</v>
@@ -8570,15 +8625,17 @@
         <v>93</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>404</v>
+        <v>393</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>395</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>396</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>83</v>
@@ -8627,10 +8684,10 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>92</v>
@@ -8642,33 +8699,33 @@
         <v>104</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>408</v>
+        <v>83</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>409</v>
+        <v>398</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>411</v>
+        <v>400</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>413</v>
+        <v>402</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8676,7 +8733,7 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>92</v>
@@ -8688,18 +8745,20 @@
         <v>83</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>416</v>
+        <v>405</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>406</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>83</v>
@@ -8748,7 +8807,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -8763,33 +8822,33 @@
         <v>104</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>419</v>
+        <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>420</v>
+        <v>409</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>83</v>
+        <v>310</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>385</v>
+        <v>410</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>83</v>
+        <v>412</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8800,7 +8859,7 @@
         <v>81</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>83</v>
@@ -8812,13 +8871,13 @@
         <v>83</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -8869,13 +8928,13 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>83</v>
@@ -8890,16 +8949,16 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>428</v>
+        <v>411</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>83</v>
@@ -8907,10 +8966,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8924,7 +8983,7 @@
         <v>92</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>83</v>
@@ -8933,17 +8992,15 @@
         <v>93</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>256</v>
+        <v>420</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>432</v>
-      </c>
+        <v>422</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -8968,13 +9025,13 @@
         <v>83</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>318</v>
+        <v>83</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>433</v>
+        <v>83</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>434</v>
+        <v>83</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>83</v>
@@ -8992,7 +9049,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -9007,33 +9064,33 @@
         <v>104</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>83</v>
+        <v>423</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>83</v>
+        <v>424</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>83</v>
+        <v>426</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>436</v>
+        <v>427</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>83</v>
+        <v>428</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>83</v>
+        <v>429</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -9041,7 +9098,7 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>92</v>
@@ -9053,16 +9110,16 @@
         <v>83</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>415</v>
+        <v>431</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -9113,7 +9170,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -9128,22 +9185,22 @@
         <v>104</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>83</v>
+        <v>436</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>442</v>
+        <v>400</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>83</v>
@@ -9151,10 +9208,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -9165,7 +9222,7 @@
         <v>81</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>83</v>
@@ -9177,17 +9234,15 @@
         <v>83</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>256</v>
+        <v>439</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>447</v>
-      </c>
+        <v>441</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -9212,13 +9267,13 @@
         <v>83</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>318</v>
+        <v>83</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>448</v>
+        <v>83</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>449</v>
+        <v>83</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>83</v>
@@ -9236,13 +9291,13 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>83</v>
@@ -9257,27 +9312,27 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>451</v>
+        <v>83</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>454</v>
+        <v>83</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -9288,7 +9343,7 @@
         <v>81</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>83</v>
@@ -9297,19 +9352,19 @@
         <v>83</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>456</v>
+        <v>256</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>457</v>
+        <v>446</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>458</v>
+        <v>447</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>459</v>
+        <v>448</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -9335,13 +9390,13 @@
         <v>83</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>83</v>
+        <v>317</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>83</v>
+        <v>449</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>83</v>
+        <v>450</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>83</v>
@@ -9359,13 +9414,13 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>83</v>
@@ -9380,16 +9435,16 @@
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>311</v>
+        <v>83</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>453</v>
+        <v>83</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>83</v>
@@ -9397,10 +9452,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9411,25 +9466,25 @@
         <v>81</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>463</v>
+        <v>431</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>465</v>
+        <v>455</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -9480,13 +9535,13 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>83</v>
@@ -9495,22 +9550,22 @@
         <v>104</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>83</v>
+        <v>456</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>83</v>
+        <v>457</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>466</v>
+        <v>83</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>83</v>
+        <v>459</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>83</v>
@@ -9518,10 +9573,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9541,18 +9596,20 @@
         <v>83</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>106</v>
+        <v>256</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>462</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>463</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>83</v>
@@ -9577,13 +9634,13 @@
         <v>83</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>83</v>
+        <v>317</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>83</v>
+        <v>464</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>83</v>
+        <v>465</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>83</v>
@@ -9601,7 +9658,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -9622,19 +9679,19 @@
         <v>83</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>83</v>
+        <v>466</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>83</v>
+        <v>467</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>83</v>
+        <v>469</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>83</v>
+        <v>470</v>
       </c>
     </row>
     <row r="54" hidden="true">
@@ -9662,7 +9719,7 @@
         <v>83</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
         <v>472</v>
@@ -9673,7 +9730,9 @@
       <c r="M54" t="s" s="2">
         <v>474</v>
       </c>
-      <c r="N54" s="2"/>
+      <c r="N54" t="s" s="2">
+        <v>475</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>83</v>
@@ -9743,16 +9802,16 @@
         <v>83</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>83</v>
+        <v>310</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>83</v>
+        <v>469</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>83</v>
@@ -9760,10 +9819,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9774,7 +9833,7 @@
         <v>81</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>83</v>
@@ -9786,18 +9845,16 @@
         <v>93</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>234</v>
+        <v>479</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="N55" s="2"/>
-      <c r="O55" t="s" s="2">
-        <v>480</v>
-      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>83</v>
       </c>
@@ -9845,13 +9902,13 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>83</v>
@@ -9866,13 +9923,13 @@
         <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>83</v>
@@ -9883,10 +9940,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9897,7 +9954,7 @@
         <v>81</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>83</v>
@@ -9906,20 +9963,18 @@
         <v>83</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>256</v>
+        <v>106</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="N56" t="s" s="2">
         <v>486</v>
       </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>83</v>
@@ -9944,13 +9999,13 @@
         <v>83</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>318</v>
+        <v>83</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>487</v>
+        <v>83</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>488</v>
+        <v>83</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>83</v>
@@ -9968,13 +10023,13 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>83</v>
@@ -9995,7 +10050,7 @@
         <v>83</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>83</v>
@@ -10006,10 +10061,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -10029,16 +10084,16 @@
         <v>83</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -10089,7 +10144,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -10110,13 +10165,13 @@
         <v>83</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>83</v>
@@ -10127,10 +10182,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -10141,28 +10196,30 @@
         <v>81</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J58" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="I58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J58" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="K58" t="s" s="2">
-        <v>497</v>
+        <v>234</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
+      <c r="O58" t="s" s="2">
+        <v>496</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
       </c>
@@ -10210,13 +10267,13 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>83</v>
@@ -10225,19 +10282,19 @@
         <v>104</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>500</v>
+        <v>83</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>502</v>
+        <v>83</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>83</v>
@@ -10248,10 +10305,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10262,10 +10319,10 @@
         <v>81</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>83</v>
@@ -10274,16 +10331,16 @@
         <v>83</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>505</v>
+        <v>256</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -10309,13 +10366,13 @@
         <v>83</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>83</v>
+        <v>317</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>83</v>
+        <v>503</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>83</v>
+        <v>504</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>83</v>
@@ -10333,13 +10390,13 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>83</v>
@@ -10354,13 +10411,13 @@
         <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>509</v>
+        <v>83</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>83</v>
@@ -10371,10 +10428,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10385,7 +10442,7 @@
         <v>81</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>83</v>
@@ -10397,13 +10454,13 @@
         <v>83</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>151</v>
+        <v>507</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>152</v>
+        <v>508</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>153</v>
+        <v>509</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -10454,19 +10511,19 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>154</v>
+        <v>506</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>83</v>
@@ -10475,13 +10532,13 @@
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>83</v>
+        <v>510</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>155</v>
+        <v>511</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>83</v>
@@ -10499,7 +10556,7 @@
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>177</v>
+        <v>83</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -10509,7 +10566,7 @@
         <v>82</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>83</v>
@@ -10518,17 +10575,15 @@
         <v>83</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>137</v>
+        <v>513</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>178</v>
+        <v>514</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>180</v>
-      </c>
+        <v>515</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -10565,19 +10620,19 @@
         <v>83</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>140</v>
+        <v>83</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>141</v>
+        <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>159</v>
+        <v>512</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -10589,22 +10644,22 @@
         <v>83</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>83</v>
+        <v>516</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>83</v>
+        <v>517</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>83</v>
+        <v>518</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>155</v>
+        <v>519</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>83</v>
@@ -10615,14 +10670,14 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>514</v>
+        <v>83</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -10632,29 +10687,27 @@
         <v>82</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>137</v>
+        <v>521</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>231</v>
-      </c>
+        <v>524</v>
+      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>83</v>
       </c>
@@ -10702,7 +10755,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -10714,7 +10767,7 @@
         <v>83</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>83</v>
@@ -10723,13 +10776,13 @@
         <v>83</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>83</v>
+        <v>525</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>135</v>
+        <v>526</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>83</v>
@@ -10740,10 +10793,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>518</v>
+        <v>527</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>518</v>
+        <v>527</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10763,21 +10816,19 @@
         <v>83</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>519</v>
+        <v>151</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>520</v>
+        <v>152</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>521</v>
+        <v>153</v>
       </c>
       <c r="N63" s="2"/>
-      <c r="O63" t="s" s="2">
-        <v>522</v>
-      </c>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>83</v>
       </c>
@@ -10825,7 +10876,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>523</v>
+        <v>154</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -10837,7 +10888,7 @@
         <v>83</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>83</v>
@@ -10852,55 +10903,55 @@
         <v>83</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>524</v>
+        <v>155</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>525</v>
+        <v>83</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>83</v>
+        <v>177</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>527</v>
+        <v>178</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="N64" s="2"/>
-      <c r="O64" t="s" s="2">
-        <v>529</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>83</v>
       </c>
@@ -10936,31 +10987,31 @@
         <v>83</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>83</v>
+        <v>140</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>83</v>
+        <v>158</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>83</v>
+        <v>141</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>530</v>
+        <v>159</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>83</v>
@@ -10975,25 +11026,25 @@
         <v>83</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>524</v>
+        <v>155</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>531</v>
+        <v>83</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>83</v>
+        <v>530</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -11006,25 +11057,25 @@
         <v>83</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="J65" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>256</v>
+        <v>137</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>535</v>
+        <v>180</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>536</v>
+        <v>231</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>83</v>
@@ -11049,13 +11100,13 @@
         <v>83</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>318</v>
+        <v>83</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>537</v>
+        <v>83</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>538</v>
+        <v>83</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>83</v>
@@ -11073,7 +11124,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -11085,7 +11136,7 @@
         <v>83</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>83</v>
@@ -11100,21 +11151,21 @@
         <v>83</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>524</v>
+        <v>135</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ65" t="s" s="2">
-        <v>540</v>
+        <v>83</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -11128,7 +11179,7 @@
         <v>92</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>83</v>
@@ -11137,16 +11188,18 @@
         <v>93</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>151</v>
+        <v>535</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
+      <c r="O66" t="s" s="2">
+        <v>538</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>83</v>
       </c>
@@ -11194,7 +11247,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -11209,7 +11262,7 @@
         <v>104</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>545</v>
+        <v>83</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>83</v>
@@ -11221,21 +11274,21 @@
         <v>83</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>524</v>
+        <v>540</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ66" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11249,7 +11302,7 @@
         <v>92</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>83</v>
@@ -11258,19 +11311,17 @@
         <v>93</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>547</v>
+        <v>151</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>550</v>
-      </c>
+        <v>544</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -11319,7 +11370,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -11334,7 +11385,7 @@
         <v>104</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>83</v>
+        <v>547</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>83</v>
@@ -11346,21 +11397,21 @@
         <v>83</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>553</v>
+        <v>540</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ67" t="s" s="2">
-        <v>83</v>
+        <v>548</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11371,7 +11422,7 @@
         <v>81</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>83</v>
@@ -11380,19 +11431,23 @@
         <v>83</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>151</v>
+        <v>256</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>152</v>
+        <v>550</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
+        <v>551</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>553</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>83</v>
       </c>
@@ -11416,13 +11471,13 @@
         <v>83</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>83</v>
+        <v>317</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>83</v>
+        <v>554</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>83</v>
+        <v>555</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>83</v>
@@ -11440,19 +11495,19 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>154</v>
+        <v>556</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>83</v>
@@ -11467,54 +11522,52 @@
         <v>83</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>155</v>
+        <v>540</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ68" t="s" s="2">
-        <v>83</v>
+        <v>557</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>177</v>
+        <v>83</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>178</v>
+        <v>559</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>180</v>
-      </c>
+        <v>560</v>
+      </c>
+      <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>83</v>
@@ -11551,34 +11604,34 @@
         <v>83</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>140</v>
+        <v>83</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="AD69" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>141</v>
+        <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>159</v>
+        <v>561</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>83</v>
+        <v>562</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>83</v>
@@ -11590,56 +11643,56 @@
         <v>83</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>155</v>
+        <v>540</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>83</v>
+        <v>557</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>556</v>
+        <v>563</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>556</v>
+        <v>563</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>514</v>
+        <v>83</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="J70" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>137</v>
+        <v>564</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>515</v>
+        <v>565</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>516</v>
+        <v>566</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>180</v>
+        <v>567</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>231</v>
+        <v>568</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>83</v>
@@ -11688,19 +11741,19 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>517</v>
+        <v>569</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>83</v>
@@ -11715,7 +11768,7 @@
         <v>83</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>135</v>
+        <v>570</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>83</v>
@@ -11726,10 +11779,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>557</v>
+        <v>571</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>557</v>
+        <v>571</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11740,7 +11793,7 @@
         <v>81</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>83</v>
@@ -11749,21 +11802,19 @@
         <v>83</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>404</v>
+        <v>151</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>558</v>
+        <v>152</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>559</v>
+        <v>153</v>
       </c>
       <c r="N71" s="2"/>
-      <c r="O71" t="s" s="2">
-        <v>560</v>
-      </c>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>83</v>
       </c>
@@ -11811,19 +11862,19 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>561</v>
+        <v>154</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>83</v>
@@ -11838,7 +11889,7 @@
         <v>83</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>562</v>
+        <v>155</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>83</v>
@@ -11849,21 +11900,21 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>563</v>
+        <v>572</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>563</v>
+        <v>572</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>83</v>
+        <v>177</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>83</v>
@@ -11872,21 +11923,21 @@
         <v>83</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>564</v>
+        <v>137</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>565</v>
+        <v>178</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="N72" s="2"/>
-      <c r="O72" t="s" s="2">
-        <v>567</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>83</v>
       </c>
@@ -11922,31 +11973,31 @@
         <v>83</v>
       </c>
       <c r="AB72" t="s" s="2">
-        <v>83</v>
+        <v>140</v>
       </c>
       <c r="AC72" t="s" s="2">
-        <v>83</v>
+        <v>158</v>
       </c>
       <c r="AD72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>83</v>
+        <v>141</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>568</v>
+        <v>159</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>569</v>
+        <v>143</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>83</v>
@@ -11961,7 +12012,7 @@
         <v>83</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>570</v>
+        <v>155</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>83</v>
@@ -11972,42 +12023,46 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>83</v>
+        <v>530</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>152</v>
+        <v>531</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N73" s="2"/>
-      <c r="O73" s="2"/>
+        <v>532</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>83</v>
       </c>
@@ -12055,19 +12110,19 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>154</v>
+        <v>533</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>83</v>
@@ -12082,7 +12137,7 @@
         <v>83</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>83</v>
@@ -12093,14 +12148,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>177</v>
+        <v>83</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -12116,21 +12171,21 @@
         <v>83</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>137</v>
+        <v>420</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>178</v>
+        <v>575</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="O74" s="2"/>
+        <v>576</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" t="s" s="2">
+        <v>577</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>83</v>
       </c>
@@ -12166,19 +12221,19 @@
         <v>83</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>140</v>
+        <v>83</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>141</v>
+        <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>159</v>
+        <v>578</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -12190,7 +12245,7 @@
         <v>83</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>83</v>
@@ -12205,7 +12260,7 @@
         <v>83</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>155</v>
+        <v>579</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>83</v>
@@ -12216,10 +12271,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12242,16 +12297,18 @@
         <v>93</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>574</v>
+        <v>581</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>576</v>
+        <v>583</v>
       </c>
       <c r="N75" s="2"/>
-      <c r="O75" s="2"/>
+      <c r="O75" t="s" s="2">
+        <v>584</v>
+      </c>
       <c r="P75" t="s" s="2">
         <v>83</v>
       </c>
@@ -12287,17 +12344,19 @@
         <v>83</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="AC75" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="AD75" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>141</v>
+        <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -12309,7 +12368,7 @@
         <v>83</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>104</v>
+        <v>586</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>83</v>
@@ -12324,7 +12383,7 @@
         <v>83</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>578</v>
+        <v>587</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>83</v>
@@ -12335,14 +12394,12 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>579</v>
+        <v>588</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="C76" t="s" s="2">
-        <v>580</v>
-      </c>
+        <v>588</v>
+      </c>
+      <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
         <v>83</v>
       </c>
@@ -12360,16 +12417,16 @@
         <v>83</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>288</v>
+        <v>151</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>575</v>
+        <v>152</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>576</v>
+        <v>153</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -12420,7 +12477,7 @@
         <v>83</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>577</v>
+        <v>154</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -12432,7 +12489,7 @@
         <v>83</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>83</v>
@@ -12447,7 +12504,7 @@
         <v>83</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>578</v>
+        <v>155</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>83</v>
@@ -12458,21 +12515,21 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>83</v>
+        <v>177</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>83</v>
@@ -12484,15 +12541,17 @@
         <v>83</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>152</v>
+        <v>178</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N77" s="2"/>
+        <v>179</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>180</v>
+      </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>83</v>
@@ -12529,31 +12588,31 @@
         <v>83</v>
       </c>
       <c r="AB77" t="s" s="2">
-        <v>83</v>
+        <v>140</v>
       </c>
       <c r="AC77" t="s" s="2">
-        <v>83</v>
+        <v>158</v>
       </c>
       <c r="AD77" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>83</v>
+        <v>141</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>83</v>
@@ -12579,21 +12638,21 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>583</v>
+        <v>590</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>177</v>
+        <v>83</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>83</v>
@@ -12602,20 +12661,18 @@
         <v>83</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>137</v>
+        <v>591</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>178</v>
+        <v>592</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>180</v>
-      </c>
+        <v>593</v>
+      </c>
+      <c r="N78" s="2"/>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>83</v>
@@ -12652,11 +12709,9 @@
         <v>83</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>363</v>
+      </c>
+      <c r="AC78" s="2"/>
       <c r="AD78" t="s" s="2">
         <v>83</v>
       </c>
@@ -12664,19 +12719,19 @@
         <v>141</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>159</v>
+        <v>594</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>83</v>
@@ -12691,7 +12746,7 @@
         <v>83</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>155</v>
+        <v>595</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>83</v>
@@ -12702,12 +12757,14 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>585</v>
+        <v>596</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="C79" s="2"/>
+        <v>590</v>
+      </c>
+      <c r="C79" t="s" s="2">
+        <v>597</v>
+      </c>
       <c r="D79" t="s" s="2">
         <v>83</v>
       </c>
@@ -12719,7 +12776,7 @@
         <v>92</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>83</v>
@@ -12728,17 +12785,15 @@
         <v>93</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>404</v>
+        <v>288</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>589</v>
-      </c>
+        <v>593</v>
+      </c>
+      <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>83</v>
@@ -12787,7 +12842,7 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -12796,16 +12851,16 @@
         <v>92</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>591</v>
+        <v>83</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>592</v>
+        <v>83</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>593</v>
+        <v>83</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>83</v>
@@ -12814,21 +12869,21 @@
         <v>83</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AP79" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ79" t="s" s="2">
-        <v>595</v>
+        <v>83</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12848,27 +12903,23 @@
         <v>83</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>404</v>
+        <v>151</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>598</v>
+        <v>152</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>600</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="N80" s="2"/>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="Q80" t="s" s="2">
-        <v>601</v>
-      </c>
+      <c r="Q80" s="2"/>
       <c r="R80" t="s" s="2">
         <v>83</v>
       </c>
@@ -12912,7 +12963,7 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>602</v>
+        <v>154</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -12921,10 +12972,10 @@
         <v>92</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>591</v>
+        <v>83</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>83</v>
@@ -12939,32 +12990,32 @@
         <v>83</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>603</v>
+        <v>155</v>
       </c>
       <c r="AP80" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ80" t="s" s="2">
-        <v>604</v>
+        <v>83</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>83</v>
+        <v>177</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>83</v>
@@ -12973,23 +13024,21 @@
         <v>83</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>606</v>
+        <v>137</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>607</v>
+        <v>178</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>608</v>
+        <v>179</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>610</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>83</v>
       </c>
@@ -13025,31 +13074,31 @@
         <v>83</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>83</v>
+        <v>140</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>83</v>
+        <v>158</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>83</v>
+        <v>141</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>611</v>
+        <v>159</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>83</v>
@@ -13064,7 +13113,7 @@
         <v>83</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>612</v>
+        <v>155</v>
       </c>
       <c r="AP81" t="s" s="2">
         <v>83</v>
@@ -13075,10 +13124,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>613</v>
+        <v>602</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>613</v>
+        <v>603</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13092,7 +13141,7 @@
         <v>92</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>83</v>
@@ -13101,15 +13150,17 @@
         <v>93</v>
       </c>
       <c r="K82" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="N82" t="s" s="2">
         <v>606</v>
       </c>
-      <c r="L82" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="N82" s="2"/>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>83</v>
@@ -13158,7 +13209,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>616</v>
+        <v>607</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -13167,16 +13218,16 @@
         <v>92</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>83</v>
+        <v>608</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>83</v>
+        <v>609</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>83</v>
+        <v>610</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>83</v>
@@ -13185,21 +13236,21 @@
         <v>83</v>
       </c>
       <c r="AO82" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="AP82" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ82" t="s" s="2">
         <v>612</v>
-      </c>
-      <c r="AP82" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ82" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13222,69 +13273,69 @@
         <v>93</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="O83" s="2"/>
+      <c r="P83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q83" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="L83" t="s" s="2">
+      <c r="R83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF83" t="s" s="2">
         <v>619</v>
       </c>
-      <c r="M83" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="P83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q83" s="2"/>
-      <c r="R83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>623</v>
-      </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
       </c>
@@ -13292,7 +13343,7 @@
         <v>92</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>83</v>
+        <v>608</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>104</v>
@@ -13310,21 +13361,21 @@
         <v>83</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ83" t="s" s="2">
-        <v>83</v>
+        <v>621</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13347,19 +13398,19 @@
         <v>93</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="N84" t="s" s="2">
         <v>626</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="O84" t="s" s="2">
         <v>627</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>622</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>83</v>
@@ -13435,7 +13486,7 @@
         <v>83</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>83</v>
@@ -13446,10 +13497,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13472,13 +13523,13 @@
         <v>93</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>112</v>
+        <v>623</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -13505,31 +13556,31 @@
         <v>83</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>250</v>
+        <v>83</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>632</v>
+        <v>83</v>
       </c>
       <c r="Z85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF85" t="s" s="2">
         <v>633</v>
-      </c>
-      <c r="AA85" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB85" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD85" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE85" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>634</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -13556,7 +13607,7 @@
         <v>83</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>83</v>
@@ -13567,10 +13618,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13593,22 +13644,24 @@
         <v>93</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>606</v>
+        <v>635</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>637</v>
       </c>
-      <c r="M86" t="s" s="2">
+      <c r="N86" t="s" s="2">
         <v>638</v>
       </c>
-      <c r="N86" s="2"/>
-      <c r="O86" s="2"/>
+      <c r="O86" t="s" s="2">
+        <v>639</v>
+      </c>
       <c r="P86" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="Q86" t="s" s="2">
-        <v>639</v>
-      </c>
+      <c r="Q86" s="2"/>
       <c r="R86" t="s" s="2">
         <v>83</v>
       </c>
@@ -13679,7 +13732,7 @@
         <v>83</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>83</v>
@@ -13690,10 +13743,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13716,16 +13769,20 @@
         <v>93</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>606</v>
+        <v>635</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="N87" s="2"/>
-      <c r="O87" s="2"/>
+        <v>644</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>639</v>
+      </c>
       <c r="P87" t="s" s="2">
         <v>83</v>
       </c>
@@ -13773,7 +13830,7 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -13800,7 +13857,7 @@
         <v>83</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>83</v>
@@ -13811,10 +13868,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13837,13 +13894,13 @@
         <v>93</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>618</v>
+        <v>112</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>637</v>
+        <v>647</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -13870,13 +13927,13 @@
         <v>83</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>83</v>
+        <v>250</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>83</v>
+        <v>649</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>83</v>
+        <v>650</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>83</v>
@@ -13894,7 +13951,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -13921,7 +13978,7 @@
         <v>83</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>624</v>
+        <v>652</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>83</v>
@@ -13932,10 +13989,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13958,20 +14015,22 @@
         <v>93</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="Q89" s="2"/>
+      <c r="Q89" t="s" s="2">
+        <v>656</v>
+      </c>
       <c r="R89" t="s" s="2">
         <v>83</v>
       </c>
@@ -14015,7 +14074,7 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -14042,7 +14101,7 @@
         <v>83</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="AP89" t="s" s="2">
         <v>83</v>
@@ -14053,10 +14112,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14079,13 +14138,13 @@
         <v>93</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>112</v>
+        <v>623</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>630</v>
+        <v>659</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>653</v>
+        <v>660</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -14112,13 +14171,13 @@
         <v>83</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>250</v>
+        <v>83</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>632</v>
+        <v>83</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>633</v>
+        <v>83</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>83</v>
@@ -14136,7 +14195,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>654</v>
+        <v>661</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -14163,7 +14222,7 @@
         <v>83</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>83</v>
@@ -14174,10 +14233,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>655</v>
+        <v>662</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>655</v>
+        <v>662</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14188,7 +14247,7 @@
         <v>81</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>83</v>
@@ -14200,17 +14259,15 @@
         <v>93</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>112</v>
+        <v>635</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>658</v>
-      </c>
+        <v>663</v>
+      </c>
+      <c r="N91" s="2"/>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>83</v>
@@ -14235,11 +14292,13 @@
         <v>83</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="Y91" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z91" t="s" s="2">
-        <v>659</v>
+        <v>83</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>83</v>
@@ -14257,13 +14316,13 @@
         <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>83</v>
@@ -14284,7 +14343,7 @@
         <v>83</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>155</v>
+        <v>641</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>83</v>
@@ -14295,10 +14354,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14309,7 +14368,7 @@
         <v>81</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>83</v>
@@ -14321,17 +14380,15 @@
         <v>93</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>662</v>
+        <v>635</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>665</v>
-      </c>
+        <v>667</v>
+      </c>
+      <c r="N92" s="2"/>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>83</v>
@@ -14380,13 +14437,13 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>83</v>
@@ -14407,7 +14464,7 @@
         <v>83</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>155</v>
+        <v>641</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>83</v>
@@ -14418,10 +14475,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14432,7 +14489,7 @@
         <v>81</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>83</v>
@@ -14447,17 +14504,13 @@
         <v>112</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>668</v>
+        <v>647</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="N93" t="s" s="2">
         <v>670</v>
       </c>
-      <c r="O93" t="s" s="2">
-        <v>671</v>
-      </c>
+      <c r="N93" s="2"/>
+      <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>83</v>
       </c>
@@ -14484,10 +14537,10 @@
         <v>250</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>672</v>
+        <v>649</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>673</v>
+        <v>650</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>83</v>
@@ -14505,13 +14558,13 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>83</v>
@@ -14532,7 +14585,7 @@
         <v>83</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>675</v>
+        <v>652</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>83</v>
@@ -14543,10 +14596,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14557,7 +14610,7 @@
         <v>81</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>83</v>
@@ -14569,15 +14622,17 @@
         <v>93</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>677</v>
+        <v>112</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>678</v>
+        <v>673</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>679</v>
-      </c>
-      <c r="N94" s="2"/>
+        <v>674</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>675</v>
+      </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>83</v>
@@ -14602,13 +14657,11 @@
         <v>83</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y94" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="Y94" s="2"/>
       <c r="Z94" t="s" s="2">
-        <v>83</v>
+        <v>676</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>83</v>
@@ -14626,13 +14679,13 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>83</v>
@@ -14653,7 +14706,7 @@
         <v>83</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>681</v>
+        <v>155</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>83</v>
@@ -14664,10 +14717,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14678,7 +14731,7 @@
         <v>81</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>83</v>
@@ -14690,16 +14743,16 @@
         <v>93</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>256</v>
+        <v>679</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -14725,13 +14778,13 @@
         <v>83</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>116</v>
+        <v>83</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>686</v>
+        <v>83</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>687</v>
+        <v>83</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>83</v>
@@ -14749,13 +14802,13 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>688</v>
+        <v>683</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>83</v>
@@ -14776,7 +14829,7 @@
         <v>83</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>689</v>
+        <v>155</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>83</v>
@@ -14787,10 +14840,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>690</v>
+        <v>684</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>690</v>
+        <v>684</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14801,7 +14854,7 @@
         <v>81</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>83</v>
@@ -14813,18 +14866,20 @@
         <v>93</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>691</v>
+        <v>112</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>692</v>
+        <v>685</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>693</v>
+        <v>686</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>694</v>
-      </c>
-      <c r="O96" s="2"/>
+        <v>687</v>
+      </c>
+      <c r="O96" t="s" s="2">
+        <v>688</v>
+      </c>
       <c r="P96" t="s" s="2">
         <v>83</v>
       </c>
@@ -14848,13 +14903,13 @@
         <v>83</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>318</v>
+        <v>250</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>695</v>
+        <v>689</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>696</v>
+        <v>690</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>83</v>
@@ -14872,13 +14927,13 @@
         <v>83</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>83</v>
@@ -14899,21 +14954,21 @@
         <v>83</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>698</v>
+        <v>692</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ96" t="s" s="2">
-        <v>699</v>
+        <v>83</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>700</v>
+        <v>693</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>700</v>
+        <v>693</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14936,20 +14991,16 @@
         <v>93</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>256</v>
+        <v>694</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>702</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>703</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>704</v>
-      </c>
+        <v>696</v>
+      </c>
+      <c r="N97" s="2"/>
+      <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>83</v>
       </c>
@@ -14973,13 +15024,13 @@
         <v>83</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>318</v>
+        <v>83</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>705</v>
+        <v>83</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>706</v>
+        <v>83</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>83</v>
@@ -14997,7 +15048,7 @@
         <v>83</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -15024,21 +15075,21 @@
         <v>83</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="AP97" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ97" t="s" s="2">
-        <v>709</v>
+        <v>83</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>710</v>
+        <v>699</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>710</v>
+        <v>699</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -15064,15 +15115,15 @@
         <v>256</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>711</v>
+        <v>700</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>712</v>
-      </c>
-      <c r="N98" s="2"/>
-      <c r="O98" t="s" s="2">
-        <v>713</v>
-      </c>
+        <v>701</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>83</v>
       </c>
@@ -15096,13 +15147,13 @@
         <v>83</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>318</v>
+        <v>116</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>714</v>
+        <v>703</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>715</v>
+        <v>704</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>83</v>
@@ -15120,7 +15171,7 @@
         <v>83</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -15147,21 +15198,21 @@
         <v>83</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>717</v>
+        <v>706</v>
       </c>
       <c r="AP98" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ98" t="s" s="2">
-        <v>718</v>
+        <v>83</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>719</v>
+        <v>707</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>719</v>
+        <v>707</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15184,20 +15235,18 @@
         <v>93</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>256</v>
+        <v>708</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>720</v>
+        <v>709</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>721</v>
+        <v>710</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>722</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>723</v>
-      </c>
+        <v>711</v>
+      </c>
+      <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>83</v>
       </c>
@@ -15221,13 +15270,13 @@
         <v>83</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>724</v>
+        <v>712</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>725</v>
+        <v>713</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>83</v>
@@ -15245,7 +15294,7 @@
         <v>83</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>726</v>
+        <v>714</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -15272,21 +15321,21 @@
         <v>83</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>727</v>
+        <v>715</v>
       </c>
       <c r="AP99" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ99" t="s" s="2">
-        <v>728</v>
+        <v>716</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>729</v>
+        <v>717</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>729</v>
+        <v>717</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15297,7 +15346,7 @@
         <v>81</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>83</v>
@@ -15309,16 +15358,20 @@
         <v>93</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>564</v>
+        <v>256</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>730</v>
+        <v>718</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>731</v>
-      </c>
-      <c r="N100" s="2"/>
-      <c r="O100" s="2"/>
+        <v>719</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="O100" t="s" s="2">
+        <v>721</v>
+      </c>
       <c r="P100" t="s" s="2">
         <v>83</v>
       </c>
@@ -15342,13 +15395,13 @@
         <v>83</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>83</v>
+        <v>317</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>83</v>
+        <v>722</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>83</v>
+        <v>723</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>83</v>
@@ -15366,13 +15419,13 @@
         <v>83</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>732</v>
+        <v>724</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>83</v>
@@ -15393,21 +15446,21 @@
         <v>83</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>83</v>
+        <v>725</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ100" t="s" s="2">
-        <v>733</v>
+        <v>726</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>734</v>
+        <v>727</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>734</v>
+        <v>727</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15427,19 +15480,21 @@
         <v>83</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>151</v>
+        <v>256</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>152</v>
+        <v>728</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>153</v>
+        <v>729</v>
       </c>
       <c r="N101" s="2"/>
-      <c r="O101" s="2"/>
+      <c r="O101" t="s" s="2">
+        <v>730</v>
+      </c>
       <c r="P101" t="s" s="2">
         <v>83</v>
       </c>
@@ -15463,13 +15518,13 @@
         <v>83</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>83</v>
+        <v>317</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>83</v>
+        <v>731</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>83</v>
+        <v>732</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>83</v>
@@ -15487,7 +15542,7 @@
         <v>83</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>154</v>
+        <v>733</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -15499,7 +15554,7 @@
         <v>83</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>83</v>
@@ -15514,32 +15569,32 @@
         <v>83</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>155</v>
+        <v>734</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ101" t="s" s="2">
-        <v>83</v>
+        <v>735</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>177</v>
+        <v>83</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>83</v>
@@ -15548,21 +15603,23 @@
         <v>83</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>137</v>
+        <v>256</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>178</v>
+        <v>737</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>179</v>
+        <v>738</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="O102" s="2"/>
+        <v>739</v>
+      </c>
+      <c r="O102" t="s" s="2">
+        <v>740</v>
+      </c>
       <c r="P102" t="s" s="2">
         <v>83</v>
       </c>
@@ -15586,43 +15643,43 @@
         <v>83</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>83</v>
+        <v>317</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>83</v>
+        <v>741</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>83</v>
+        <v>742</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB102" t="s" s="2">
-        <v>140</v>
+        <v>83</v>
       </c>
       <c r="AC102" t="s" s="2">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="AD102" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE102" t="s" s="2">
-        <v>141</v>
+        <v>83</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>159</v>
+        <v>743</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>83</v>
@@ -15637,21 +15694,21 @@
         <v>83</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>155</v>
+        <v>744</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ102" t="s" s="2">
-        <v>83</v>
+        <v>745</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>736</v>
+        <v>746</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>736</v>
+        <v>746</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15662,7 +15719,7 @@
         <v>81</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>83</v>
@@ -15674,18 +15731,16 @@
         <v>93</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>256</v>
+        <v>581</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>737</v>
+        <v>747</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>738</v>
+        <v>748</v>
       </c>
       <c r="N103" s="2"/>
-      <c r="O103" t="s" s="2">
-        <v>739</v>
-      </c>
+      <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>83</v>
       </c>
@@ -15709,13 +15764,13 @@
         <v>83</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>318</v>
+        <v>83</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>740</v>
+        <v>83</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>741</v>
+        <v>83</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>83</v>
@@ -15733,13 +15788,13 @@
         <v>83</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>742</v>
+        <v>749</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>83</v>
@@ -15766,15 +15821,15 @@
         <v>83</v>
       </c>
       <c r="AQ103" t="s" s="2">
-        <v>743</v>
+        <v>750</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>744</v>
+        <v>751</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>744</v>
+        <v>751</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15794,23 +15849,19 @@
         <v>83</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>745</v>
+        <v>151</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>746</v>
+        <v>152</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>747</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>748</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>749</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="N104" s="2"/>
+      <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>83</v>
       </c>
@@ -15858,7 +15909,7 @@
         <v>83</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>750</v>
+        <v>154</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>81</v>
@@ -15870,7 +15921,7 @@
         <v>83</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>83</v>
@@ -15885,13 +15936,13 @@
         <v>83</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>727</v>
+        <v>155</v>
       </c>
       <c r="AP104" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ104" t="s" s="2">
-        <v>751</v>
+        <v>83</v>
       </c>
     </row>
     <row r="105" hidden="true">
@@ -15903,14 +15954,14 @@
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>83</v>
+        <v>177</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>83</v>
@@ -15919,23 +15970,21 @@
         <v>83</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>753</v>
+        <v>137</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>754</v>
+        <v>178</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>755</v>
+        <v>179</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>756</v>
-      </c>
-      <c r="O105" t="s" s="2">
-        <v>757</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
         <v>83</v>
       </c>
@@ -15971,31 +16020,31 @@
         <v>83</v>
       </c>
       <c r="AB105" t="s" s="2">
-        <v>83</v>
+        <v>140</v>
       </c>
       <c r="AC105" t="s" s="2">
-        <v>83</v>
+        <v>158</v>
       </c>
       <c r="AD105" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>83</v>
+        <v>141</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>758</v>
+        <v>159</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>83</v>
@@ -16010,21 +16059,21 @@
         <v>83</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>759</v>
+        <v>155</v>
       </c>
       <c r="AP105" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ105" t="s" s="2">
-        <v>760</v>
+        <v>83</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>761</v>
+        <v>753</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>761</v>
+        <v>753</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -16047,19 +16096,17 @@
         <v>93</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>762</v>
+        <v>256</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>763</v>
+        <v>754</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>764</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>765</v>
-      </c>
+        <v>755</v>
+      </c>
+      <c r="N106" s="2"/>
       <c r="O106" t="s" s="2">
-        <v>766</v>
+        <v>756</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>83</v>
@@ -16084,13 +16131,13 @@
         <v>83</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>83</v>
+        <v>317</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>83</v>
+        <v>757</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>83</v>
+        <v>758</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>83</v>
@@ -16108,7 +16155,7 @@
         <v>83</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>767</v>
+        <v>759</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
@@ -16135,21 +16182,21 @@
         <v>83</v>
       </c>
       <c r="AO106" t="s" s="2">
-        <v>768</v>
+        <v>83</v>
       </c>
       <c r="AP106" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ106" t="s" s="2">
-        <v>769</v>
+        <v>760</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>770</v>
+        <v>761</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>770</v>
+        <v>761</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -16172,19 +16219,19 @@
         <v>93</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>771</v>
+        <v>762</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>772</v>
+        <v>763</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>773</v>
+        <v>764</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>774</v>
+        <v>765</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>775</v>
+        <v>766</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>83</v>
@@ -16233,7 +16280,7 @@
         <v>83</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>776</v>
+        <v>767</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -16260,21 +16307,21 @@
         <v>83</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>777</v>
+        <v>744</v>
       </c>
       <c r="AP107" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ107" t="s" s="2">
-        <v>83</v>
+        <v>768</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>778</v>
+        <v>769</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>778</v>
+        <v>769</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -16297,17 +16344,19 @@
         <v>93</v>
       </c>
       <c r="K108" t="s" s="2">
+        <v>770</v>
+      </c>
+      <c r="L108" t="s" s="2">
         <v>771</v>
       </c>
-      <c r="L108" t="s" s="2">
-        <v>779</v>
-      </c>
       <c r="M108" t="s" s="2">
-        <v>780</v>
-      </c>
-      <c r="N108" s="2"/>
+        <v>772</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>773</v>
+      </c>
       <c r="O108" t="s" s="2">
-        <v>781</v>
+        <v>774</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>83</v>
@@ -16356,7 +16405,7 @@
         <v>83</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>782</v>
+        <v>775</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -16383,21 +16432,21 @@
         <v>83</v>
       </c>
       <c r="AO108" t="s" s="2">
+        <v>776</v>
+      </c>
+      <c r="AP108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ108" t="s" s="2">
         <v>777</v>
-      </c>
-      <c r="AP108" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ108" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>783</v>
+        <v>778</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>783</v>
+        <v>778</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16417,19 +16466,23 @@
         <v>83</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>784</v>
+        <v>779</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>785</v>
+        <v>780</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>786</v>
-      </c>
-      <c r="N109" s="2"/>
-      <c r="O109" s="2"/>
+        <v>781</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>782</v>
+      </c>
+      <c r="O109" t="s" s="2">
+        <v>783</v>
+      </c>
       <c r="P109" t="s" s="2">
         <v>83</v>
       </c>
@@ -16477,7 +16530,7 @@
         <v>83</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
@@ -16501,24 +16554,24 @@
         <v>83</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>787</v>
+        <v>83</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="AP109" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ109" t="s" s="2">
-        <v>83</v>
+        <v>786</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -16538,19 +16591,23 @@
         <v>83</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>151</v>
+        <v>788</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>152</v>
+        <v>789</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N110" s="2"/>
-      <c r="O110" s="2"/>
+        <v>790</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>791</v>
+      </c>
+      <c r="O110" t="s" s="2">
+        <v>792</v>
+      </c>
       <c r="P110" t="s" s="2">
         <v>83</v>
       </c>
@@ -16598,7 +16655,7 @@
         <v>83</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>154</v>
+        <v>793</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
@@ -16610,7 +16667,7 @@
         <v>83</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>83</v>
@@ -16625,7 +16682,7 @@
         <v>83</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>155</v>
+        <v>794</v>
       </c>
       <c r="AP110" t="s" s="2">
         <v>83</v>
@@ -16636,21 +16693,21 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>790</v>
+        <v>795</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>790</v>
+        <v>795</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>177</v>
+        <v>83</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>83</v>
@@ -16659,21 +16716,21 @@
         <v>83</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>137</v>
+        <v>788</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>178</v>
+        <v>796</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="O111" s="2"/>
+        <v>797</v>
+      </c>
+      <c r="N111" s="2"/>
+      <c r="O111" t="s" s="2">
+        <v>798</v>
+      </c>
       <c r="P111" t="s" s="2">
         <v>83</v>
       </c>
@@ -16721,19 +16778,19 @@
         <v>83</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>159</v>
+        <v>799</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>83</v>
@@ -16748,7 +16805,7 @@
         <v>83</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>155</v>
+        <v>794</v>
       </c>
       <c r="AP111" t="s" s="2">
         <v>83</v>
@@ -16759,46 +16816,42 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>791</v>
+        <v>800</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>791</v>
+        <v>800</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>514</v>
+        <v>83</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H112" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I112" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>137</v>
+        <v>801</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>515</v>
+        <v>802</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>231</v>
-      </c>
+        <v>803</v>
+      </c>
+      <c r="N112" s="2"/>
+      <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>83</v>
       </c>
@@ -16846,19 +16899,19 @@
         <v>83</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>517</v>
+        <v>800</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="AK112" t="s" s="2">
         <v>83</v>
@@ -16870,10 +16923,10 @@
         <v>83</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>83</v>
+        <v>804</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>135</v>
+        <v>805</v>
       </c>
       <c r="AP112" t="s" s="2">
         <v>83</v>
@@ -16884,10 +16937,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>792</v>
+        <v>806</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>792</v>
+        <v>806</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16910,17 +16963,15 @@
         <v>83</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>784</v>
+        <v>151</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>793</v>
+        <v>152</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>794</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>795</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="N113" s="2"/>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
         <v>83</v>
@@ -16969,7 +17020,7 @@
         <v>83</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>792</v>
+        <v>154</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
@@ -16981,7 +17032,7 @@
         <v>83</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>83</v>
@@ -16996,7 +17047,7 @@
         <v>83</v>
       </c>
       <c r="AO113" t="s" s="2">
-        <v>796</v>
+        <v>155</v>
       </c>
       <c r="AP113" t="s" s="2">
         <v>83</v>
@@ -17007,21 +17058,21 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>797</v>
+        <v>807</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>797</v>
+        <v>807</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>83</v>
+        <v>177</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>83</v>
@@ -17033,15 +17084,17 @@
         <v>83</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>152</v>
+        <v>178</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N114" s="2"/>
+        <v>179</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>180</v>
+      </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
         <v>83</v>
@@ -17090,19 +17143,19 @@
         <v>83</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>83</v>
@@ -17128,14 +17181,14 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>798</v>
+        <v>808</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>798</v>
+        <v>808</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>177</v>
+        <v>530</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
@@ -17148,24 +17201,26 @@
         <v>83</v>
       </c>
       <c r="I115" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="K115" t="s" s="2">
         <v>137</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>178</v>
+        <v>531</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>179</v>
+        <v>532</v>
       </c>
       <c r="N115" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="O115" s="2"/>
+      <c r="O115" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="P115" t="s" s="2">
         <v>83</v>
       </c>
@@ -17213,7 +17268,7 @@
         <v>83</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>159</v>
+        <v>533</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>81</v>
@@ -17240,7 +17295,7 @@
         <v>83</v>
       </c>
       <c r="AO115" t="s" s="2">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="AP115" t="s" s="2">
         <v>83</v>
@@ -17251,46 +17306,44 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>799</v>
+        <v>809</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>799</v>
+        <v>809</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>514</v>
+        <v>83</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I116" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="J116" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>137</v>
+        <v>801</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>515</v>
+        <v>810</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>516</v>
+        <v>811</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="O116" t="s" s="2">
-        <v>231</v>
-      </c>
+        <v>812</v>
+      </c>
+      <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
         <v>83</v>
       </c>
@@ -17338,19 +17391,19 @@
         <v>83</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>517</v>
+        <v>809</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI116" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="AK116" t="s" s="2">
         <v>83</v>
@@ -17365,7 +17418,7 @@
         <v>83</v>
       </c>
       <c r="AO116" t="s" s="2">
-        <v>135</v>
+        <v>813</v>
       </c>
       <c r="AP116" t="s" s="2">
         <v>83</v>
@@ -17376,10 +17429,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>800</v>
+        <v>814</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>800</v>
+        <v>814</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -17402,13 +17455,13 @@
         <v>83</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>771</v>
+        <v>151</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>801</v>
+        <v>152</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>802</v>
+        <v>153</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -17459,7 +17512,7 @@
         <v>83</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>800</v>
+        <v>154</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>81</v>
@@ -17471,7 +17524,7 @@
         <v>83</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>83</v>
@@ -17486,7 +17539,7 @@
         <v>83</v>
       </c>
       <c r="AO117" t="s" s="2">
-        <v>803</v>
+        <v>155</v>
       </c>
       <c r="AP117" t="s" s="2">
         <v>83</v>
@@ -17497,21 +17550,21 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>804</v>
+        <v>815</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>804</v>
+        <v>815</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>83</v>
+        <v>177</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G118" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H118" t="s" s="2">
         <v>83</v>
@@ -17523,15 +17576,17 @@
         <v>83</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>805</v>
+        <v>137</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>806</v>
+        <v>178</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>807</v>
-      </c>
-      <c r="N118" s="2"/>
+        <v>179</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>180</v>
+      </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
         <v>83</v>
@@ -17580,19 +17635,19 @@
         <v>83</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>804</v>
+        <v>159</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI118" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>83</v>
@@ -17607,7 +17662,7 @@
         <v>83</v>
       </c>
       <c r="AO118" t="s" s="2">
-        <v>808</v>
+        <v>155</v>
       </c>
       <c r="AP118" t="s" s="2">
         <v>83</v>
@@ -17618,42 +17673,46 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>809</v>
+        <v>816</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>809</v>
+        <v>816</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>83</v>
+        <v>530</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H119" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I119" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="J119" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>805</v>
+        <v>137</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>810</v>
+        <v>531</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>811</v>
-      </c>
-      <c r="N119" s="2"/>
-      <c r="O119" s="2"/>
+        <v>532</v>
+      </c>
+      <c r="N119" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="O119" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="P119" t="s" s="2">
         <v>83</v>
       </c>
@@ -17701,19 +17760,19 @@
         <v>83</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>809</v>
+        <v>533</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI119" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK119" t="s" s="2">
         <v>83</v>
@@ -17728,7 +17787,7 @@
         <v>83</v>
       </c>
       <c r="AO119" t="s" s="2">
-        <v>808</v>
+        <v>135</v>
       </c>
       <c r="AP119" t="s" s="2">
         <v>83</v>
@@ -17739,10 +17798,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>812</v>
+        <v>817</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>812</v>
+        <v>817</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17765,20 +17824,16 @@
         <v>83</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>288</v>
+        <v>788</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>813</v>
+        <v>818</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>814</v>
-      </c>
-      <c r="N120" t="s" s="2">
-        <v>815</v>
-      </c>
-      <c r="O120" t="s" s="2">
-        <v>816</v>
-      </c>
+        <v>819</v>
+      </c>
+      <c r="N120" s="2"/>
+      <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
         <v>83</v>
       </c>
@@ -17826,7 +17881,7 @@
         <v>83</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>812</v>
+        <v>817</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>81</v>
@@ -17850,10 +17905,10 @@
         <v>83</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>817</v>
+        <v>83</v>
       </c>
       <c r="AO120" t="s" s="2">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="AP120" t="s" s="2">
         <v>83</v>
@@ -17864,10 +17919,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17881,7 +17936,7 @@
         <v>92</v>
       </c>
       <c r="H121" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="I121" t="s" s="2">
         <v>83</v>
@@ -17890,17 +17945,15 @@
         <v>83</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>677</v>
+        <v>822</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>821</v>
-      </c>
-      <c r="N121" t="s" s="2">
-        <v>822</v>
-      </c>
+        <v>824</v>
+      </c>
+      <c r="N121" s="2"/>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
         <v>83</v>
@@ -17949,7 +18002,7 @@
         <v>83</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>81</v>
@@ -17964,33 +18017,33 @@
         <v>104</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>823</v>
+        <v>83</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>824</v>
+        <v>83</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO121" t="s" s="2">
         <v>825</v>
       </c>
-      <c r="AO121" t="s" s="2">
-        <v>826</v>
-      </c>
       <c r="AP121" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ121" t="s" s="2">
-        <v>827</v>
+        <v>83</v>
       </c>
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -18004,7 +18057,7 @@
         <v>92</v>
       </c>
       <c r="H122" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="I122" t="s" s="2">
         <v>83</v>
@@ -18013,13 +18066,13 @@
         <v>83</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>771</v>
+        <v>822</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -18070,7 +18123,7 @@
         <v>83</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>81</v>
@@ -18085,33 +18138,33 @@
         <v>104</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>831</v>
+        <v>83</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>832</v>
+        <v>83</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>833</v>
+        <v>83</v>
       </c>
       <c r="AO122" t="s" s="2">
-        <v>834</v>
+        <v>825</v>
       </c>
       <c r="AP122" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ122" t="s" s="2">
-        <v>835</v>
+        <v>83</v>
       </c>
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>836</v>
+        <v>829</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>836</v>
+        <v>829</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -18125,7 +18178,7 @@
         <v>92</v>
       </c>
       <c r="H123" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="I123" t="s" s="2">
         <v>83</v>
@@ -18134,18 +18187,20 @@
         <v>83</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>805</v>
+        <v>288</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>837</v>
+        <v>830</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>838</v>
+        <v>831</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>839</v>
-      </c>
-      <c r="O123" s="2"/>
+        <v>832</v>
+      </c>
+      <c r="O123" t="s" s="2">
+        <v>833</v>
+      </c>
       <c r="P123" t="s" s="2">
         <v>83</v>
       </c>
@@ -18193,7 +18248,7 @@
         <v>83</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>836</v>
+        <v>829</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>81</v>
@@ -18208,19 +18263,19 @@
         <v>104</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>840</v>
+        <v>83</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>841</v>
+        <v>83</v>
       </c>
       <c r="AM123" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>842</v>
+        <v>834</v>
       </c>
       <c r="AO123" t="s" s="2">
-        <v>843</v>
+        <v>835</v>
       </c>
       <c r="AP123" t="s" s="2">
         <v>83</v>
@@ -18231,10 +18286,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>844</v>
+        <v>836</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>844</v>
+        <v>836</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -18248,7 +18303,7 @@
         <v>92</v>
       </c>
       <c r="H124" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="I124" t="s" s="2">
         <v>83</v>
@@ -18257,15 +18312,17 @@
         <v>83</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>295</v>
+        <v>694</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>845</v>
+        <v>837</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>846</v>
-      </c>
-      <c r="N124" s="2"/>
+        <v>838</v>
+      </c>
+      <c r="N124" t="s" s="2">
+        <v>839</v>
+      </c>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
         <v>83</v>
@@ -18314,7 +18371,7 @@
         <v>83</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>844</v>
+        <v>836</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>81</v>
@@ -18329,33 +18386,33 @@
         <v>104</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>83</v>
+        <v>840</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>83</v>
+        <v>841</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>83</v>
+        <v>842</v>
       </c>
       <c r="AO124" t="s" s="2">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="AP124" t="s" s="2">
-        <v>443</v>
+        <v>83</v>
       </c>
       <c r="AQ124" t="s" s="2">
-        <v>83</v>
+        <v>844</v>
       </c>
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -18369,7 +18426,7 @@
         <v>92</v>
       </c>
       <c r="H125" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="I125" t="s" s="2">
         <v>83</v>
@@ -18378,13 +18435,13 @@
         <v>83</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
@@ -18435,7 +18492,7 @@
         <v>83</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>81</v>
@@ -18450,25 +18507,25 @@
         <v>104</v>
       </c>
       <c r="AK125" t="s" s="2">
-        <v>83</v>
+        <v>848</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>83</v>
+        <v>849</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN125" t="s" s="2">
+        <v>850</v>
+      </c>
+      <c r="AO125" t="s" s="2">
         <v>851</v>
       </c>
-      <c r="AO125" t="s" s="2">
+      <c r="AP125" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ125" t="s" s="2">
         <v>852</v>
-      </c>
-      <c r="AP125" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ125" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="126" hidden="true">
@@ -18490,7 +18547,7 @@
         <v>92</v>
       </c>
       <c r="H126" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="I126" t="s" s="2">
         <v>83</v>
@@ -18499,15 +18556,17 @@
         <v>83</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>151</v>
+        <v>822</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>152</v>
+        <v>854</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N126" s="2"/>
+        <v>855</v>
+      </c>
+      <c r="N126" t="s" s="2">
+        <v>856</v>
+      </c>
       <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
         <v>83</v>
@@ -18556,7 +18615,7 @@
         <v>83</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>154</v>
+        <v>853</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>81</v>
@@ -18568,22 +18627,22 @@
         <v>83</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>83</v>
+        <v>857</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>83</v>
+        <v>858</v>
       </c>
       <c r="AM126" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>83</v>
+        <v>859</v>
       </c>
       <c r="AO126" t="s" s="2">
-        <v>155</v>
+        <v>860</v>
       </c>
       <c r="AP126" t="s" s="2">
         <v>83</v>
@@ -18594,21 +18653,21 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>854</v>
+        <v>861</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>854</v>
+        <v>861</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
-        <v>177</v>
+        <v>83</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G127" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H127" t="s" s="2">
         <v>83</v>
@@ -18620,17 +18679,15 @@
         <v>83</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>137</v>
+        <v>295</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>178</v>
+        <v>862</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>180</v>
-      </c>
+        <v>863</v>
+      </c>
+      <c r="N127" s="2"/>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
         <v>83</v>
@@ -18679,19 +18736,19 @@
         <v>83</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>159</v>
+        <v>861</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH127" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI127" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="AK127" t="s" s="2">
         <v>83</v>
@@ -18706,10 +18763,10 @@
         <v>83</v>
       </c>
       <c r="AO127" t="s" s="2">
-        <v>155</v>
+        <v>864</v>
       </c>
       <c r="AP127" t="s" s="2">
-        <v>83</v>
+        <v>459</v>
       </c>
       <c r="AQ127" t="s" s="2">
         <v>83</v>
@@ -18717,46 +18774,42 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>855</v>
+        <v>865</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>855</v>
+        <v>865</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>514</v>
+        <v>83</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G128" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H128" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I128" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="J128" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>137</v>
+        <v>801</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>515</v>
+        <v>866</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="N128" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="O128" t="s" s="2">
-        <v>231</v>
-      </c>
+        <v>867</v>
+      </c>
+      <c r="N128" s="2"/>
+      <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
         <v>83</v>
       </c>
@@ -18804,19 +18857,19 @@
         <v>83</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>517</v>
+        <v>865</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH128" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI128" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="AK128" t="s" s="2">
         <v>83</v>
@@ -18828,10 +18881,10 @@
         <v>83</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>83</v>
+        <v>868</v>
       </c>
       <c r="AO128" t="s" s="2">
-        <v>135</v>
+        <v>869</v>
       </c>
       <c r="AP128" t="s" s="2">
         <v>83</v>
@@ -18842,10 +18895,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>856</v>
+        <v>870</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>856</v>
+        <v>870</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18853,7 +18906,7 @@
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="G129" t="s" s="2">
         <v>92</v>
@@ -18868,17 +18921,15 @@
         <v>83</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>691</v>
+        <v>151</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>857</v>
+        <v>152</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>858</v>
-      </c>
-      <c r="N129" t="s" s="2">
-        <v>859</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="N129" s="2"/>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
         <v>83</v>
@@ -18903,13 +18954,13 @@
         <v>83</v>
       </c>
       <c r="X129" t="s" s="2">
-        <v>318</v>
+        <v>83</v>
       </c>
       <c r="Y129" t="s" s="2">
-        <v>860</v>
+        <v>83</v>
       </c>
       <c r="Z129" t="s" s="2">
-        <v>861</v>
+        <v>83</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>83</v>
@@ -18927,10 +18978,10 @@
         <v>83</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>856</v>
+        <v>154</v>
       </c>
       <c r="AG129" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AH129" t="s" s="2">
         <v>92</v>
@@ -18939,7 +18990,7 @@
         <v>83</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="AK129" t="s" s="2">
         <v>83</v>
@@ -18951,35 +19002,35 @@
         <v>83</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>851</v>
+        <v>83</v>
       </c>
       <c r="AO129" t="s" s="2">
-        <v>862</v>
+        <v>155</v>
       </c>
       <c r="AP129" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ129" t="s" s="2">
-        <v>863</v>
+        <v>83</v>
       </c>
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>864</v>
+        <v>871</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>864</v>
+        <v>871</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>83</v>
+        <v>177</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G130" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H130" t="s" s="2">
         <v>83</v>
@@ -18991,15 +19042,17 @@
         <v>83</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>256</v>
+        <v>137</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>865</v>
+        <v>178</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>866</v>
-      </c>
-      <c r="N130" s="2"/>
+        <v>179</v>
+      </c>
+      <c r="N130" t="s" s="2">
+        <v>180</v>
+      </c>
       <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
         <v>83</v>
@@ -19024,13 +19077,13 @@
         <v>83</v>
       </c>
       <c r="X130" t="s" s="2">
-        <v>318</v>
+        <v>83</v>
       </c>
       <c r="Y130" t="s" s="2">
-        <v>867</v>
+        <v>83</v>
       </c>
       <c r="Z130" t="s" s="2">
-        <v>868</v>
+        <v>83</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>83</v>
@@ -19048,19 +19101,19 @@
         <v>83</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>864</v>
+        <v>159</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH130" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI130" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ130" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK130" t="s" s="2">
         <v>83</v>
@@ -19072,16 +19125,16 @@
         <v>83</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>869</v>
+        <v>83</v>
       </c>
       <c r="AO130" t="s" s="2">
-        <v>870</v>
+        <v>155</v>
       </c>
       <c r="AP130" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ130" t="s" s="2">
-        <v>871</v>
+        <v>83</v>
       </c>
     </row>
     <row r="131" hidden="true">
@@ -19093,35 +19146,39 @@
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
-        <v>83</v>
+        <v>530</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G131" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H131" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I131" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="J131" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>873</v>
+        <v>137</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>874</v>
+        <v>531</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>875</v>
-      </c>
-      <c r="N131" s="2"/>
-      <c r="O131" s="2"/>
+        <v>532</v>
+      </c>
+      <c r="N131" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="O131" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="P131" t="s" s="2">
         <v>83</v>
       </c>
@@ -19169,19 +19226,19 @@
         <v>83</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>872</v>
+        <v>533</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH131" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI131" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ131" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK131" t="s" s="2">
         <v>83</v>
@@ -19190,13 +19247,13 @@
         <v>83</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>876</v>
+        <v>83</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>869</v>
+        <v>83</v>
       </c>
       <c r="AO131" t="s" s="2">
-        <v>877</v>
+        <v>135</v>
       </c>
       <c r="AP131" t="s" s="2">
         <v>83</v>
@@ -19207,21 +19264,21 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>878</v>
+        <v>873</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>878</v>
+        <v>873</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>879</v>
+        <v>83</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="G132" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H132" t="s" s="2">
         <v>83</v>
@@ -19233,16 +19290,16 @@
         <v>83</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>880</v>
+        <v>708</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>881</v>
+        <v>874</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>882</v>
+        <v>875</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>883</v>
+        <v>876</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -19268,13 +19325,13 @@
         <v>83</v>
       </c>
       <c r="X132" t="s" s="2">
-        <v>83</v>
+        <v>317</v>
       </c>
       <c r="Y132" t="s" s="2">
-        <v>83</v>
+        <v>877</v>
       </c>
       <c r="Z132" t="s" s="2">
-        <v>83</v>
+        <v>878</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>83</v>
@@ -19292,13 +19349,13 @@
         <v>83</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>878</v>
+        <v>873</v>
       </c>
       <c r="AG132" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AH132" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI132" t="s" s="2">
         <v>83</v>
@@ -19316,24 +19373,24 @@
         <v>83</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>83</v>
+        <v>868</v>
       </c>
       <c r="AO132" t="s" s="2">
-        <v>884</v>
+        <v>879</v>
       </c>
       <c r="AP132" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ132" t="s" s="2">
-        <v>83</v>
+        <v>880</v>
       </c>
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -19344,7 +19401,7 @@
         <v>81</v>
       </c>
       <c r="G133" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H133" t="s" s="2">
         <v>83</v>
@@ -19356,17 +19413,15 @@
         <v>83</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>886</v>
+        <v>256</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>887</v>
+        <v>882</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>888</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>889</v>
-      </c>
+        <v>883</v>
+      </c>
+      <c r="N133" s="2"/>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
         <v>83</v>
@@ -19391,13 +19446,13 @@
         <v>83</v>
       </c>
       <c r="X133" t="s" s="2">
-        <v>83</v>
+        <v>317</v>
       </c>
       <c r="Y133" t="s" s="2">
-        <v>83</v>
+        <v>884</v>
       </c>
       <c r="Z133" t="s" s="2">
-        <v>83</v>
+        <v>885</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>83</v>
@@ -19415,13 +19470,13 @@
         <v>83</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH133" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI133" t="s" s="2">
         <v>83</v>
@@ -19436,23 +19491,390 @@
         <v>83</v>
       </c>
       <c r="AM133" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN133" t="s" s="2">
+        <v>886</v>
+      </c>
+      <c r="AO133" t="s" s="2">
+        <v>887</v>
+      </c>
+      <c r="AP133" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ133" t="s" s="2">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="134" hidden="true">
+      <c r="A134" t="s" s="2">
+        <v>889</v>
+      </c>
+      <c r="B134" t="s" s="2">
+        <v>889</v>
+      </c>
+      <c r="C134" s="2"/>
+      <c r="D134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E134" s="2"/>
+      <c r="F134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G134" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K134" t="s" s="2">
         <v>890</v>
       </c>
-      <c r="AN133" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO133" t="s" s="2">
+      <c r="L134" t="s" s="2">
         <v>891</v>
       </c>
-      <c r="AP133" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ133" t="s" s="2">
+      <c r="M134" t="s" s="2">
+        <v>892</v>
+      </c>
+      <c r="N134" s="2"/>
+      <c r="O134" s="2"/>
+      <c r="P134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q134" s="2"/>
+      <c r="R134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF134" t="s" s="2">
+        <v>889</v>
+      </c>
+      <c r="AG134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH134" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ134" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM134" t="s" s="2">
+        <v>893</v>
+      </c>
+      <c r="AN134" t="s" s="2">
+        <v>886</v>
+      </c>
+      <c r="AO134" t="s" s="2">
+        <v>894</v>
+      </c>
+      <c r="AP134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ134" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="135" hidden="true">
+      <c r="A135" t="s" s="2">
+        <v>895</v>
+      </c>
+      <c r="B135" t="s" s="2">
+        <v>895</v>
+      </c>
+      <c r="C135" s="2"/>
+      <c r="D135" t="s" s="2">
+        <v>896</v>
+      </c>
+      <c r="E135" s="2"/>
+      <c r="F135" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G135" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H135" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I135" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J135" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K135" t="s" s="2">
+        <v>897</v>
+      </c>
+      <c r="L135" t="s" s="2">
+        <v>898</v>
+      </c>
+      <c r="M135" t="s" s="2">
+        <v>899</v>
+      </c>
+      <c r="N135" t="s" s="2">
+        <v>900</v>
+      </c>
+      <c r="O135" s="2"/>
+      <c r="P135" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q135" s="2"/>
+      <c r="R135" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S135" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T135" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U135" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V135" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W135" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X135" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y135" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z135" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA135" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB135" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC135" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD135" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE135" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF135" t="s" s="2">
+        <v>895</v>
+      </c>
+      <c r="AG135" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH135" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI135" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ135" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK135" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL135" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM135" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN135" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO135" t="s" s="2">
+        <v>901</v>
+      </c>
+      <c r="AP135" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ135" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="136" hidden="true">
+      <c r="A136" t="s" s="2">
+        <v>902</v>
+      </c>
+      <c r="B136" t="s" s="2">
+        <v>902</v>
+      </c>
+      <c r="C136" s="2"/>
+      <c r="D136" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E136" s="2"/>
+      <c r="F136" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G136" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H136" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I136" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J136" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K136" t="s" s="2">
+        <v>903</v>
+      </c>
+      <c r="L136" t="s" s="2">
+        <v>904</v>
+      </c>
+      <c r="M136" t="s" s="2">
+        <v>905</v>
+      </c>
+      <c r="N136" t="s" s="2">
+        <v>906</v>
+      </c>
+      <c r="O136" s="2"/>
+      <c r="P136" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q136" s="2"/>
+      <c r="R136" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S136" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T136" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U136" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V136" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W136" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X136" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y136" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z136" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA136" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB136" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC136" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD136" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE136" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF136" t="s" s="2">
+        <v>902</v>
+      </c>
+      <c r="AG136" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH136" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI136" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ136" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK136" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL136" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM136" t="s" s="2">
+        <v>907</v>
+      </c>
+      <c r="AN136" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO136" t="s" s="2">
+        <v>908</v>
+      </c>
+      <c r="AP136" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ136" t="s" s="2">
         <v>83</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AQ133">
+  <autoFilter ref="A1:AQ136">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -19462,7 +19884,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI132">
+  <conditionalFormatting sqref="A2:AI135">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5318" uniqueCount="909">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5318" uniqueCount="910">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -656,7 +656,7 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>1749: source value from PENDING OUTPATIENT ORDERS - ORDER TYPE (52.41-2)</t>
+    <t>1749: source value based on PENDING OUTPATIENT ORDERS - ORDER TYPE (52.41-2)</t>
   </si>
   <si>
     <t>RxOut.PendingRxOrder.OrderType</t>
@@ -891,7 +891,7 @@
     <t>Identifier.value</t>
   </si>
   <si>
-    <t>1747: source value from PENDING OUTPATIENT ORDERS - PLACER NUMBER (52.41-.01)</t>
+    <t>1747: source value based on PENDING OUTPATIENT ORDERS - PLACER NUMBER (52.41-.01)</t>
   </si>
   <si>
     <t>RxOut.PendingRxOrder.PlacerCPRSOrderIEN,RxOut.PendingRxOrder.PlacerCPRSOrderSID</t>
@@ -1221,7 +1221,11 @@
     <t>medicationCodeableConcept</t>
   </si>
   <si>
-    <t>1754: source value from PENDING OUTPATIENT ORDERS - DRUG (52.41-11)</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+mrp-24-1753:If drug null then source value from (52.41-8) {null}</t>
+  </si>
+  <si>
+    <t>1754: source value based on PENDING OUTPATIENT ORDERS - DRUG (52.41-11)</t>
   </si>
   <si>
     <t>RxOut.PendingRxOrder.LocalDrugIEN,RxOut.PendingRxOrder.LocalDrugSID</t>
@@ -1339,7 +1343,7 @@
     <t>The date (and perhaps time) when the prescription was initially written or authored on.</t>
   </si>
   <si>
-    <t>1757: source value from PENDING OUTPATIENT ORDERS - LOGIN DATE (52.41-15)</t>
+    <t>1757: source value based on PENDING OUTPATIENT ORDERS - LOGIN DATE (52.41-15)</t>
   </si>
   <si>
     <t>RxOut.PendingRxOrder.LoginDateTime</t>
@@ -1373,7 +1377,7 @@
     <t>The individual, organization, or device that initiated the request and has responsibility for its activation.</t>
   </si>
   <si>
-    <t>1751: reference from PENDING OUTPATIENT ORDERS - PROVIDER (52.41-5)</t>
+    <t>1751: reference based on PENDING OUTPATIENT ORDERS - PROVIDER (52.41-5)</t>
   </si>
   <si>
     <t>RxOut.PendingRxOrder.ProviderIEN,RxOut.PendingRxOrder.ProviderSID</t>
@@ -1440,7 +1444,7 @@
     <t>The person who entered the order on behalf of another individual for example in the case of a verbal or a telephone order.</t>
   </si>
   <si>
-    <t>1750: reference from PENDING OUTPATIENT ORDERS - ENTERED BY (52.41-4)</t>
+    <t>1750: reference based on PENDING OUTPATIENT ORDERS - ENTERED BY (52.41-4)</t>
   </si>
   <si>
     <t>RxOut.PendingRxOrder.EnteredByStaffIEN,RxOut.PendingRxOrder.EnteredByStaffSID</t>
@@ -1625,7 +1629,7 @@
     <t>Extra information about the prescription that could not be conveyed by the other attributes.</t>
   </si>
   <si>
-    <t>1759: source value from PENDING OUTPATIENT ORDERS - PROVIDER COMMENTS (52.41-9)</t>
+    <t>1759: source value based on PENDING OUTPATIENT ORDERS - PROVIDER COMMENTS (52.41-9)</t>
   </si>
   <si>
     <t>Request.note</t>
@@ -1913,7 +1917,7 @@
 </t>
   </si>
   <si>
-    <t>1752: source value from PENDING OUTPATIENT ORDERS - EFFECTIVE DATE (52.41-6)</t>
+    <t>1752: source value based on PENDING OUTPATIENT ORDERS - EFFECTIVE DATE (52.41-6)</t>
   </si>
   <si>
     <t>RxOut.PendingRxOrder.EffectiveDateTime,RxOut.PharmacyInstructions.EffectiveDateTime,RxOut.ProviderComments.EffectiveDateTime</t>
@@ -2619,7 +2623,7 @@
     <t>If displaying "number of authorized fills", add 1 to this number.</t>
   </si>
   <si>
-    <t>1756: source value from PENDING OUTPATIENT ORDERS - # OF REFILLS (52.41-13)</t>
+    <t>1756: source value based on PENDING OUTPATIENT ORDERS - # OF REFILLS (52.41-13)</t>
   </si>
   <si>
     <t>RxOut.PendingRxOrder.NumberOfRefills</t>
@@ -2643,7 +2647,7 @@
     <t>The amount that is to be dispensed for one fill.</t>
   </si>
   <si>
-    <t>1755: source value from PENDING OUTPATIENT ORDERS - QTY (52.41-12)</t>
+    <t>1755: source value based on PENDING OUTPATIENT ORDERS - QTY (52.41-12)</t>
   </si>
   <si>
     <t>RxOut.PendingRxOrder.LocalQty</t>
@@ -2670,7 +2674,7 @@
     <t>In some situations, this attribute may be used instead of quantity to identify the amount supplied by how long it is expected to last, rather than the physical quantity issued, e.g. 90 days supply of medication (based on an ordered dosage). When possible, it is always better to specify quantity, as this tends to be more precise. expectedSupplyDuration will always be an estimate that can be influenced by external factors.</t>
   </si>
   <si>
-    <t>1758: source value from PENDING OUTPATIENT ORDERS - DAYS SUPPLY (52.41-101)</t>
+    <t>1758: source value based on PENDING OUTPATIENT ORDERS - DAYS SUPPLY (52.41-101)</t>
   </si>
   <si>
     <t>RxOut.PendingRxOrder.DaysSupply</t>
@@ -3182,7 +3186,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="88.6875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="88.69921875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="126.07421875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>
@@ -8448,13 +8452,13 @@
         <v>83</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>104</v>
+        <v>386</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>379</v>
@@ -8474,13 +8478,13 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>373</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D44" t="s" s="2">
         <v>83</v>
@@ -8502,7 +8506,7 @@
         <v>93</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L44" t="s" s="2">
         <v>375</v>
@@ -8576,7 +8580,7 @@
         <v>104</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>83</v>
@@ -8599,10 +8603,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8625,16 +8629,16 @@
         <v>93</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -8684,7 +8688,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>92</v>
@@ -8699,33 +8703,33 @@
         <v>104</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8748,16 +8752,16 @@
         <v>83</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -8807,7 +8811,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -8822,33 +8826,33 @@
         <v>104</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>310</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8871,13 +8875,13 @@
         <v>83</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -8928,7 +8932,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -8949,16 +8953,16 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>83</v>
@@ -8966,10 +8970,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8992,13 +8996,13 @@
         <v>93</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -9049,7 +9053,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -9064,33 +9068,33 @@
         <v>104</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -9113,13 +9117,13 @@
         <v>93</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -9170,7 +9174,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -9185,22 +9189,22 @@
         <v>104</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>83</v>
@@ -9208,10 +9212,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -9234,13 +9238,13 @@
         <v>83</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -9291,7 +9295,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -9312,16 +9316,16 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>83</v>
@@ -9329,10 +9333,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -9358,13 +9362,13 @@
         <v>256</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -9393,10 +9397,10 @@
         <v>317</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>83</v>
@@ -9414,7 +9418,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -9435,13 +9439,13 @@
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>83</v>
@@ -9452,10 +9456,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9478,13 +9482,13 @@
         <v>83</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -9535,7 +9539,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -9550,10 +9554,10 @@
         <v>104</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>83</v>
@@ -9562,10 +9566,10 @@
         <v>83</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>83</v>
@@ -9573,10 +9577,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9602,13 +9606,13 @@
         <v>256</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -9637,10 +9641,10 @@
         <v>317</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>83</v>
@@ -9658,7 +9662,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -9679,27 +9683,27 @@
         <v>83</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9722,16 +9726,16 @@
         <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -9781,7 +9785,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -9802,16 +9806,16 @@
         <v>83</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>310</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>83</v>
@@ -9819,10 +9823,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9845,13 +9849,13 @@
         <v>93</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -9902,7 +9906,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -9923,13 +9927,13 @@
         <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>83</v>
@@ -9940,10 +9944,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9969,10 +9973,10 @@
         <v>106</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -10023,7 +10027,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -10050,7 +10054,7 @@
         <v>83</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>83</v>
@@ -10061,10 +10065,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -10087,13 +10091,13 @@
         <v>93</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -10144,7 +10148,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -10165,13 +10169,13 @@
         <v>83</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>83</v>
@@ -10182,10 +10186,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -10211,14 +10215,14 @@
         <v>234</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
@@ -10267,7 +10271,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -10288,13 +10292,13 @@
         <v>83</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>83</v>
@@ -10305,10 +10309,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10334,13 +10338,13 @@
         <v>256</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -10369,10 +10373,10 @@
         <v>317</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>83</v>
@@ -10390,7 +10394,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -10417,7 +10421,7 @@
         <v>83</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>83</v>
@@ -10428,10 +10432,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10454,13 +10458,13 @@
         <v>83</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -10511,7 +10515,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -10532,13 +10536,13 @@
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>83</v>
@@ -10549,10 +10553,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10575,13 +10579,13 @@
         <v>83</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -10632,7 +10636,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -10647,19 +10651,19 @@
         <v>104</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>83</v>
@@ -10670,10 +10674,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10696,16 +10700,16 @@
         <v>83</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -10755,7 +10759,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -10776,13 +10780,13 @@
         <v>83</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>83</v>
@@ -10793,10 +10797,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10914,10 +10918,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -11037,14 +11041,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -11066,10 +11070,10 @@
         <v>137</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N65" t="s" s="2">
         <v>180</v>
@@ -11124,7 +11128,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -11162,10 +11166,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -11188,17 +11192,17 @@
         <v>93</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>83</v>
@@ -11247,7 +11251,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -11274,21 +11278,21 @@
         <v>83</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ66" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11314,14 +11318,14 @@
         <v>151</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -11370,7 +11374,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -11385,7 +11389,7 @@
         <v>104</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>83</v>
@@ -11397,21 +11401,21 @@
         <v>83</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ67" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11437,16 +11441,16 @@
         <v>256</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>83</v>
@@ -11474,10 +11478,10 @@
         <v>317</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>83</v>
@@ -11495,7 +11499,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -11522,21 +11526,21 @@
         <v>83</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ68" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11562,10 +11566,10 @@
         <v>151</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -11616,7 +11620,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -11631,7 +11635,7 @@
         <v>104</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>83</v>
@@ -11643,21 +11647,21 @@
         <v>83</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11680,19 +11684,19 @@
         <v>93</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>83</v>
@@ -11741,7 +11745,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -11768,7 +11772,7 @@
         <v>83</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>83</v>
@@ -11779,10 +11783,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11900,10 +11904,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -12023,14 +12027,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -12052,10 +12056,10 @@
         <v>137</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N73" t="s" s="2">
         <v>180</v>
@@ -12110,7 +12114,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -12148,10 +12152,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12174,17 +12178,17 @@
         <v>93</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>83</v>
@@ -12233,7 +12237,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -12260,7 +12264,7 @@
         <v>83</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>83</v>
@@ -12271,10 +12275,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12297,17 +12301,17 @@
         <v>93</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>83</v>
@@ -12356,7 +12360,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -12368,7 +12372,7 @@
         <v>83</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>83</v>
@@ -12383,7 +12387,7 @@
         <v>83</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>83</v>
@@ -12394,10 +12398,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12515,10 +12519,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12638,10 +12642,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12664,13 +12668,13 @@
         <v>93</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -12719,7 +12723,7 @@
         <v>141</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -12746,7 +12750,7 @@
         <v>83</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>83</v>
@@ -12757,13 +12761,13 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D79" t="s" s="2">
         <v>83</v>
@@ -12788,10 +12792,10 @@
         <v>288</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12842,7 +12846,7 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -12869,7 +12873,7 @@
         <v>83</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AP79" t="s" s="2">
         <v>83</v>
@@ -12880,10 +12884,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -13001,10 +13005,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -13124,10 +13128,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13150,16 +13154,16 @@
         <v>93</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -13209,7 +13213,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -13218,16 +13222,16 @@
         <v>92</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>83</v>
@@ -13236,21 +13240,21 @@
         <v>83</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ82" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13273,23 +13277,23 @@
         <v>93</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q83" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="R83" t="s" s="2">
         <v>83</v>
@@ -13334,7 +13338,7 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -13343,7 +13347,7 @@
         <v>92</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>104</v>
@@ -13361,21 +13365,21 @@
         <v>83</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ83" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13398,19 +13402,19 @@
         <v>93</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>83</v>
@@ -13459,7 +13463,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -13486,7 +13490,7 @@
         <v>83</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>83</v>
@@ -13497,10 +13501,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13523,13 +13527,13 @@
         <v>93</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -13580,7 +13584,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -13607,7 +13611,7 @@
         <v>83</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>83</v>
@@ -13618,10 +13622,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13644,19 +13648,19 @@
         <v>93</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>83</v>
@@ -13705,7 +13709,7 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -13732,7 +13736,7 @@
         <v>83</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>83</v>
@@ -13743,10 +13747,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13769,19 +13773,19 @@
         <v>93</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>83</v>
@@ -13830,7 +13834,7 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -13857,7 +13861,7 @@
         <v>83</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>83</v>
@@ -13868,10 +13872,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13897,10 +13901,10 @@
         <v>112</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -13930,10 +13934,10 @@
         <v>250</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>83</v>
@@ -13951,7 +13955,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -13978,7 +13982,7 @@
         <v>83</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>83</v>
@@ -13989,10 +13993,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -14015,13 +14019,13 @@
         <v>93</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -14029,7 +14033,7 @@
         <v>83</v>
       </c>
       <c r="Q89" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="R89" t="s" s="2">
         <v>83</v>
@@ -14074,7 +14078,7 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -14101,7 +14105,7 @@
         <v>83</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AP89" t="s" s="2">
         <v>83</v>
@@ -14112,10 +14116,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14138,13 +14142,13 @@
         <v>93</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -14195,7 +14199,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -14222,7 +14226,7 @@
         <v>83</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>83</v>
@@ -14233,10 +14237,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14259,13 +14263,13 @@
         <v>93</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -14316,7 +14320,7 @@
         <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -14343,7 +14347,7 @@
         <v>83</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>83</v>
@@ -14354,10 +14358,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14380,13 +14384,13 @@
         <v>93</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -14437,7 +14441,7 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -14464,7 +14468,7 @@
         <v>83</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>83</v>
@@ -14475,10 +14479,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14504,10 +14508,10 @@
         <v>112</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -14537,10 +14541,10 @@
         <v>250</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>83</v>
@@ -14558,7 +14562,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -14585,7 +14589,7 @@
         <v>83</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>83</v>
@@ -14596,10 +14600,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14625,13 +14629,13 @@
         <v>112</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -14661,7 +14665,7 @@
       </c>
       <c r="Y94" s="2"/>
       <c r="Z94" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>83</v>
@@ -14679,7 +14683,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -14717,10 +14721,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14743,16 +14747,16 @@
         <v>93</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -14802,7 +14806,7 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -14840,10 +14844,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14869,16 +14873,16 @@
         <v>112</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>83</v>
@@ -14906,10 +14910,10 @@
         <v>250</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>83</v>
@@ -14927,7 +14931,7 @@
         <v>83</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -14954,7 +14958,7 @@
         <v>83</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>83</v>
@@ -14965,10 +14969,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14991,13 +14995,13 @@
         <v>93</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -15048,7 +15052,7 @@
         <v>83</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -15075,7 +15079,7 @@
         <v>83</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="AP97" t="s" s="2">
         <v>83</v>
@@ -15086,10 +15090,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -15115,13 +15119,13 @@
         <v>256</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -15150,10 +15154,10 @@
         <v>116</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>83</v>
@@ -15171,7 +15175,7 @@
         <v>83</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -15198,7 +15202,7 @@
         <v>83</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="AP98" t="s" s="2">
         <v>83</v>
@@ -15209,10 +15213,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15235,16 +15239,16 @@
         <v>93</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -15273,10 +15277,10 @@
         <v>317</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>83</v>
@@ -15294,7 +15298,7 @@
         <v>83</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -15321,21 +15325,21 @@
         <v>83</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="AP99" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ99" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15361,16 +15365,16 @@
         <v>256</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>83</v>
@@ -15398,10 +15402,10 @@
         <v>317</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>83</v>
@@ -15419,7 +15423,7 @@
         <v>83</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
@@ -15446,21 +15450,21 @@
         <v>83</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ100" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15486,14 +15490,14 @@
         <v>256</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>83</v>
@@ -15521,10 +15525,10 @@
         <v>317</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>83</v>
@@ -15542,7 +15546,7 @@
         <v>83</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -15569,21 +15573,21 @@
         <v>83</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ101" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15609,16 +15613,16 @@
         <v>256</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>83</v>
@@ -15646,10 +15650,10 @@
         <v>317</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>83</v>
@@ -15667,7 +15671,7 @@
         <v>83</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
@@ -15694,21 +15698,21 @@
         <v>83</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ102" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15731,13 +15735,13 @@
         <v>93</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -15788,7 +15792,7 @@
         <v>83</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>81</v>
@@ -15821,15 +15825,15 @@
         <v>83</v>
       </c>
       <c r="AQ103" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15947,10 +15951,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -16070,10 +16074,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -16099,14 +16103,14 @@
         <v>256</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>83</v>
@@ -16134,10 +16138,10 @@
         <v>317</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>83</v>
@@ -16155,7 +16159,7 @@
         <v>83</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
@@ -16188,15 +16192,15 @@
         <v>83</v>
       </c>
       <c r="AQ106" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -16219,19 +16223,19 @@
         <v>93</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>83</v>
@@ -16280,7 +16284,7 @@
         <v>83</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -16307,21 +16311,21 @@
         <v>83</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="AP107" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ107" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -16344,19 +16348,19 @@
         <v>93</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>83</v>
@@ -16405,7 +16409,7 @@
         <v>83</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -16432,21 +16436,21 @@
         <v>83</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="AP108" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ108" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16469,19 +16473,19 @@
         <v>93</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>83</v>
@@ -16530,7 +16534,7 @@
         <v>83</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
@@ -16557,21 +16561,21 @@
         <v>83</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="AP109" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ109" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -16594,19 +16598,19 @@
         <v>93</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>83</v>
@@ -16655,7 +16659,7 @@
         <v>83</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
@@ -16682,7 +16686,7 @@
         <v>83</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="AP110" t="s" s="2">
         <v>83</v>
@@ -16693,10 +16697,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16719,17 +16723,17 @@
         <v>93</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>83</v>
@@ -16778,7 +16782,7 @@
         <v>83</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>81</v>
@@ -16805,7 +16809,7 @@
         <v>83</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="AP111" t="s" s="2">
         <v>83</v>
@@ -16816,10 +16820,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16842,13 +16846,13 @@
         <v>83</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -16899,7 +16903,7 @@
         <v>83</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
@@ -16923,10 +16927,10 @@
         <v>83</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="AP112" t="s" s="2">
         <v>83</v>
@@ -16937,10 +16941,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -17058,10 +17062,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -17181,14 +17185,14 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
@@ -17210,10 +17214,10 @@
         <v>137</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N115" t="s" s="2">
         <v>180</v>
@@ -17268,7 +17272,7 @@
         <v>83</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>81</v>
@@ -17306,10 +17310,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -17332,16 +17336,16 @@
         <v>83</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -17391,7 +17395,7 @@
         <v>83</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>81</v>
@@ -17418,7 +17422,7 @@
         <v>83</v>
       </c>
       <c r="AO116" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="AP116" t="s" s="2">
         <v>83</v>
@@ -17429,10 +17433,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -17550,10 +17554,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -17673,14 +17677,14 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
@@ -17702,10 +17706,10 @@
         <v>137</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N119" t="s" s="2">
         <v>180</v>
@@ -17760,7 +17764,7 @@
         <v>83</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>81</v>
@@ -17798,10 +17802,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17824,13 +17828,13 @@
         <v>83</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -17881,7 +17885,7 @@
         <v>83</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>81</v>
@@ -17908,7 +17912,7 @@
         <v>83</v>
       </c>
       <c r="AO120" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="AP120" t="s" s="2">
         <v>83</v>
@@ -17919,10 +17923,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17945,13 +17949,13 @@
         <v>83</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -18002,7 +18006,7 @@
         <v>83</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>81</v>
@@ -18029,7 +18033,7 @@
         <v>83</v>
       </c>
       <c r="AO121" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="AP121" t="s" s="2">
         <v>83</v>
@@ -18040,10 +18044,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -18066,13 +18070,13 @@
         <v>83</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -18123,7 +18127,7 @@
         <v>83</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>81</v>
@@ -18150,7 +18154,7 @@
         <v>83</v>
       </c>
       <c r="AO122" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="AP122" t="s" s="2">
         <v>83</v>
@@ -18161,10 +18165,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -18190,16 +18194,16 @@
         <v>288</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>83</v>
@@ -18248,7 +18252,7 @@
         <v>83</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>81</v>
@@ -18272,10 +18276,10 @@
         <v>83</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="AO123" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="AP123" t="s" s="2">
         <v>83</v>
@@ -18286,10 +18290,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -18312,16 +18316,16 @@
         <v>83</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
@@ -18371,7 +18375,7 @@
         <v>83</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>81</v>
@@ -18386,33 +18390,33 @@
         <v>104</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="AO124" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="AP124" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ124" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -18435,13 +18439,13 @@
         <v>83</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
@@ -18492,7 +18496,7 @@
         <v>83</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>81</v>
@@ -18507,33 +18511,33 @@
         <v>104</v>
       </c>
       <c r="AK125" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="AO125" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="AP125" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ125" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -18556,16 +18560,16 @@
         <v>83</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
@@ -18615,7 +18619,7 @@
         <v>83</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>81</v>
@@ -18630,19 +18634,19 @@
         <v>104</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="AM126" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="AO126" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="AP126" t="s" s="2">
         <v>83</v>
@@ -18653,10 +18657,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -18682,10 +18686,10 @@
         <v>295</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -18736,7 +18740,7 @@
         <v>83</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>81</v>
@@ -18763,10 +18767,10 @@
         <v>83</v>
       </c>
       <c r="AO127" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="AP127" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AQ127" t="s" s="2">
         <v>83</v>
@@ -18774,10 +18778,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18800,13 +18804,13 @@
         <v>83</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -18857,7 +18861,7 @@
         <v>83</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>81</v>
@@ -18881,10 +18885,10 @@
         <v>83</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="AO128" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="AP128" t="s" s="2">
         <v>83</v>
@@ -18895,10 +18899,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -19016,10 +19020,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -19139,14 +19143,14 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
@@ -19168,10 +19172,10 @@
         <v>137</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N131" t="s" s="2">
         <v>180</v>
@@ -19226,7 +19230,7 @@
         <v>83</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>81</v>
@@ -19264,10 +19268,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -19290,16 +19294,16 @@
         <v>83</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -19328,10 +19332,10 @@
         <v>317</v>
       </c>
       <c r="Y132" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="Z132" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>83</v>
@@ -19349,7 +19353,7 @@
         <v>83</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>92</v>
@@ -19373,24 +19377,24 @@
         <v>83</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="AO132" t="s" s="2">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="AP132" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ132" t="s" s="2">
-        <v>880</v>
+        <v>881</v>
       </c>
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -19416,10 +19420,10 @@
         <v>256</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -19449,10 +19453,10 @@
         <v>317</v>
       </c>
       <c r="Y133" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="Z133" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>83</v>
@@ -19470,7 +19474,7 @@
         <v>83</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>81</v>
@@ -19494,24 +19498,24 @@
         <v>83</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="AO133" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="AP133" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ133" t="s" s="2">
-        <v>888</v>
+        <v>889</v>
       </c>
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -19534,13 +19538,13 @@
         <v>83</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -19591,7 +19595,7 @@
         <v>83</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>81</v>
@@ -19612,13 +19616,13 @@
         <v>83</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="AO134" t="s" s="2">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="AP134" t="s" s="2">
         <v>83</v>
@@ -19629,14 +19633,14 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
@@ -19655,16 +19659,16 @@
         <v>83</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
@@ -19714,7 +19718,7 @@
         <v>83</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>81</v>
@@ -19741,7 +19745,7 @@
         <v>83</v>
       </c>
       <c r="AO135" t="s" s="2">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="AP135" t="s" s="2">
         <v>83</v>
@@ -19752,10 +19756,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19778,16 +19782,16 @@
         <v>83</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
@@ -19837,7 +19841,7 @@
         <v>83</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>81</v>
@@ -19858,13 +19862,13 @@
         <v>83</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="AN136" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO136" t="s" s="2">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="AP136" t="s" s="2">
         <v>83</v>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5318" uniqueCount="910">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5318" uniqueCount="912">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -825,6 +825,14 @@
     <t>Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://terminology.hl7.org/CodeSystem/v2-0203"/&gt;
+    &lt;code value="PLAC"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>extensible</t>
   </si>
   <si>
@@ -835,6 +843,9 @@
   </si>
   <si>
     <t>Identifier.type</t>
+  </si>
+  <si>
+    <t>1747-2: fixed value = http://terminology.hl7.org/CodeSystem/v2-0203#PLAC</t>
   </si>
   <si>
     <t>CX.5</t>
@@ -6412,7 +6423,7 @@
         <v>92</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>83</v>
@@ -6443,7 +6454,7 @@
         <v>83</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>83</v>
+        <v>261</v>
       </c>
       <c r="T27" t="s" s="2">
         <v>83</v>
@@ -6458,13 +6469,13 @@
         <v>83</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>83</v>
@@ -6482,7 +6493,7 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -6497,7 +6508,7 @@
         <v>104</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>83</v>
+        <v>266</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>83</v>
@@ -6515,15 +6526,15 @@
         <v>83</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -6549,16 +6560,16 @@
         <v>106</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>83</v>
@@ -6568,10 +6579,10 @@
         <v>83</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="U28" t="s" s="2">
         <v>83</v>
@@ -6607,7 +6618,7 @@
         <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -6622,7 +6633,7 @@
         <v>104</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>83</v>
@@ -6634,21 +6645,21 @@
         <v>83</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6674,13 +6685,13 @@
         <v>151</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -6694,7 +6705,7 @@
         <v>83</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="U29" t="s" s="2">
         <v>83</v>
@@ -6730,7 +6741,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -6745,10 +6756,10 @@
         <v>104</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>83</v>
@@ -6757,21 +6768,21 @@
         <v>83</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6794,13 +6805,13 @@
         <v>93</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -6851,7 +6862,7 @@
         <v>83</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -6878,21 +6889,21 @@
         <v>83</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6915,16 +6926,16 @@
         <v>93</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -6974,7 +6985,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -7001,21 +7012,21 @@
         <v>83</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -7041,13 +7052,13 @@
         <v>112</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -7076,10 +7087,10 @@
         <v>250</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>83</v>
@@ -7097,7 +7108,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>92</v>
@@ -7112,22 +7123,22 @@
         <v>104</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>83</v>
@@ -7135,10 +7146,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -7164,13 +7175,13 @@
         <v>256</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -7196,13 +7207,13 @@
         <v>83</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>83</v>
@@ -7220,7 +7231,7 @@
         <v>83</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -7241,13 +7252,13 @@
         <v>83</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>83</v>
@@ -7258,10 +7269,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -7287,13 +7298,13 @@
         <v>112</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -7322,10 +7333,10 @@
         <v>250</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>83</v>
@@ -7343,7 +7354,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>92</v>
@@ -7358,22 +7369,22 @@
         <v>104</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>83</v>
@@ -7381,10 +7392,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -7410,13 +7421,13 @@
         <v>256</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -7442,19 +7453,19 @@
         <v>83</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AC35" s="2"/>
       <c r="AD35" t="s" s="2">
@@ -7464,7 +7475,7 @@
         <v>141</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -7479,7 +7490,7 @@
         <v>104</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>83</v>
@@ -7488,13 +7499,13 @@
         <v>83</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>83</v>
@@ -7502,13 +7513,13 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>83</v>
@@ -7533,13 +7544,13 @@
         <v>256</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -7568,10 +7579,10 @@
         <v>250</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>83</v>
@@ -7589,7 +7600,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -7604,7 +7615,7 @@
         <v>104</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>83</v>
@@ -7613,13 +7624,13 @@
         <v>83</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>83</v>
@@ -7627,10 +7638,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7656,10 +7667,10 @@
         <v>112</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -7689,10 +7700,10 @@
         <v>250</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>83</v>
@@ -7710,7 +7721,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -7731,16 +7742,16 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>83</v>
@@ -7748,10 +7759,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7777,13 +7788,13 @@
         <v>220</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -7833,7 +7844,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -7860,7 +7871,7 @@
         <v>83</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>83</v>
@@ -7871,10 +7882,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7897,13 +7908,13 @@
         <v>93</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -7942,17 +7953,17 @@
         <v>83</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AC39" s="2"/>
       <c r="AD39" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -7979,7 +7990,7 @@
         <v>83</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>83</v>
@@ -7990,13 +8001,13 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>83</v>
@@ -8021,10 +8032,10 @@
         <v>220</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -8075,7 +8086,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -8090,7 +8101,7 @@
         <v>104</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>83</v>
@@ -8102,7 +8113,7 @@
         <v>83</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>83</v>
@@ -8113,13 +8124,13 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D41" t="s" s="2">
         <v>83</v>
@@ -8141,13 +8152,13 @@
         <v>93</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -8198,7 +8209,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -8213,7 +8224,7 @@
         <v>104</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>83</v>
@@ -8225,7 +8236,7 @@
         <v>83</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>83</v>
@@ -8236,10 +8247,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -8262,16 +8273,16 @@
         <v>93</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -8297,27 +8308,27 @@
         <v>83</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AC42" s="2"/>
       <c r="AD42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>92</v>
@@ -8338,30 +8349,30 @@
         <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D43" t="s" s="2">
         <v>83</v>
@@ -8386,13 +8397,13 @@
         <v>256</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -8418,11 +8429,11 @@
         <v>83</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Y43" s="2"/>
       <c r="Z43" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>83</v>
@@ -8440,7 +8451,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>92</v>
@@ -8452,39 +8463,39 @@
         <v>83</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D44" t="s" s="2">
         <v>83</v>
@@ -8506,16 +8517,16 @@
         <v>93</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -8565,7 +8576,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>92</v>
@@ -8580,33 +8591,33 @@
         <v>104</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8629,16 +8640,16 @@
         <v>93</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -8688,7 +8699,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>92</v>
@@ -8703,33 +8714,33 @@
         <v>104</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8752,16 +8763,16 @@
         <v>83</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -8811,7 +8822,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -8826,33 +8837,33 @@
         <v>104</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8875,13 +8886,13 @@
         <v>83</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -8932,7 +8943,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -8953,16 +8964,16 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>83</v>
@@ -8970,10 +8981,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8996,13 +9007,13 @@
         <v>93</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -9053,7 +9064,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -9068,33 +9079,33 @@
         <v>104</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -9117,13 +9128,13 @@
         <v>93</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -9174,7 +9185,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -9189,22 +9200,22 @@
         <v>104</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>83</v>
@@ -9212,10 +9223,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -9238,13 +9249,13 @@
         <v>83</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -9295,7 +9306,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -9316,16 +9327,16 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>83</v>
@@ -9333,10 +9344,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -9362,13 +9373,13 @@
         <v>256</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -9394,13 +9405,13 @@
         <v>83</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>83</v>
@@ -9418,7 +9429,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -9439,13 +9450,13 @@
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>83</v>
@@ -9456,10 +9467,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9482,13 +9493,13 @@
         <v>83</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -9539,7 +9550,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -9554,10 +9565,10 @@
         <v>104</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>83</v>
@@ -9566,10 +9577,10 @@
         <v>83</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>83</v>
@@ -9577,10 +9588,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9606,13 +9617,13 @@
         <v>256</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -9638,13 +9649,13 @@
         <v>83</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>83</v>
@@ -9662,7 +9673,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -9683,27 +9694,27 @@
         <v>83</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9726,16 +9737,16 @@
         <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -9785,7 +9796,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -9806,16 +9817,16 @@
         <v>83</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>83</v>
@@ -9823,10 +9834,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9849,13 +9860,13 @@
         <v>93</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -9906,7 +9917,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -9927,13 +9938,13 @@
         <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>83</v>
@@ -9944,10 +9955,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9973,10 +9984,10 @@
         <v>106</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -10027,7 +10038,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -10054,7 +10065,7 @@
         <v>83</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>83</v>
@@ -10065,10 +10076,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -10091,13 +10102,13 @@
         <v>93</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -10148,7 +10159,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -10169,13 +10180,13 @@
         <v>83</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>83</v>
@@ -10186,10 +10197,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -10215,14 +10226,14 @@
         <v>234</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
@@ -10271,7 +10282,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -10292,13 +10303,13 @@
         <v>83</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>83</v>
@@ -10309,10 +10320,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10338,13 +10349,13 @@
         <v>256</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -10370,13 +10381,13 @@
         <v>83</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>83</v>
@@ -10394,7 +10405,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -10421,7 +10432,7 @@
         <v>83</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>83</v>
@@ -10432,10 +10443,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10458,13 +10469,13 @@
         <v>83</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -10515,7 +10526,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -10536,13 +10547,13 @@
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>83</v>
@@ -10553,10 +10564,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10579,13 +10590,13 @@
         <v>83</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -10636,7 +10647,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -10651,19 +10662,19 @@
         <v>104</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>83</v>
@@ -10674,10 +10685,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10700,16 +10711,16 @@
         <v>83</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -10759,7 +10770,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -10780,13 +10791,13 @@
         <v>83</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>83</v>
@@ -10797,10 +10808,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10918,10 +10929,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -11041,14 +11052,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -11070,10 +11081,10 @@
         <v>137</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="N65" t="s" s="2">
         <v>180</v>
@@ -11128,7 +11139,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -11166,10 +11177,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -11192,17 +11203,17 @@
         <v>93</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>83</v>
@@ -11251,7 +11262,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -11278,21 +11289,21 @@
         <v>83</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ66" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11318,14 +11329,14 @@
         <v>151</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -11374,7 +11385,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -11389,7 +11400,7 @@
         <v>104</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>83</v>
@@ -11401,21 +11412,21 @@
         <v>83</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ67" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11441,16 +11452,16 @@
         <v>256</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>83</v>
@@ -11475,13 +11486,13 @@
         <v>83</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>83</v>
@@ -11499,7 +11510,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -11526,21 +11537,21 @@
         <v>83</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ68" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11566,10 +11577,10 @@
         <v>151</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -11620,7 +11631,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -11635,7 +11646,7 @@
         <v>104</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>83</v>
@@ -11647,21 +11658,21 @@
         <v>83</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11684,19 +11695,19 @@
         <v>93</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>83</v>
@@ -11745,7 +11756,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -11772,7 +11783,7 @@
         <v>83</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>83</v>
@@ -11783,10 +11794,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11904,10 +11915,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -12027,14 +12038,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -12056,10 +12067,10 @@
         <v>137</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="N73" t="s" s="2">
         <v>180</v>
@@ -12114,7 +12125,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -12152,10 +12163,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12178,17 +12189,17 @@
         <v>93</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>83</v>
@@ -12237,7 +12248,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -12264,7 +12275,7 @@
         <v>83</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>83</v>
@@ -12275,10 +12286,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12301,17 +12312,17 @@
         <v>93</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>83</v>
@@ -12360,7 +12371,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -12372,7 +12383,7 @@
         <v>83</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>83</v>
@@ -12387,7 +12398,7 @@
         <v>83</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>83</v>
@@ -12398,10 +12409,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12519,10 +12530,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12642,10 +12653,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12668,13 +12679,13 @@
         <v>93</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -12713,7 +12724,7 @@
         <v>83</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AC78" s="2"/>
       <c r="AD78" t="s" s="2">
@@ -12723,7 +12734,7 @@
         <v>141</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -12750,7 +12761,7 @@
         <v>83</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>83</v>
@@ -12761,13 +12772,13 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="D79" t="s" s="2">
         <v>83</v>
@@ -12789,13 +12800,13 @@
         <v>93</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12846,7 +12857,7 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -12873,7 +12884,7 @@
         <v>83</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="AP79" t="s" s="2">
         <v>83</v>
@@ -12884,10 +12895,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -13005,10 +13016,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -13128,10 +13139,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13154,16 +13165,16 @@
         <v>93</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -13213,7 +13224,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -13222,16 +13233,16 @@
         <v>92</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>83</v>
@@ -13240,21 +13251,21 @@
         <v>83</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ82" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13277,23 +13288,23 @@
         <v>93</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q83" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="R83" t="s" s="2">
         <v>83</v>
@@ -13338,7 +13349,7 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -13347,7 +13358,7 @@
         <v>92</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>104</v>
@@ -13365,21 +13376,21 @@
         <v>83</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ83" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13402,19 +13413,19 @@
         <v>93</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>83</v>
@@ -13463,7 +13474,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -13490,7 +13501,7 @@
         <v>83</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>83</v>
@@ -13501,10 +13512,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13527,13 +13538,13 @@
         <v>93</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -13584,7 +13595,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -13611,7 +13622,7 @@
         <v>83</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>83</v>
@@ -13622,10 +13633,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13648,19 +13659,19 @@
         <v>93</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>83</v>
@@ -13709,7 +13720,7 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -13736,7 +13747,7 @@
         <v>83</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>83</v>
@@ -13747,10 +13758,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13773,19 +13784,19 @@
         <v>93</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>83</v>
@@ -13834,7 +13845,7 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -13861,7 +13872,7 @@
         <v>83</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>83</v>
@@ -13872,10 +13883,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13901,10 +13912,10 @@
         <v>112</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -13934,10 +13945,10 @@
         <v>250</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>83</v>
@@ -13955,7 +13966,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -13982,7 +13993,7 @@
         <v>83</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>83</v>
@@ -13993,10 +14004,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -14019,13 +14030,13 @@
         <v>93</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -14033,7 +14044,7 @@
         <v>83</v>
       </c>
       <c r="Q89" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="R89" t="s" s="2">
         <v>83</v>
@@ -14078,7 +14089,7 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -14105,7 +14116,7 @@
         <v>83</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="AP89" t="s" s="2">
         <v>83</v>
@@ -14116,10 +14127,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14142,13 +14153,13 @@
         <v>93</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -14199,7 +14210,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -14226,7 +14237,7 @@
         <v>83</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>83</v>
@@ -14237,10 +14248,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14263,13 +14274,13 @@
         <v>93</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -14320,7 +14331,7 @@
         <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -14347,7 +14358,7 @@
         <v>83</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>83</v>
@@ -14358,10 +14369,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14384,13 +14395,13 @@
         <v>93</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -14441,7 +14452,7 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -14468,7 +14479,7 @@
         <v>83</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>83</v>
@@ -14479,10 +14490,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14508,10 +14519,10 @@
         <v>112</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -14541,10 +14552,10 @@
         <v>250</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>83</v>
@@ -14562,7 +14573,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -14589,7 +14600,7 @@
         <v>83</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>83</v>
@@ -14600,10 +14611,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14629,13 +14640,13 @@
         <v>112</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -14665,7 +14676,7 @@
       </c>
       <c r="Y94" s="2"/>
       <c r="Z94" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>83</v>
@@ -14683,7 +14694,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -14721,10 +14732,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14747,16 +14758,16 @@
         <v>93</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -14806,7 +14817,7 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -14844,10 +14855,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14873,16 +14884,16 @@
         <v>112</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>83</v>
@@ -14910,10 +14921,10 @@
         <v>250</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>83</v>
@@ -14931,7 +14942,7 @@
         <v>83</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -14958,7 +14969,7 @@
         <v>83</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>83</v>
@@ -14969,10 +14980,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14995,13 +15006,13 @@
         <v>93</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -15052,7 +15063,7 @@
         <v>83</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -15079,7 +15090,7 @@
         <v>83</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="AP97" t="s" s="2">
         <v>83</v>
@@ -15090,10 +15101,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -15119,13 +15130,13 @@
         <v>256</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -15154,10 +15165,10 @@
         <v>116</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>83</v>
@@ -15175,7 +15186,7 @@
         <v>83</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -15202,7 +15213,7 @@
         <v>83</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="AP98" t="s" s="2">
         <v>83</v>
@@ -15213,10 +15224,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15239,16 +15250,16 @@
         <v>93</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -15274,13 +15285,13 @@
         <v>83</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>83</v>
@@ -15298,7 +15309,7 @@
         <v>83</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -15325,21 +15336,21 @@
         <v>83</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="AP99" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ99" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15365,16 +15376,16 @@
         <v>256</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>83</v>
@@ -15399,13 +15410,13 @@
         <v>83</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>83</v>
@@ -15423,7 +15434,7 @@
         <v>83</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
@@ -15450,21 +15461,21 @@
         <v>83</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ100" t="s" s="2">
-        <v>727</v>
+        <v>729</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15490,14 +15501,14 @@
         <v>256</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" t="s" s="2">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>83</v>
@@ -15522,13 +15533,13 @@
         <v>83</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>83</v>
@@ -15546,7 +15557,7 @@
         <v>83</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -15573,21 +15584,21 @@
         <v>83</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ101" t="s" s="2">
-        <v>736</v>
+        <v>738</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15613,16 +15624,16 @@
         <v>256</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>83</v>
@@ -15647,13 +15658,13 @@
         <v>83</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>83</v>
@@ -15671,7 +15682,7 @@
         <v>83</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
@@ -15698,21 +15709,21 @@
         <v>83</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ102" t="s" s="2">
-        <v>746</v>
+        <v>748</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15735,13 +15746,13 @@
         <v>93</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -15792,7 +15803,7 @@
         <v>83</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>81</v>
@@ -15825,15 +15836,15 @@
         <v>83</v>
       </c>
       <c r="AQ103" t="s" s="2">
-        <v>751</v>
+        <v>753</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15951,10 +15962,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -16074,10 +16085,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -16103,14 +16114,14 @@
         <v>256</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" t="s" s="2">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>83</v>
@@ -16135,13 +16146,13 @@
         <v>83</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>83</v>
@@ -16159,7 +16170,7 @@
         <v>83</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
@@ -16192,15 +16203,15 @@
         <v>83</v>
       </c>
       <c r="AQ106" t="s" s="2">
-        <v>761</v>
+        <v>763</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -16223,19 +16234,19 @@
         <v>93</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>83</v>
@@ -16284,7 +16295,7 @@
         <v>83</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -16311,21 +16322,21 @@
         <v>83</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="AP107" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ107" t="s" s="2">
-        <v>769</v>
+        <v>771</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -16348,19 +16359,19 @@
         <v>93</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>83</v>
@@ -16409,7 +16420,7 @@
         <v>83</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -16436,21 +16447,21 @@
         <v>83</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="AP108" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ108" t="s" s="2">
-        <v>778</v>
+        <v>780</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16473,19 +16484,19 @@
         <v>93</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>83</v>
@@ -16534,7 +16545,7 @@
         <v>83</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
@@ -16561,21 +16572,21 @@
         <v>83</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="AP109" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ109" t="s" s="2">
-        <v>787</v>
+        <v>789</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -16598,19 +16609,19 @@
         <v>93</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>83</v>
@@ -16659,7 +16670,7 @@
         <v>83</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
@@ -16686,7 +16697,7 @@
         <v>83</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="AP110" t="s" s="2">
         <v>83</v>
@@ -16697,10 +16708,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16723,17 +16734,17 @@
         <v>93</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" t="s" s="2">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>83</v>
@@ -16782,7 +16793,7 @@
         <v>83</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>81</v>
@@ -16809,7 +16820,7 @@
         <v>83</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="AP111" t="s" s="2">
         <v>83</v>
@@ -16820,10 +16831,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16846,13 +16857,13 @@
         <v>83</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -16903,7 +16914,7 @@
         <v>83</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
@@ -16927,10 +16938,10 @@
         <v>83</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="AP112" t="s" s="2">
         <v>83</v>
@@ -16941,10 +16952,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -17062,10 +17073,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -17185,14 +17196,14 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
@@ -17214,10 +17225,10 @@
         <v>137</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="N115" t="s" s="2">
         <v>180</v>
@@ -17272,7 +17283,7 @@
         <v>83</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>81</v>
@@ -17310,10 +17321,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -17336,16 +17347,16 @@
         <v>83</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -17395,7 +17406,7 @@
         <v>83</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>81</v>
@@ -17422,7 +17433,7 @@
         <v>83</v>
       </c>
       <c r="AO116" t="s" s="2">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="AP116" t="s" s="2">
         <v>83</v>
@@ -17433,10 +17444,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -17554,10 +17565,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -17677,14 +17688,14 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
@@ -17706,10 +17717,10 @@
         <v>137</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="N119" t="s" s="2">
         <v>180</v>
@@ -17764,7 +17775,7 @@
         <v>83</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>81</v>
@@ -17802,10 +17813,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17828,13 +17839,13 @@
         <v>83</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -17885,7 +17896,7 @@
         <v>83</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>81</v>
@@ -17912,7 +17923,7 @@
         <v>83</v>
       </c>
       <c r="AO120" t="s" s="2">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="AP120" t="s" s="2">
         <v>83</v>
@@ -17923,10 +17934,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17949,13 +17960,13 @@
         <v>83</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -18006,7 +18017,7 @@
         <v>83</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>81</v>
@@ -18033,7 +18044,7 @@
         <v>83</v>
       </c>
       <c r="AO121" t="s" s="2">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="AP121" t="s" s="2">
         <v>83</v>
@@ -18044,10 +18055,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -18070,13 +18081,13 @@
         <v>83</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -18127,7 +18138,7 @@
         <v>83</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>81</v>
@@ -18154,7 +18165,7 @@
         <v>83</v>
       </c>
       <c r="AO122" t="s" s="2">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="AP122" t="s" s="2">
         <v>83</v>
@@ -18165,10 +18176,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -18191,19 +18202,19 @@
         <v>83</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>83</v>
@@ -18252,7 +18263,7 @@
         <v>83</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>81</v>
@@ -18276,10 +18287,10 @@
         <v>83</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="AO123" t="s" s="2">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="AP123" t="s" s="2">
         <v>83</v>
@@ -18290,10 +18301,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -18316,16 +18327,16 @@
         <v>83</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
@@ -18375,7 +18386,7 @@
         <v>83</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>81</v>
@@ -18390,33 +18401,33 @@
         <v>104</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="AO124" t="s" s="2">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="AP124" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ124" t="s" s="2">
-        <v>845</v>
+        <v>847</v>
       </c>
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -18439,13 +18450,13 @@
         <v>83</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
@@ -18496,7 +18507,7 @@
         <v>83</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>81</v>
@@ -18511,33 +18522,33 @@
         <v>104</v>
       </c>
       <c r="AK125" t="s" s="2">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="AO125" t="s" s="2">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="AP125" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ125" t="s" s="2">
-        <v>853</v>
+        <v>855</v>
       </c>
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -18560,16 +18571,16 @@
         <v>83</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
@@ -18619,7 +18630,7 @@
         <v>83</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>81</v>
@@ -18634,19 +18645,19 @@
         <v>104</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="AM126" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="AO126" t="s" s="2">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="AP126" t="s" s="2">
         <v>83</v>
@@ -18657,10 +18668,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -18683,13 +18694,13 @@
         <v>83</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -18740,7 +18751,7 @@
         <v>83</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>81</v>
@@ -18767,10 +18778,10 @@
         <v>83</v>
       </c>
       <c r="AO127" t="s" s="2">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="AP127" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AQ127" t="s" s="2">
         <v>83</v>
@@ -18778,10 +18789,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18804,13 +18815,13 @@
         <v>83</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -18861,7 +18872,7 @@
         <v>83</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>81</v>
@@ -18885,10 +18896,10 @@
         <v>83</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="AO128" t="s" s="2">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="AP128" t="s" s="2">
         <v>83</v>
@@ -18899,10 +18910,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -19020,10 +19031,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -19143,14 +19154,14 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
@@ -19172,10 +19183,10 @@
         <v>137</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="N131" t="s" s="2">
         <v>180</v>
@@ -19230,7 +19241,7 @@
         <v>83</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>81</v>
@@ -19268,10 +19279,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -19294,16 +19305,16 @@
         <v>83</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -19329,13 +19340,13 @@
         <v>83</v>
       </c>
       <c r="X132" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Y132" t="s" s="2">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="Z132" t="s" s="2">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>83</v>
@@ -19353,7 +19364,7 @@
         <v>83</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>92</v>
@@ -19377,24 +19388,24 @@
         <v>83</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="AO132" t="s" s="2">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="AP132" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ132" t="s" s="2">
-        <v>881</v>
+        <v>883</v>
       </c>
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -19420,10 +19431,10 @@
         <v>256</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -19450,13 +19461,13 @@
         <v>83</v>
       </c>
       <c r="X133" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Y133" t="s" s="2">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="Z133" t="s" s="2">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>83</v>
@@ -19474,7 +19485,7 @@
         <v>83</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>81</v>
@@ -19498,24 +19509,24 @@
         <v>83</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="AO133" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="AP133" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ133" t="s" s="2">
-        <v>889</v>
+        <v>891</v>
       </c>
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -19538,13 +19549,13 @@
         <v>83</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -19595,7 +19606,7 @@
         <v>83</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>81</v>
@@ -19616,13 +19627,13 @@
         <v>83</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="AO134" t="s" s="2">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="AP134" t="s" s="2">
         <v>83</v>
@@ -19633,14 +19644,14 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
@@ -19659,16 +19670,16 @@
         <v>83</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
@@ -19718,7 +19729,7 @@
         <v>83</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>81</v>
@@ -19745,7 +19756,7 @@
         <v>83</v>
       </c>
       <c r="AO135" t="s" s="2">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="AP135" t="s" s="2">
         <v>83</v>
@@ -19756,10 +19767,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19782,16 +19793,16 @@
         <v>83</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
@@ -19841,7 +19852,7 @@
         <v>83</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>81</v>
@@ -19862,13 +19873,13 @@
         <v>83</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="AN136" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO136" t="s" s="2">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="AP136" t="s" s="2">
         <v>83</v>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1233,7 +1233,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-mrp-24-1753:If drug null then source value from (52.41-8) {null}</t>
+mrp-24-1753:If drug null then source value from (52.41-8) {true}</t>
   </si>
   <si>
     <t>1754: source value based on PENDING OUTPATIENT ORDERS - DRUG (52.41-11)</t>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5318" uniqueCount="912">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5318" uniqueCount="911">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1075,9 +1075,6 @@
   <si>
     <t xml:space="preserve">pattern:$this}
 </t>
-  </si>
-  <si>
-    <t>2198: target not supported</t>
   </si>
   <si>
     <t>Message/Body/NewRx/MedicationPrescribed/Directions@@ -7490,19 +7487,19 @@
         <v>104</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="AL35" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN35" t="s" s="2">
+      <c r="AO35" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>333</v>
@@ -7513,13 +7510,13 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>334</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>83</v>
@@ -7579,7 +7576,7 @@
         <v>250</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="Z36" t="s" s="2">
         <v>339</v>
@@ -7615,7 +7612,7 @@
         <v>104</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>83</v>
@@ -7624,10 +7621,10 @@
         <v>83</v>
       </c>
       <c r="AN36" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AO36" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="AO36" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>333</v>
@@ -7638,10 +7635,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7667,10 +7664,10 @@
         <v>112</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -7700,11 +7697,11 @@
         <v>250</v>
       </c>
       <c r="Y37" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="Z37" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="Z37" t="s" s="2">
-        <v>352</v>
-      </c>
       <c r="AA37" t="s" s="2">
         <v>83</v>
       </c>
@@ -7721,7 +7718,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -7742,16 +7739,16 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AN37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO37" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="AN37" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO37" t="s" s="2">
+      <c r="AP37" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="AP37" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>83</v>
@@ -7759,10 +7756,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7788,13 +7785,13 @@
         <v>220</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -7844,7 +7841,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -7871,7 +7868,7 @@
         <v>83</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>83</v>
@@ -7882,10 +7879,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7908,13 +7905,13 @@
         <v>93</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -7953,17 +7950,17 @@
         <v>83</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AC39" s="2"/>
       <c r="AD39" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -7990,7 +7987,7 @@
         <v>83</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>83</v>
@@ -8001,13 +7998,13 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="C40" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="B40" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="C40" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>83</v>
@@ -8032,10 +8029,10 @@
         <v>220</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -8086,7 +8083,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -8101,7 +8098,7 @@
         <v>104</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>83</v>
@@ -8113,7 +8110,7 @@
         <v>83</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>83</v>
@@ -8124,13 +8121,13 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="C41" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="B41" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="C41" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="D41" t="s" s="2">
         <v>83</v>
@@ -8152,13 +8149,13 @@
         <v>93</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -8209,7 +8206,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -8224,7 +8221,7 @@
         <v>104</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>83</v>
@@ -8236,7 +8233,7 @@
         <v>83</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>83</v>
@@ -8247,10 +8244,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -8273,16 +8270,16 @@
         <v>93</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -8312,23 +8309,23 @@
       </c>
       <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AC42" s="2"/>
       <c r="AD42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>92</v>
@@ -8349,30 +8346,30 @@
         <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="AN42" t="s" s="2">
+      <c r="AO42" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="AO42" t="s" s="2">
+      <c r="AP42" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="AP42" t="s" s="2">
+      <c r="AQ42" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="AQ42" t="s" s="2">
-        <v>385</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="C43" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="B43" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="C43" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="D43" t="s" s="2">
         <v>83</v>
@@ -8397,13 +8394,13 @@
         <v>256</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -8433,69 +8430,69 @@
       </c>
       <c r="Y43" s="2"/>
       <c r="Z43" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AM43" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="AA43" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="AG43" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AH43" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI43" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ43" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="AK43" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AN43" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="AN43" t="s" s="2">
+      <c r="AO43" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="AO43" t="s" s="2">
+      <c r="AP43" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="AP43" t="s" s="2">
+      <c r="AQ43" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="AQ43" t="s" s="2">
-        <v>385</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="C44" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="B44" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="C44" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="D44" t="s" s="2">
         <v>83</v>
@@ -8517,16 +8514,16 @@
         <v>93</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -8576,7 +8573,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>92</v>
@@ -8591,33 +8588,33 @@
         <v>104</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM44" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="AN44" t="s" s="2">
+      <c r="AO44" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="AO44" t="s" s="2">
+      <c r="AP44" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="AP44" t="s" s="2">
+      <c r="AQ44" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="AQ44" t="s" s="2">
-        <v>385</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8640,16 +8637,16 @@
         <v>93</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -8699,7 +8696,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>92</v>
@@ -8714,33 +8711,33 @@
         <v>104</v>
       </c>
       <c r="AK45" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM45" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="AL45" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM45" t="s" s="2">
+      <c r="AN45" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="AN45" t="s" s="2">
+      <c r="AO45" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="AO45" t="s" s="2">
+      <c r="AP45" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="AP45" t="s" s="2">
+      <c r="AQ45" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="AQ45" t="s" s="2">
-        <v>405</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8763,16 +8760,16 @@
         <v>83</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -8822,7 +8819,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -8837,33 +8834,33 @@
         <v>104</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>312</v>
       </c>
       <c r="AO46" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AP46" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="AP46" t="s" s="2">
+      <c r="AQ46" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="AQ46" t="s" s="2">
-        <v>415</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8886,13 +8883,13 @@
         <v>83</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -8943,7 +8940,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -8964,16 +8961,16 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO47" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="AN47" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>421</v>
-      </c>
       <c r="AP47" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>83</v>
@@ -8981,10 +8978,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -9007,13 +9004,13 @@
         <v>93</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>425</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -9064,7 +9061,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -9079,33 +9076,33 @@
         <v>104</v>
       </c>
       <c r="AK48" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AL48" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="AL48" t="s" s="2">
+      <c r="AM48" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="AM48" t="s" s="2">
+      <c r="AN48" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="AN48" t="s" s="2">
+      <c r="AO48" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="AO48" t="s" s="2">
+      <c r="AP48" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="AP48" t="s" s="2">
+      <c r="AQ48" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="AQ48" t="s" s="2">
-        <v>432</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -9128,13 +9125,13 @@
         <v>93</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -9185,7 +9182,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -9200,22 +9197,22 @@
         <v>104</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AL49" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="AL49" t="s" s="2">
+      <c r="AM49" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="AM49" t="s" s="2">
+      <c r="AN49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO49" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AP49" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="AP49" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>83</v>
@@ -9223,10 +9220,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -9249,13 +9246,13 @@
         <v>83</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -9306,7 +9303,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -9327,16 +9324,16 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO50" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="AN50" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO50" t="s" s="2">
+      <c r="AP50" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="AP50" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>83</v>
@@ -9344,10 +9341,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -9373,13 +9370,13 @@
         <v>256</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -9408,11 +9405,11 @@
         <v>319</v>
       </c>
       <c r="Y51" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="Z51" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="Z51" t="s" s="2">
-        <v>453</v>
-      </c>
       <c r="AA51" t="s" s="2">
         <v>83</v>
       </c>
@@ -9429,7 +9426,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -9450,13 +9447,13 @@
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO51" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>83</v>
@@ -9467,10 +9464,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9493,13 +9490,13 @@
         <v>83</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -9550,7 +9547,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -9565,22 +9562,22 @@
         <v>104</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AL52" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="AL52" t="s" s="2">
+      <c r="AM52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO52" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="AM52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO52" t="s" s="2">
+      <c r="AP52" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="AP52" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>83</v>
@@ -9588,10 +9585,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9617,13 +9614,13 @@
         <v>256</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>466</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -9652,11 +9649,11 @@
         <v>319</v>
       </c>
       <c r="Y53" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="Z53" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="Z53" t="s" s="2">
-        <v>468</v>
-      </c>
       <c r="AA53" t="s" s="2">
         <v>83</v>
       </c>
@@ -9673,7 +9670,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -9694,27 +9691,27 @@
         <v>83</v>
       </c>
       <c r="AM53" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AN53" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="AN53" t="s" s="2">
+      <c r="AO53" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="AO53" t="s" s="2">
+      <c r="AP53" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="AP53" t="s" s="2">
+      <c r="AQ53" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="AQ53" t="s" s="2">
-        <v>473</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9737,16 +9734,16 @@
         <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -9796,7 +9793,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -9817,16 +9814,16 @@
         <v>83</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>312</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>83</v>
@@ -9834,10 +9831,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9860,13 +9857,13 @@
         <v>93</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>483</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>484</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -9917,7 +9914,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -9938,13 +9935,13 @@
         <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO55" t="s" s="2">
         <v>485</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>486</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>83</v>
@@ -9955,10 +9952,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9984,10 +9981,10 @@
         <v>106</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -10038,7 +10035,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -10065,7 +10062,7 @@
         <v>83</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>83</v>
@@ -10076,10 +10073,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -10102,13 +10099,13 @@
         <v>93</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -10159,7 +10156,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -10180,13 +10177,13 @@
         <v>83</v>
       </c>
       <c r="AM57" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO57" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>495</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>83</v>
@@ -10197,10 +10194,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -10226,14 +10223,14 @@
         <v>234</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
@@ -10282,7 +10279,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -10303,13 +10300,13 @@
         <v>83</v>
       </c>
       <c r="AM58" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO58" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>83</v>
@@ -10320,10 +10317,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10349,13 +10346,13 @@
         <v>256</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>503</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>505</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -10384,11 +10381,11 @@
         <v>319</v>
       </c>
       <c r="Y59" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="Z59" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="Z59" t="s" s="2">
-        <v>507</v>
-      </c>
       <c r="AA59" t="s" s="2">
         <v>83</v>
       </c>
@@ -10405,7 +10402,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -10432,7 +10429,7 @@
         <v>83</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>83</v>
@@ -10443,10 +10440,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10469,13 +10466,13 @@
         <v>83</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>511</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>512</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -10526,7 +10523,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -10547,13 +10544,13 @@
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO60" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>514</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>83</v>
@@ -10564,10 +10561,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10590,13 +10587,13 @@
         <v>83</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>517</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -10647,7 +10644,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -10662,19 +10659,19 @@
         <v>104</v>
       </c>
       <c r="AK61" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM61" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="AL61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM61" t="s" s="2">
+      <c r="AN61" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="AN61" t="s" s="2">
+      <c r="AO61" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>522</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>83</v>
@@ -10685,10 +10682,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10711,16 +10708,16 @@
         <v>83</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>524</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>525</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>527</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -10770,7 +10767,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -10791,13 +10788,13 @@
         <v>83</v>
       </c>
       <c r="AM62" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO62" t="s" s="2">
         <v>528</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>529</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>83</v>
@@ -10808,10 +10805,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10929,10 +10926,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -11052,14 +11049,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -11081,10 +11078,10 @@
         <v>137</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>534</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>535</v>
       </c>
       <c r="N65" t="s" s="2">
         <v>180</v>
@@ -11139,7 +11136,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -11177,10 +11174,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -11203,17 +11200,17 @@
         <v>93</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="L66" t="s" s="2">
         <v>538</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="M66" t="s" s="2">
         <v>539</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>540</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>83</v>
@@ -11262,7 +11259,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -11289,21 +11286,21 @@
         <v>83</v>
       </c>
       <c r="AO66" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="AP66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ66" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="AP66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ66" t="s" s="2">
-        <v>544</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11329,14 +11326,14 @@
         <v>151</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>547</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -11385,7 +11382,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -11400,33 +11397,33 @@
         <v>104</v>
       </c>
       <c r="AK67" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="AP67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ67" t="s" s="2">
         <v>550</v>
-      </c>
-      <c r="AL67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="AP67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ67" t="s" s="2">
-        <v>551</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11452,16 +11449,16 @@
         <v>256</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>554</v>
       </c>
-      <c r="N68" t="s" s="2">
+      <c r="O68" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>556</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>83</v>
@@ -11489,28 +11486,28 @@
         <v>319</v>
       </c>
       <c r="Y68" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="Z68" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="Z68" t="s" s="2">
+      <c r="AA68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF68" t="s" s="2">
         <v>558</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>559</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -11537,21 +11534,21 @@
         <v>83</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ68" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11577,10 +11574,10 @@
         <v>151</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>563</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -11631,7 +11628,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -11646,7 +11643,7 @@
         <v>104</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>83</v>
@@ -11658,21 +11655,21 @@
         <v>83</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11695,19 +11692,19 @@
         <v>93</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="L70" t="s" s="2">
         <v>567</v>
       </c>
-      <c r="L70" t="s" s="2">
+      <c r="M70" t="s" s="2">
         <v>568</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="N70" t="s" s="2">
+      <c r="O70" t="s" s="2">
         <v>570</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>571</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>83</v>
@@ -11756,7 +11753,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -11783,7 +11780,7 @@
         <v>83</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>83</v>
@@ -11794,10 +11791,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11915,10 +11912,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -12038,14 +12035,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -12067,10 +12064,10 @@
         <v>137</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>534</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>535</v>
       </c>
       <c r="N73" t="s" s="2">
         <v>180</v>
@@ -12125,7 +12122,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -12163,10 +12160,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12189,17 +12186,17 @@
         <v>93</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>578</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>579</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>83</v>
@@ -12248,7 +12245,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -12275,7 +12272,7 @@
         <v>83</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>83</v>
@@ -12286,10 +12283,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12312,17 +12309,17 @@
         <v>93</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="L75" t="s" s="2">
         <v>584</v>
       </c>
-      <c r="L75" t="s" s="2">
+      <c r="M75" t="s" s="2">
         <v>585</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>586</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>83</v>
@@ -12371,34 +12368,34 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
         <v>588</v>
       </c>
-      <c r="AG75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH75" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ75" t="s" s="2">
+      <c r="AK75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO75" t="s" s="2">
         <v>589</v>
-      </c>
-      <c r="AK75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO75" t="s" s="2">
-        <v>590</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>83</v>
@@ -12409,10 +12406,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12530,10 +12527,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12653,10 +12650,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12679,13 +12676,13 @@
         <v>93</v>
       </c>
       <c r="K78" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="L78" t="s" s="2">
         <v>594</v>
       </c>
-      <c r="L78" t="s" s="2">
+      <c r="M78" t="s" s="2">
         <v>595</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>596</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -12724,7 +12721,7 @@
         <v>83</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AC78" s="2"/>
       <c r="AD78" t="s" s="2">
@@ -12734,7 +12731,7 @@
         <v>141</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -12761,7 +12758,7 @@
         <v>83</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>83</v>
@@ -12772,13 +12769,13 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="C79" t="s" s="2">
         <v>599</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="C79" t="s" s="2">
-        <v>600</v>
       </c>
       <c r="D79" t="s" s="2">
         <v>83</v>
@@ -12803,10 +12800,10 @@
         <v>290</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>595</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>596</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12857,7 +12854,7 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -12884,7 +12881,7 @@
         <v>83</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="AP79" t="s" s="2">
         <v>83</v>
@@ -12895,10 +12892,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="B80" t="s" s="2">
         <v>601</v>
-      </c>
-      <c r="B80" t="s" s="2">
-        <v>602</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -13016,10 +13013,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="B81" t="s" s="2">
         <v>603</v>
-      </c>
-      <c r="B81" t="s" s="2">
-        <v>604</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -13139,10 +13136,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="B82" t="s" s="2">
         <v>605</v>
-      </c>
-      <c r="B82" t="s" s="2">
-        <v>606</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13165,16 +13162,16 @@
         <v>93</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>607</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="N82" t="s" s="2">
         <v>608</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>609</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -13224,48 +13221,48 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI82" t="s" s="2">
         <v>610</v>
-      </c>
-      <c r="AG82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH82" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI82" t="s" s="2">
-        <v>611</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK82" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="AL82" t="s" s="2">
         <v>612</v>
       </c>
-      <c r="AL82" t="s" s="2">
+      <c r="AM82" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO82" t="s" s="2">
         <v>613</v>
       </c>
-      <c r="AM82" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO82" t="s" s="2">
+      <c r="AP82" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ82" t="s" s="2">
         <v>614</v>
-      </c>
-      <c r="AP82" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ82" t="s" s="2">
-        <v>615</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="B83" t="s" s="2">
         <v>616</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>617</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13288,69 +13285,69 @@
         <v>93</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>619</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>620</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q83" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="R83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF83" t="s" s="2">
         <v>621</v>
       </c>
-      <c r="R83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>622</v>
-      </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
       </c>
@@ -13358,7 +13355,7 @@
         <v>92</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>104</v>
@@ -13376,21 +13373,21 @@
         <v>83</v>
       </c>
       <c r="AO83" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="AP83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ83" t="s" s="2">
         <v>623</v>
-      </c>
-      <c r="AP83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ83" t="s" s="2">
-        <v>624</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13413,19 +13410,19 @@
         <v>93</v>
       </c>
       <c r="K84" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="L84" t="s" s="2">
         <v>626</v>
       </c>
-      <c r="L84" t="s" s="2">
+      <c r="M84" t="s" s="2">
         <v>627</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>628</v>
       </c>
-      <c r="N84" t="s" s="2">
+      <c r="O84" t="s" s="2">
         <v>629</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>630</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>83</v>
@@ -13474,7 +13471,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -13501,7 +13498,7 @@
         <v>83</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>83</v>
@@ -13512,10 +13509,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13538,13 +13535,13 @@
         <v>93</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>634</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>635</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -13595,7 +13592,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -13622,7 +13619,7 @@
         <v>83</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>83</v>
@@ -13633,10 +13630,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13659,19 +13656,19 @@
         <v>93</v>
       </c>
       <c r="K86" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="L86" t="s" s="2">
         <v>638</v>
       </c>
-      <c r="L86" t="s" s="2">
+      <c r="M86" t="s" s="2">
         <v>639</v>
       </c>
-      <c r="M86" t="s" s="2">
+      <c r="N86" t="s" s="2">
         <v>640</v>
       </c>
-      <c r="N86" t="s" s="2">
+      <c r="O86" t="s" s="2">
         <v>641</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>642</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>83</v>
@@ -13720,7 +13717,7 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -13747,7 +13744,7 @@
         <v>83</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>83</v>
@@ -13758,10 +13755,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13784,19 +13781,19 @@
         <v>93</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>646</v>
       </c>
-      <c r="M87" t="s" s="2">
-        <v>647</v>
-      </c>
       <c r="N87" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="O87" t="s" s="2">
         <v>641</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>642</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>83</v>
@@ -13845,7 +13842,7 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -13872,7 +13869,7 @@
         <v>83</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>83</v>
@@ -13883,10 +13880,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13912,10 +13909,10 @@
         <v>112</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>650</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>651</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -13945,28 +13942,28 @@
         <v>250</v>
       </c>
       <c r="Y88" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="Z88" t="s" s="2">
         <v>652</v>
       </c>
-      <c r="Z88" t="s" s="2">
+      <c r="AA88" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF88" t="s" s="2">
         <v>653</v>
-      </c>
-      <c r="AA88" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB88" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC88" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD88" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE88" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF88" t="s" s="2">
-        <v>654</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -13993,7 +13990,7 @@
         <v>83</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>83</v>
@@ -14004,10 +14001,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -14030,13 +14027,13 @@
         <v>93</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="M89" t="s" s="2">
         <v>657</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>658</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -14044,52 +14041,52 @@
         <v>83</v>
       </c>
       <c r="Q89" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="R89" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF89" t="s" s="2">
         <v>659</v>
-      </c>
-      <c r="R89" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S89" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T89" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U89" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V89" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W89" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X89" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y89" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z89" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA89" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB89" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC89" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD89" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE89" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF89" t="s" s="2">
-        <v>660</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -14116,7 +14113,7 @@
         <v>83</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="AP89" t="s" s="2">
         <v>83</v>
@@ -14127,10 +14124,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14153,13 +14150,13 @@
         <v>93</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>662</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>663</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -14210,7 +14207,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -14237,7 +14234,7 @@
         <v>83</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>83</v>
@@ -14248,10 +14245,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14274,13 +14271,13 @@
         <v>93</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -14331,7 +14328,7 @@
         <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -14358,7 +14355,7 @@
         <v>83</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>83</v>
@@ -14369,10 +14366,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14395,13 +14392,13 @@
         <v>93</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>669</v>
-      </c>
-      <c r="M92" t="s" s="2">
-        <v>670</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -14452,7 +14449,7 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -14479,7 +14476,7 @@
         <v>83</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>83</v>
@@ -14490,10 +14487,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14519,10 +14516,10 @@
         <v>112</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -14552,11 +14549,11 @@
         <v>250</v>
       </c>
       <c r="Y93" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="Z93" t="s" s="2">
         <v>652</v>
       </c>
-      <c r="Z93" t="s" s="2">
-        <v>653</v>
-      </c>
       <c r="AA93" t="s" s="2">
         <v>83</v>
       </c>
@@ -14573,7 +14570,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -14600,7 +14597,7 @@
         <v>83</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>83</v>
@@ -14611,10 +14608,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14640,13 +14637,13 @@
         <v>112</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>676</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="N94" t="s" s="2">
         <v>677</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>678</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -14676,25 +14673,25 @@
       </c>
       <c r="Y94" s="2"/>
       <c r="Z94" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF94" t="s" s="2">
         <v>679</v>
-      </c>
-      <c r="AA94" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB94" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC94" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD94" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE94" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF94" t="s" s="2">
-        <v>680</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -14732,10 +14729,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14758,16 +14755,16 @@
         <v>93</v>
       </c>
       <c r="K95" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="L95" t="s" s="2">
         <v>682</v>
       </c>
-      <c r="L95" t="s" s="2">
+      <c r="M95" t="s" s="2">
         <v>683</v>
       </c>
-      <c r="M95" t="s" s="2">
+      <c r="N95" t="s" s="2">
         <v>684</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>685</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -14817,7 +14814,7 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -14855,10 +14852,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14884,16 +14881,16 @@
         <v>112</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>688</v>
       </c>
-      <c r="M96" t="s" s="2">
+      <c r="N96" t="s" s="2">
         <v>689</v>
       </c>
-      <c r="N96" t="s" s="2">
+      <c r="O96" t="s" s="2">
         <v>690</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>691</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>83</v>
@@ -14921,28 +14918,28 @@
         <v>250</v>
       </c>
       <c r="Y96" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="Z96" t="s" s="2">
         <v>692</v>
       </c>
-      <c r="Z96" t="s" s="2">
+      <c r="AA96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF96" t="s" s="2">
         <v>693</v>
-      </c>
-      <c r="AA96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF96" t="s" s="2">
-        <v>694</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -14969,7 +14966,7 @@
         <v>83</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>83</v>
@@ -14980,10 +14977,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -15006,13 +15003,13 @@
         <v>93</v>
       </c>
       <c r="K97" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="L97" t="s" s="2">
         <v>697</v>
       </c>
-      <c r="L97" t="s" s="2">
+      <c r="M97" t="s" s="2">
         <v>698</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>699</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -15063,7 +15060,7 @@
         <v>83</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -15090,7 +15087,7 @@
         <v>83</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="AP97" t="s" s="2">
         <v>83</v>
@@ -15101,10 +15098,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -15130,13 +15127,13 @@
         <v>256</v>
       </c>
       <c r="L98" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="M98" t="s" s="2">
         <v>703</v>
       </c>
-      <c r="M98" t="s" s="2">
+      <c r="N98" t="s" s="2">
         <v>704</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>705</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -15165,28 +15162,28 @@
         <v>116</v>
       </c>
       <c r="Y98" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="Z98" t="s" s="2">
         <v>706</v>
       </c>
-      <c r="Z98" t="s" s="2">
+      <c r="AA98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF98" t="s" s="2">
         <v>707</v>
-      </c>
-      <c r="AA98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF98" t="s" s="2">
-        <v>708</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -15213,7 +15210,7 @@
         <v>83</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="AP98" t="s" s="2">
         <v>83</v>
@@ -15224,10 +15221,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15250,16 +15247,16 @@
         <v>93</v>
       </c>
       <c r="K99" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="L99" t="s" s="2">
         <v>711</v>
       </c>
-      <c r="L99" t="s" s="2">
+      <c r="M99" t="s" s="2">
         <v>712</v>
       </c>
-      <c r="M99" t="s" s="2">
+      <c r="N99" t="s" s="2">
         <v>713</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>714</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -15288,28 +15285,28 @@
         <v>319</v>
       </c>
       <c r="Y99" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="Z99" t="s" s="2">
         <v>715</v>
       </c>
-      <c r="Z99" t="s" s="2">
+      <c r="AA99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF99" t="s" s="2">
         <v>716</v>
-      </c>
-      <c r="AA99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF99" t="s" s="2">
-        <v>717</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -15336,21 +15333,21 @@
         <v>83</v>
       </c>
       <c r="AO99" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="AP99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ99" t="s" s="2">
         <v>718</v>
-      </c>
-      <c r="AP99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ99" t="s" s="2">
-        <v>719</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15376,16 +15373,16 @@
         <v>256</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>721</v>
       </c>
-      <c r="M100" t="s" s="2">
+      <c r="N100" t="s" s="2">
         <v>722</v>
       </c>
-      <c r="N100" t="s" s="2">
+      <c r="O100" t="s" s="2">
         <v>723</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>724</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>83</v>
@@ -15413,28 +15410,28 @@
         <v>319</v>
       </c>
       <c r="Y100" t="s" s="2">
+        <v>724</v>
+      </c>
+      <c r="Z100" t="s" s="2">
         <v>725</v>
       </c>
-      <c r="Z100" t="s" s="2">
+      <c r="AA100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF100" t="s" s="2">
         <v>726</v>
-      </c>
-      <c r="AA100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF100" t="s" s="2">
-        <v>727</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
@@ -15461,21 +15458,21 @@
         <v>83</v>
       </c>
       <c r="AO100" t="s" s="2">
+        <v>727</v>
+      </c>
+      <c r="AP100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ100" t="s" s="2">
         <v>728</v>
-      </c>
-      <c r="AP100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ100" t="s" s="2">
-        <v>729</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15501,14 +15498,14 @@
         <v>256</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>730</v>
+      </c>
+      <c r="M101" t="s" s="2">
         <v>731</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>732</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" t="s" s="2">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>83</v>
@@ -15536,28 +15533,28 @@
         <v>319</v>
       </c>
       <c r="Y101" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="Z101" t="s" s="2">
         <v>734</v>
       </c>
-      <c r="Z101" t="s" s="2">
+      <c r="AA101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF101" t="s" s="2">
         <v>735</v>
-      </c>
-      <c r="AA101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF101" t="s" s="2">
-        <v>736</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -15584,21 +15581,21 @@
         <v>83</v>
       </c>
       <c r="AO101" t="s" s="2">
+        <v>736</v>
+      </c>
+      <c r="AP101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ101" t="s" s="2">
         <v>737</v>
-      </c>
-      <c r="AP101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ101" t="s" s="2">
-        <v>738</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15624,16 +15621,16 @@
         <v>256</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>739</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>740</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>741</v>
       </c>
-      <c r="N102" t="s" s="2">
+      <c r="O102" t="s" s="2">
         <v>742</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>743</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>83</v>
@@ -15661,28 +15658,28 @@
         <v>319</v>
       </c>
       <c r="Y102" t="s" s="2">
+        <v>743</v>
+      </c>
+      <c r="Z102" t="s" s="2">
         <v>744</v>
       </c>
-      <c r="Z102" t="s" s="2">
+      <c r="AA102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF102" t="s" s="2">
         <v>745</v>
-      </c>
-      <c r="AA102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF102" t="s" s="2">
-        <v>746</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
@@ -15709,21 +15706,21 @@
         <v>83</v>
       </c>
       <c r="AO102" t="s" s="2">
+        <v>746</v>
+      </c>
+      <c r="AP102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ102" t="s" s="2">
         <v>747</v>
-      </c>
-      <c r="AP102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ102" t="s" s="2">
-        <v>748</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15746,13 +15743,13 @@
         <v>93</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="M103" t="s" s="2">
         <v>750</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>751</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -15803,7 +15800,7 @@
         <v>83</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>81</v>
@@ -15836,15 +15833,15 @@
         <v>83</v>
       </c>
       <c r="AQ103" t="s" s="2">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15962,10 +15959,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -16085,10 +16082,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -16114,14 +16111,14 @@
         <v>256</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>756</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>757</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>758</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" t="s" s="2">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>83</v>
@@ -16149,28 +16146,28 @@
         <v>319</v>
       </c>
       <c r="Y106" t="s" s="2">
+        <v>759</v>
+      </c>
+      <c r="Z106" t="s" s="2">
         <v>760</v>
       </c>
-      <c r="Z106" t="s" s="2">
+      <c r="AA106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF106" t="s" s="2">
         <v>761</v>
-      </c>
-      <c r="AA106" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB106" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC106" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD106" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE106" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF106" t="s" s="2">
-        <v>762</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
@@ -16203,15 +16200,15 @@
         <v>83</v>
       </c>
       <c r="AQ106" t="s" s="2">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -16234,19 +16231,19 @@
         <v>93</v>
       </c>
       <c r="K107" t="s" s="2">
+        <v>764</v>
+      </c>
+      <c r="L107" t="s" s="2">
         <v>765</v>
       </c>
-      <c r="L107" t="s" s="2">
+      <c r="M107" t="s" s="2">
         <v>766</v>
       </c>
-      <c r="M107" t="s" s="2">
+      <c r="N107" t="s" s="2">
         <v>767</v>
       </c>
-      <c r="N107" t="s" s="2">
+      <c r="O107" t="s" s="2">
         <v>768</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>769</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>83</v>
@@ -16295,7 +16292,7 @@
         <v>83</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -16322,21 +16319,21 @@
         <v>83</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="AP107" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ107" t="s" s="2">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -16359,19 +16356,19 @@
         <v>93</v>
       </c>
       <c r="K108" t="s" s="2">
+        <v>772</v>
+      </c>
+      <c r="L108" t="s" s="2">
         <v>773</v>
       </c>
-      <c r="L108" t="s" s="2">
+      <c r="M108" t="s" s="2">
         <v>774</v>
       </c>
-      <c r="M108" t="s" s="2">
+      <c r="N108" t="s" s="2">
         <v>775</v>
       </c>
-      <c r="N108" t="s" s="2">
+      <c r="O108" t="s" s="2">
         <v>776</v>
-      </c>
-      <c r="O108" t="s" s="2">
-        <v>777</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>83</v>
@@ -16420,7 +16417,7 @@
         <v>83</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -16447,21 +16444,21 @@
         <v>83</v>
       </c>
       <c r="AO108" t="s" s="2">
+        <v>778</v>
+      </c>
+      <c r="AP108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ108" t="s" s="2">
         <v>779</v>
-      </c>
-      <c r="AP108" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ108" t="s" s="2">
-        <v>780</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16484,19 +16481,19 @@
         <v>93</v>
       </c>
       <c r="K109" t="s" s="2">
+        <v>781</v>
+      </c>
+      <c r="L109" t="s" s="2">
         <v>782</v>
       </c>
-      <c r="L109" t="s" s="2">
+      <c r="M109" t="s" s="2">
         <v>783</v>
       </c>
-      <c r="M109" t="s" s="2">
+      <c r="N109" t="s" s="2">
         <v>784</v>
       </c>
-      <c r="N109" t="s" s="2">
+      <c r="O109" t="s" s="2">
         <v>785</v>
-      </c>
-      <c r="O109" t="s" s="2">
-        <v>786</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>83</v>
@@ -16545,7 +16542,7 @@
         <v>83</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
@@ -16572,21 +16569,21 @@
         <v>83</v>
       </c>
       <c r="AO109" t="s" s="2">
+        <v>787</v>
+      </c>
+      <c r="AP109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ109" t="s" s="2">
         <v>788</v>
-      </c>
-      <c r="AP109" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ109" t="s" s="2">
-        <v>789</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -16609,19 +16606,19 @@
         <v>93</v>
       </c>
       <c r="K110" t="s" s="2">
+        <v>790</v>
+      </c>
+      <c r="L110" t="s" s="2">
         <v>791</v>
       </c>
-      <c r="L110" t="s" s="2">
+      <c r="M110" t="s" s="2">
         <v>792</v>
       </c>
-      <c r="M110" t="s" s="2">
+      <c r="N110" t="s" s="2">
         <v>793</v>
       </c>
-      <c r="N110" t="s" s="2">
+      <c r="O110" t="s" s="2">
         <v>794</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>795</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>83</v>
@@ -16670,7 +16667,7 @@
         <v>83</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
@@ -16697,7 +16694,7 @@
         <v>83</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AP110" t="s" s="2">
         <v>83</v>
@@ -16708,10 +16705,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16734,17 +16731,17 @@
         <v>93</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="L111" t="s" s="2">
+        <v>798</v>
+      </c>
+      <c r="M111" t="s" s="2">
         <v>799</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>800</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" t="s" s="2">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>83</v>
@@ -16793,7 +16790,7 @@
         <v>83</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>81</v>
@@ -16820,7 +16817,7 @@
         <v>83</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AP111" t="s" s="2">
         <v>83</v>
@@ -16831,10 +16828,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16857,13 +16854,13 @@
         <v>83</v>
       </c>
       <c r="K112" t="s" s="2">
+        <v>803</v>
+      </c>
+      <c r="L112" t="s" s="2">
         <v>804</v>
       </c>
-      <c r="L112" t="s" s="2">
+      <c r="M112" t="s" s="2">
         <v>805</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>806</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -16914,7 +16911,7 @@
         <v>83</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
@@ -16938,10 +16935,10 @@
         <v>83</v>
       </c>
       <c r="AN112" t="s" s="2">
+        <v>806</v>
+      </c>
+      <c r="AO112" t="s" s="2">
         <v>807</v>
-      </c>
-      <c r="AO112" t="s" s="2">
-        <v>808</v>
       </c>
       <c r="AP112" t="s" s="2">
         <v>83</v>
@@ -16952,10 +16949,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -17073,10 +17070,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -17196,14 +17193,14 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
@@ -17225,10 +17222,10 @@
         <v>137</v>
       </c>
       <c r="L115" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="M115" t="s" s="2">
         <v>534</v>
-      </c>
-      <c r="M115" t="s" s="2">
-        <v>535</v>
       </c>
       <c r="N115" t="s" s="2">
         <v>180</v>
@@ -17283,7 +17280,7 @@
         <v>83</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>81</v>
@@ -17321,10 +17318,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -17347,16 +17344,16 @@
         <v>83</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="L116" t="s" s="2">
+        <v>812</v>
+      </c>
+      <c r="M116" t="s" s="2">
         <v>813</v>
       </c>
-      <c r="M116" t="s" s="2">
+      <c r="N116" t="s" s="2">
         <v>814</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>815</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -17406,7 +17403,7 @@
         <v>83</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>81</v>
@@ -17433,7 +17430,7 @@
         <v>83</v>
       </c>
       <c r="AO116" t="s" s="2">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="AP116" t="s" s="2">
         <v>83</v>
@@ -17444,10 +17441,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -17565,10 +17562,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -17688,14 +17685,14 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
@@ -17717,10 +17714,10 @@
         <v>137</v>
       </c>
       <c r="L119" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="M119" t="s" s="2">
         <v>534</v>
-      </c>
-      <c r="M119" t="s" s="2">
-        <v>535</v>
       </c>
       <c r="N119" t="s" s="2">
         <v>180</v>
@@ -17775,7 +17772,7 @@
         <v>83</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>81</v>
@@ -17813,10 +17810,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17839,13 +17836,13 @@
         <v>83</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="L120" t="s" s="2">
+        <v>820</v>
+      </c>
+      <c r="M120" t="s" s="2">
         <v>821</v>
-      </c>
-      <c r="M120" t="s" s="2">
-        <v>822</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -17896,7 +17893,7 @@
         <v>83</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>81</v>
@@ -17923,7 +17920,7 @@
         <v>83</v>
       </c>
       <c r="AO120" t="s" s="2">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="AP120" t="s" s="2">
         <v>83</v>
@@ -17934,10 +17931,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17960,13 +17957,13 @@
         <v>83</v>
       </c>
       <c r="K121" t="s" s="2">
+        <v>824</v>
+      </c>
+      <c r="L121" t="s" s="2">
         <v>825</v>
       </c>
-      <c r="L121" t="s" s="2">
+      <c r="M121" t="s" s="2">
         <v>826</v>
-      </c>
-      <c r="M121" t="s" s="2">
-        <v>827</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -18017,7 +18014,7 @@
         <v>83</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>81</v>
@@ -18044,7 +18041,7 @@
         <v>83</v>
       </c>
       <c r="AO121" t="s" s="2">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="AP121" t="s" s="2">
         <v>83</v>
@@ -18055,10 +18052,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -18081,13 +18078,13 @@
         <v>83</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="L122" t="s" s="2">
+        <v>829</v>
+      </c>
+      <c r="M122" t="s" s="2">
         <v>830</v>
-      </c>
-      <c r="M122" t="s" s="2">
-        <v>831</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -18138,7 +18135,7 @@
         <v>83</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>81</v>
@@ -18165,7 +18162,7 @@
         <v>83</v>
       </c>
       <c r="AO122" t="s" s="2">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="AP122" t="s" s="2">
         <v>83</v>
@@ -18176,10 +18173,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -18205,16 +18202,16 @@
         <v>290</v>
       </c>
       <c r="L123" t="s" s="2">
+        <v>832</v>
+      </c>
+      <c r="M123" t="s" s="2">
         <v>833</v>
       </c>
-      <c r="M123" t="s" s="2">
+      <c r="N123" t="s" s="2">
         <v>834</v>
       </c>
-      <c r="N123" t="s" s="2">
+      <c r="O123" t="s" s="2">
         <v>835</v>
-      </c>
-      <c r="O123" t="s" s="2">
-        <v>836</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>83</v>
@@ -18263,7 +18260,7 @@
         <v>83</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>81</v>
@@ -18287,10 +18284,10 @@
         <v>83</v>
       </c>
       <c r="AN123" t="s" s="2">
+        <v>836</v>
+      </c>
+      <c r="AO123" t="s" s="2">
         <v>837</v>
-      </c>
-      <c r="AO123" t="s" s="2">
-        <v>838</v>
       </c>
       <c r="AP123" t="s" s="2">
         <v>83</v>
@@ -18301,10 +18298,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -18327,16 +18324,16 @@
         <v>83</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="L124" t="s" s="2">
+        <v>839</v>
+      </c>
+      <c r="M124" t="s" s="2">
         <v>840</v>
       </c>
-      <c r="M124" t="s" s="2">
+      <c r="N124" t="s" s="2">
         <v>841</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>842</v>
       </c>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
@@ -18386,7 +18383,7 @@
         <v>83</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>81</v>
@@ -18401,33 +18398,33 @@
         <v>104</v>
       </c>
       <c r="AK124" t="s" s="2">
+        <v>842</v>
+      </c>
+      <c r="AL124" t="s" s="2">
         <v>843</v>
       </c>
-      <c r="AL124" t="s" s="2">
+      <c r="AM124" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN124" t="s" s="2">
         <v>844</v>
       </c>
-      <c r="AM124" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN124" t="s" s="2">
+      <c r="AO124" t="s" s="2">
         <v>845</v>
       </c>
-      <c r="AO124" t="s" s="2">
+      <c r="AP124" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ124" t="s" s="2">
         <v>846</v>
-      </c>
-      <c r="AP124" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ124" t="s" s="2">
-        <v>847</v>
       </c>
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -18450,13 +18447,13 @@
         <v>83</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="L125" t="s" s="2">
+        <v>848</v>
+      </c>
+      <c r="M125" t="s" s="2">
         <v>849</v>
-      </c>
-      <c r="M125" t="s" s="2">
-        <v>850</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
@@ -18507,7 +18504,7 @@
         <v>83</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>81</v>
@@ -18522,33 +18519,33 @@
         <v>104</v>
       </c>
       <c r="AK125" t="s" s="2">
+        <v>850</v>
+      </c>
+      <c r="AL125" t="s" s="2">
         <v>851</v>
       </c>
-      <c r="AL125" t="s" s="2">
+      <c r="AM125" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN125" t="s" s="2">
         <v>852</v>
       </c>
-      <c r="AM125" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN125" t="s" s="2">
+      <c r="AO125" t="s" s="2">
         <v>853</v>
       </c>
-      <c r="AO125" t="s" s="2">
+      <c r="AP125" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ125" t="s" s="2">
         <v>854</v>
-      </c>
-      <c r="AP125" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ125" t="s" s="2">
-        <v>855</v>
       </c>
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -18571,16 +18568,16 @@
         <v>83</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="L126" t="s" s="2">
+        <v>856</v>
+      </c>
+      <c r="M126" t="s" s="2">
         <v>857</v>
       </c>
-      <c r="M126" t="s" s="2">
+      <c r="N126" t="s" s="2">
         <v>858</v>
-      </c>
-      <c r="N126" t="s" s="2">
-        <v>859</v>
       </c>
       <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
@@ -18630,7 +18627,7 @@
         <v>83</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>81</v>
@@ -18645,19 +18642,19 @@
         <v>104</v>
       </c>
       <c r="AK126" t="s" s="2">
+        <v>859</v>
+      </c>
+      <c r="AL126" t="s" s="2">
         <v>860</v>
       </c>
-      <c r="AL126" t="s" s="2">
+      <c r="AM126" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN126" t="s" s="2">
         <v>861</v>
       </c>
-      <c r="AM126" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN126" t="s" s="2">
+      <c r="AO126" t="s" s="2">
         <v>862</v>
-      </c>
-      <c r="AO126" t="s" s="2">
-        <v>863</v>
       </c>
       <c r="AP126" t="s" s="2">
         <v>83</v>
@@ -18668,10 +18665,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -18697,10 +18694,10 @@
         <v>297</v>
       </c>
       <c r="L127" t="s" s="2">
+        <v>864</v>
+      </c>
+      <c r="M127" t="s" s="2">
         <v>865</v>
-      </c>
-      <c r="M127" t="s" s="2">
-        <v>866</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -18751,7 +18748,7 @@
         <v>83</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>81</v>
@@ -18778,10 +18775,10 @@
         <v>83</v>
       </c>
       <c r="AO127" t="s" s="2">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="AP127" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AQ127" t="s" s="2">
         <v>83</v>
@@ -18789,10 +18786,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18815,13 +18812,13 @@
         <v>83</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="L128" t="s" s="2">
+        <v>868</v>
+      </c>
+      <c r="M128" t="s" s="2">
         <v>869</v>
-      </c>
-      <c r="M128" t="s" s="2">
-        <v>870</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -18872,7 +18869,7 @@
         <v>83</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>81</v>
@@ -18896,10 +18893,10 @@
         <v>83</v>
       </c>
       <c r="AN128" t="s" s="2">
+        <v>870</v>
+      </c>
+      <c r="AO128" t="s" s="2">
         <v>871</v>
-      </c>
-      <c r="AO128" t="s" s="2">
-        <v>872</v>
       </c>
       <c r="AP128" t="s" s="2">
         <v>83</v>
@@ -18910,10 +18907,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -19031,10 +19028,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -19154,14 +19151,14 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
@@ -19183,10 +19180,10 @@
         <v>137</v>
       </c>
       <c r="L131" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="M131" t="s" s="2">
         <v>534</v>
-      </c>
-      <c r="M131" t="s" s="2">
-        <v>535</v>
       </c>
       <c r="N131" t="s" s="2">
         <v>180</v>
@@ -19241,7 +19238,7 @@
         <v>83</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>81</v>
@@ -19279,10 +19276,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -19305,16 +19302,16 @@
         <v>83</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="L132" t="s" s="2">
+        <v>876</v>
+      </c>
+      <c r="M132" t="s" s="2">
         <v>877</v>
       </c>
-      <c r="M132" t="s" s="2">
+      <c r="N132" t="s" s="2">
         <v>878</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>879</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -19343,11 +19340,11 @@
         <v>319</v>
       </c>
       <c r="Y132" t="s" s="2">
+        <v>879</v>
+      </c>
+      <c r="Z132" t="s" s="2">
         <v>880</v>
       </c>
-      <c r="Z132" t="s" s="2">
-        <v>881</v>
-      </c>
       <c r="AA132" t="s" s="2">
         <v>83</v>
       </c>
@@ -19364,7 +19361,7 @@
         <v>83</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>92</v>
@@ -19388,24 +19385,24 @@
         <v>83</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="AO132" t="s" s="2">
+        <v>881</v>
+      </c>
+      <c r="AP132" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ132" t="s" s="2">
         <v>882</v>
-      </c>
-      <c r="AP132" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ132" t="s" s="2">
-        <v>883</v>
       </c>
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -19431,10 +19428,10 @@
         <v>256</v>
       </c>
       <c r="L133" t="s" s="2">
+        <v>884</v>
+      </c>
+      <c r="M133" t="s" s="2">
         <v>885</v>
-      </c>
-      <c r="M133" t="s" s="2">
-        <v>886</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -19464,11 +19461,11 @@
         <v>319</v>
       </c>
       <c r="Y133" t="s" s="2">
+        <v>886</v>
+      </c>
+      <c r="Z133" t="s" s="2">
         <v>887</v>
       </c>
-      <c r="Z133" t="s" s="2">
-        <v>888</v>
-      </c>
       <c r="AA133" t="s" s="2">
         <v>83</v>
       </c>
@@ -19485,7 +19482,7 @@
         <v>83</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>81</v>
@@ -19509,24 +19506,24 @@
         <v>83</v>
       </c>
       <c r="AN133" t="s" s="2">
+        <v>888</v>
+      </c>
+      <c r="AO133" t="s" s="2">
         <v>889</v>
       </c>
-      <c r="AO133" t="s" s="2">
+      <c r="AP133" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ133" t="s" s="2">
         <v>890</v>
-      </c>
-      <c r="AP133" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ133" t="s" s="2">
-        <v>891</v>
       </c>
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -19549,13 +19546,13 @@
         <v>83</v>
       </c>
       <c r="K134" t="s" s="2">
+        <v>892</v>
+      </c>
+      <c r="L134" t="s" s="2">
         <v>893</v>
       </c>
-      <c r="L134" t="s" s="2">
+      <c r="M134" t="s" s="2">
         <v>894</v>
-      </c>
-      <c r="M134" t="s" s="2">
-        <v>895</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -19606,7 +19603,7 @@
         <v>83</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>81</v>
@@ -19627,13 +19624,13 @@
         <v>83</v>
       </c>
       <c r="AM134" t="s" s="2">
+        <v>895</v>
+      </c>
+      <c r="AN134" t="s" s="2">
+        <v>888</v>
+      </c>
+      <c r="AO134" t="s" s="2">
         <v>896</v>
-      </c>
-      <c r="AN134" t="s" s="2">
-        <v>889</v>
-      </c>
-      <c r="AO134" t="s" s="2">
-        <v>897</v>
       </c>
       <c r="AP134" t="s" s="2">
         <v>83</v>
@@ -19644,14 +19641,14 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
@@ -19670,16 +19667,16 @@
         <v>83</v>
       </c>
       <c r="K135" t="s" s="2">
+        <v>899</v>
+      </c>
+      <c r="L135" t="s" s="2">
         <v>900</v>
       </c>
-      <c r="L135" t="s" s="2">
+      <c r="M135" t="s" s="2">
         <v>901</v>
       </c>
-      <c r="M135" t="s" s="2">
+      <c r="N135" t="s" s="2">
         <v>902</v>
-      </c>
-      <c r="N135" t="s" s="2">
-        <v>903</v>
       </c>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
@@ -19729,7 +19726,7 @@
         <v>83</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>81</v>
@@ -19756,7 +19753,7 @@
         <v>83</v>
       </c>
       <c r="AO135" t="s" s="2">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="AP135" t="s" s="2">
         <v>83</v>
@@ -19767,10 +19764,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19793,16 +19790,16 @@
         <v>83</v>
       </c>
       <c r="K136" t="s" s="2">
+        <v>905</v>
+      </c>
+      <c r="L136" t="s" s="2">
         <v>906</v>
       </c>
-      <c r="L136" t="s" s="2">
+      <c r="M136" t="s" s="2">
         <v>907</v>
       </c>
-      <c r="M136" t="s" s="2">
+      <c r="N136" t="s" s="2">
         <v>908</v>
-      </c>
-      <c r="N136" t="s" s="2">
-        <v>909</v>
       </c>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
@@ -19852,7 +19849,7 @@
         <v>83</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>81</v>
@@ -19873,13 +19870,13 @@
         <v>83</v>
       </c>
       <c r="AM136" t="s" s="2">
+        <v>909</v>
+      </c>
+      <c r="AN136" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO136" t="s" s="2">
         <v>910</v>
-      </c>
-      <c r="AN136" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO136" t="s" s="2">
-        <v>911</v>
       </c>
       <c r="AP136" t="s" s="2">
         <v>83</v>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestPending.xlsx
+++ b/docs/StructureDefinition-MedicationRequestPending.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
